--- a/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
+++ b/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dee/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dee/Desktop/GitHub- Repo/tms/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B132BA1E-7498-FF46-B2F5-CDA7A65DDD4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{528FA606-338F-FC4E-9D7F-FF9663C7EEBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17440" xr2:uid="{E6C00C04-EC41-2C4E-99E6-E8DF178218EF}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17440" activeTab="2" xr2:uid="{E6C00C04-EC41-2C4E-99E6-E8DF178218EF}"/>
   </bookViews>
   <sheets>
     <sheet name="DB capacity" sheetId="1" r:id="rId1"/>
@@ -2375,9 +2375,6 @@
     <t>Capacity</t>
   </si>
   <si>
-    <t>20T</t>
-  </si>
-  <si>
     <t>15T</t>
   </si>
   <si>
@@ -2409,6 +2406,9 @@
   </si>
   <si>
     <t>Frequency</t>
+  </si>
+  <si>
+    <t>18T</t>
   </si>
 </sst>
 </file>
@@ -9143,7 +9143,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="25" t="s">
-        <v>776</v>
+        <v>787</v>
       </c>
       <c r="B2" s="26">
         <v>1000</v>
@@ -9151,7 +9151,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="25" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B3" s="26">
         <v>800</v>
@@ -9159,7 +9159,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="25" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B4" s="26">
         <v>600</v>
@@ -9167,7 +9167,7 @@
     </row>
     <row r="5" spans="1:2" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B5" s="28">
         <v>350</v>
@@ -9175,34 +9175,34 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="31" t="s">
+        <v>785</v>
+      </c>
+      <c r="B11" s="31" t="s">
         <v>786</v>
-      </c>
-      <c r="B11" s="31" t="s">
-        <v>787</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="19" t="s">
+        <v>779</v>
+      </c>
+      <c r="B12" s="19" t="s">
         <v>780</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="19" t="s">
+        <v>781</v>
+      </c>
+      <c r="B13" s="19" t="s">
         <v>782</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="B14" s="19" t="s">
         <v>784</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>785</v>
       </c>
     </row>
   </sheetData>

--- a/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
+++ b/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dee/Desktop/GitHub- Repo/tms/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dee/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{528FA606-338F-FC4E-9D7F-FF9663C7EEBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B132BA1E-7498-FF46-B2F5-CDA7A65DDD4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17440" activeTab="2" xr2:uid="{E6C00C04-EC41-2C4E-99E6-E8DF178218EF}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17440" xr2:uid="{E6C00C04-EC41-2C4E-99E6-E8DF178218EF}"/>
   </bookViews>
   <sheets>
     <sheet name="DB capacity" sheetId="1" r:id="rId1"/>
@@ -2375,6 +2375,9 @@
     <t>Capacity</t>
   </si>
   <si>
+    <t>20T</t>
+  </si>
+  <si>
     <t>15T</t>
   </si>
   <si>
@@ -2406,9 +2409,6 @@
   </si>
   <si>
     <t>Frequency</t>
-  </si>
-  <si>
-    <t>18T</t>
   </si>
 </sst>
 </file>
@@ -9143,7 +9143,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="25" t="s">
-        <v>787</v>
+        <v>776</v>
       </c>
       <c r="B2" s="26">
         <v>1000</v>
@@ -9151,7 +9151,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="25" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B3" s="26">
         <v>800</v>
@@ -9159,7 +9159,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="25" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B4" s="26">
         <v>600</v>
@@ -9167,7 +9167,7 @@
     </row>
     <row r="5" spans="1:2" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B5" s="28">
         <v>350</v>
@@ -9175,34 +9175,34 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="31" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="19" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="19" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="19" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
   </sheetData>

--- a/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
+++ b/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dee/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dee/Desktop/GitHub- Repo/tms/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B132BA1E-7498-FF46-B2F5-CDA7A65DDD4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17440" xr2:uid="{E6C00C04-EC41-2C4E-99E6-E8DF178218EF}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17440" activeTab="1" xr2:uid="{E6C00C04-EC41-2C4E-99E6-E8DF178218EF}"/>
   </bookViews>
   <sheets>
     <sheet name="DB capacity" sheetId="1" r:id="rId1"/>

--- a/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
+++ b/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dee/Desktop/GitHub- Repo/tms/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B132BA1E-7498-FF46-B2F5-CDA7A65DDD4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD245A52-F7AB-544C-8945-CBEC40280485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17440" activeTab="1" xr2:uid="{E6C00C04-EC41-2C4E-99E6-E8DF178218EF}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17440" activeTab="2" xr2:uid="{E6C00C04-EC41-2C4E-99E6-E8DF178218EF}"/>
   </bookViews>
   <sheets>
     <sheet name="DB capacity" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DB capacity'!$B$3:$F$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vehicle Database'!$A$1:$G$111</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2149" uniqueCount="788">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2150" uniqueCount="789">
   <si>
     <t>Agency / Route</t>
   </si>
@@ -2409,6 +2410,9 @@
   </si>
   <si>
     <t>Frequency</t>
+  </si>
+  <si>
+    <t>18T</t>
   </si>
 </sst>
 </file>
@@ -9126,7 +9130,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{585CAF69-F7C5-D145-9C83-B92BB69526E1}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.83203125" bestFit="1" customWidth="1"/>
@@ -9146,62 +9150,70 @@
         <v>776</v>
       </c>
       <c r="B2" s="26">
-        <v>1000</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="25" t="s">
-        <v>777</v>
+        <v>788</v>
       </c>
       <c r="B3" s="26">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="25" t="s">
+        <v>777</v>
+      </c>
+      <c r="B4" s="26">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="25" t="s">
         <v>778</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B5" s="26">
         <v>600</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="27" t="s">
+    <row r="6" spans="1:2" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="27" t="s">
         <v>779</v>
       </c>
-      <c r="B5" s="28">
+      <c r="B6" s="28">
         <v>350</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="31" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="31" t="s">
         <v>786</v>
       </c>
-      <c r="B11" s="31" t="s">
+      <c r="B12" s="31" t="s">
         <v>787</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="19" t="s">
-        <v>780</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="19" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="19" t="s">
+        <v>782</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="19" t="s">
         <v>784</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B15" s="19" t="s">
         <v>785</v>
       </c>
     </row>

--- a/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
+++ b/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dee/Desktop/GitHub- Repo/tms/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B4D5CEE-C4B7-0147-A349-4B9B44875F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{801888A7-6AD2-AD41-95CA-508518243C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,6 +18,9 @@
     <sheet name="Assumptions" sheetId="3" r:id="rId3"/>
     <sheet name="DB Target" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vehicle Database'!$A$1:$G$60</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1893" uniqueCount="727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1853" uniqueCount="719">
   <si>
     <t>S. N.</t>
   </si>
@@ -74,12 +77,6 @@
     <t>Own</t>
   </si>
   <si>
-    <t>UP32AN3938</t>
-  </si>
-  <si>
-    <t>UP32AN6958</t>
-  </si>
-  <si>
     <t>UP32AN9883</t>
   </si>
   <si>
@@ -167,9 +164,6 @@
     <t>UP41AT2863</t>
   </si>
   <si>
-    <t>UP41AT4026</t>
-  </si>
-  <si>
     <t>UP41T1378</t>
   </si>
   <si>
@@ -188,9 +182,6 @@
     <t>UP41T6972</t>
   </si>
   <si>
-    <t>UP41T8559</t>
-  </si>
-  <si>
     <t>UP41T9169</t>
   </si>
   <si>
@@ -200,9 +191,6 @@
     <t>UP41T4849</t>
   </si>
   <si>
-    <t>UP32BN4925</t>
-  </si>
-  <si>
     <t>UP41T7677</t>
   </si>
   <si>
@@ -215,9 +203,6 @@
     <t>UP32HN2127</t>
   </si>
   <si>
-    <t>UP32HN2137</t>
-  </si>
-  <si>
     <t>UP41T5380</t>
   </si>
   <si>
@@ -233,13 +218,7 @@
     <t>UP32CZ7229</t>
   </si>
   <si>
-    <t>UP41T6902</t>
-  </si>
-  <si>
     <t>UP32AN6957</t>
-  </si>
-  <si>
-    <t>UP41T5263</t>
   </si>
   <si>
     <t>UP32CZ7228</t>
@@ -2986,33 +2965,33 @@
     <row r="2" spans="2:6" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="2:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="3" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B4" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F4" s="6">
         <v>18</v>
@@ -3020,16 +2999,16 @@
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B5" s="5" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F5" s="6">
         <v>15</v>
@@ -3037,16 +3016,16 @@
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B6" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F6" s="6">
         <v>15</v>
@@ -3054,16 +3033,16 @@
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B7" s="5" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F7" s="6">
         <v>4</v>
@@ -3071,16 +3050,16 @@
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B8" s="5" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F8" s="6">
         <v>15</v>
@@ -3088,16 +3067,16 @@
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B9" s="5" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F9" s="6">
         <v>15</v>
@@ -3105,16 +3084,16 @@
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B10" s="5" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F10" s="6">
         <v>4</v>
@@ -3122,16 +3101,16 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B11" s="5" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F11" s="6">
         <v>15</v>
@@ -3139,16 +3118,16 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B12" s="5" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F12" s="6">
         <v>15</v>
@@ -3156,16 +3135,16 @@
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B13" s="5" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F13" s="6">
         <v>25</v>
@@ -3173,16 +3152,16 @@
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B14" s="5" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F14" s="6">
         <v>15</v>
@@ -3190,16 +3169,16 @@
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B15" s="5" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F15" s="6">
         <v>18</v>
@@ -3207,16 +3186,16 @@
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B16" s="5" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F16" s="6">
         <v>18</v>
@@ -3224,16 +3203,16 @@
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B17" s="5" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F17" s="6">
         <v>9</v>
@@ -3241,16 +3220,16 @@
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B18" s="5" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F18" s="6">
         <v>9</v>
@@ -3258,16 +3237,16 @@
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B19" s="5" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F19" s="6">
         <v>15</v>
@@ -3275,16 +3254,16 @@
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B20" s="5" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F20" s="6">
         <v>15</v>
@@ -3292,16 +3271,16 @@
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B21" s="5" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F21" s="6">
         <v>15</v>
@@ -3309,16 +3288,16 @@
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="5" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F22" s="6">
         <v>9</v>
@@ -3326,16 +3305,16 @@
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B23" s="5" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F23" s="6">
         <v>4</v>
@@ -3343,16 +3322,16 @@
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B24" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F24" s="6">
         <v>9</v>
@@ -3360,16 +3339,16 @@
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B25" s="5" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F25" s="6">
         <v>6</v>
@@ -3377,16 +3356,16 @@
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B26" s="5" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F26" s="6">
         <v>25</v>
@@ -3394,16 +3373,16 @@
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B27" s="5" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F27" s="6">
         <v>25</v>
@@ -3411,16 +3390,16 @@
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B28" s="5" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F28" s="6">
         <v>4</v>
@@ -3428,16 +3407,16 @@
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B29" s="5" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F29" s="6">
         <v>15</v>
@@ -3445,16 +3424,16 @@
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="5" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F30" s="6">
         <v>9</v>
@@ -3462,16 +3441,16 @@
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B31" s="5" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F31" s="6">
         <v>25</v>
@@ -3479,16 +3458,16 @@
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B32" s="5" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F32" s="6">
         <v>6</v>
@@ -3496,16 +3475,16 @@
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B33" s="5" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F33" s="6">
         <v>9</v>
@@ -3513,16 +3492,16 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B34" s="5" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F34" s="6">
         <v>15</v>
@@ -3530,16 +3509,16 @@
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B35" s="5" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F35" s="6">
         <v>9</v>
@@ -3547,16 +3526,16 @@
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B36" s="5" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F36" s="6">
         <v>4</v>
@@ -3564,16 +3543,16 @@
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B37" s="5" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F37" s="6">
         <v>15</v>
@@ -3581,16 +3560,16 @@
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="5" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F38" s="6">
         <v>15</v>
@@ -3598,16 +3577,16 @@
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B39" s="5" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F39" s="6">
         <v>4</v>
@@ -3615,16 +3594,16 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B40" s="5" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F40" s="6">
         <v>25</v>
@@ -3632,16 +3611,16 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B41" s="5" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F41" s="6">
         <v>25</v>
@@ -3649,16 +3628,16 @@
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B42" s="5" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F42" s="6">
         <v>15</v>
@@ -3666,16 +3645,16 @@
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B43" s="5" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F43" s="6">
         <v>4</v>
@@ -3683,16 +3662,16 @@
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B44" s="5" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F44" s="6">
         <v>15</v>
@@ -3700,31 +3679,31 @@
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B45" s="5" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="F45" s="6"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="5" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F46" s="6">
         <v>4</v>
@@ -3732,16 +3711,16 @@
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B47" s="5" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F47" s="6">
         <v>4</v>
@@ -3749,16 +3728,16 @@
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B48" s="5" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F48" s="6">
         <v>6</v>
@@ -3766,16 +3745,16 @@
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B49" s="5" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F49" s="6">
         <v>15</v>
@@ -3783,16 +3762,16 @@
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B50" s="5" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F50" s="6">
         <v>4</v>
@@ -3800,46 +3779,46 @@
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B51" s="5" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F51" s="6"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="5" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F52" s="6"/>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B53" s="5" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="F53" s="6">
         <v>4</v>
@@ -3847,16 +3826,16 @@
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B54" s="5" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F54" s="6">
         <v>25</v>
@@ -3864,16 +3843,16 @@
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B55" s="5" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F55" s="6">
         <v>15</v>
@@ -3881,16 +3860,16 @@
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B56" s="5" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F56" s="6">
         <v>15</v>
@@ -3898,16 +3877,16 @@
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B57" s="5" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F57" s="6">
         <v>9</v>
@@ -3915,16 +3894,16 @@
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B58" s="5" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F58" s="6">
         <v>25</v>
@@ -3932,16 +3911,16 @@
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B59" s="5" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F59" s="6">
         <v>15</v>
@@ -3949,16 +3928,16 @@
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B60" s="5" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F60" s="6">
         <v>15</v>
@@ -3966,16 +3945,16 @@
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B61" s="5" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F61" s="6">
         <v>25</v>
@@ -3983,16 +3962,16 @@
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B62" s="5" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F62" s="6">
         <v>9</v>
@@ -4000,16 +3979,16 @@
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B63" s="5" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F63" s="6">
         <v>25</v>
@@ -4017,16 +3996,16 @@
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B64" s="5" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F64" s="6">
         <v>12</v>
@@ -4034,16 +4013,16 @@
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B65" s="5" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F65" s="6">
         <v>25</v>
@@ -4051,16 +4030,16 @@
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B66" s="5" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F66" s="6">
         <v>25</v>
@@ -4068,16 +4047,16 @@
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B67" s="5" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F67" s="6">
         <v>25</v>
@@ -4085,16 +4064,16 @@
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B68" s="5" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F68" s="6">
         <v>25</v>
@@ -4102,16 +4081,16 @@
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B69" s="5" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F69" s="6">
         <v>15</v>
@@ -4119,16 +4098,16 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B70" s="5" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F70" s="6">
         <v>15</v>
@@ -4136,16 +4115,16 @@
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B71" s="5" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F71" s="6">
         <v>25</v>
@@ -4153,16 +4132,16 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B72" s="5" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F72" s="6">
         <v>18</v>
@@ -4170,16 +4149,16 @@
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B73" s="5" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="F73" s="6">
         <v>15</v>
@@ -4187,16 +4166,16 @@
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B74" s="5" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="F74" s="6">
         <v>15</v>
@@ -4204,16 +4183,16 @@
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B75" s="5" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F75" s="6">
         <v>25</v>
@@ -4221,16 +4200,16 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B76" s="5" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F76" s="6">
         <v>15</v>
@@ -4238,16 +4217,16 @@
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B77" s="5" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F77" s="6">
         <v>15</v>
@@ -4255,16 +4234,16 @@
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B78" s="5" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F78" s="6">
         <v>15</v>
@@ -4272,16 +4251,16 @@
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B79" s="5" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F79" s="6">
         <v>25</v>
@@ -4289,16 +4268,16 @@
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B80" s="5" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F80" s="6">
         <v>25</v>
@@ -4306,16 +4285,16 @@
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B81" s="5" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F81" s="6">
         <v>25</v>
@@ -4323,16 +4302,16 @@
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B82" s="5" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F82" s="6">
         <v>25</v>
@@ -4340,16 +4319,16 @@
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B83" s="5" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F83" s="6">
         <v>25</v>
@@ -4357,16 +4336,16 @@
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B84" s="5" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F84" s="6">
         <v>15</v>
@@ -4374,16 +4353,16 @@
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B85" s="5" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F85" s="6">
         <v>25</v>
@@ -4391,16 +4370,16 @@
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B86" s="5" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F86" s="6">
         <v>25</v>
@@ -4408,16 +4387,16 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B87" s="5" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F87" s="6">
         <v>25</v>
@@ -4425,16 +4404,16 @@
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B88" s="5" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F88" s="6">
         <v>15</v>
@@ -4442,16 +4421,16 @@
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B89" s="5" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F89" s="6">
         <v>15</v>
@@ -4459,16 +4438,16 @@
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B90" s="5" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F90" s="6">
         <v>15</v>
@@ -4476,16 +4455,16 @@
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B91" s="5" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F91" s="6">
         <v>15</v>
@@ -4493,16 +4472,16 @@
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B92" s="5" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F92" s="6">
         <v>15</v>
@@ -4510,16 +4489,16 @@
     </row>
     <row r="93" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B93" s="5" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F93" s="6">
         <v>18</v>
@@ -4527,16 +4506,16 @@
     </row>
     <row r="94" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B94" s="5" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F94" s="6">
         <v>15</v>
@@ -4544,16 +4523,16 @@
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B95" s="5" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F95" s="6">
         <v>25</v>
@@ -4561,16 +4540,16 @@
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B96" s="5" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F96" s="6">
         <v>15</v>
@@ -4578,16 +4557,16 @@
     </row>
     <row r="97" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B97" s="5" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F97" s="6">
         <v>25</v>
@@ -4595,16 +4574,16 @@
     </row>
     <row r="98" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B98" s="5" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F98" s="6">
         <v>25</v>
@@ -4612,16 +4591,16 @@
     </row>
     <row r="99" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B99" s="5" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F99" s="6">
         <v>25</v>
@@ -4629,16 +4608,16 @@
     </row>
     <row r="100" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B100" s="5" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F100" s="6">
         <v>15</v>
@@ -4646,16 +4625,16 @@
     </row>
     <row r="101" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B101" s="5" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F101" s="6">
         <v>15</v>
@@ -4663,16 +4642,16 @@
     </row>
     <row r="102" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B102" s="5" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F102" s="10">
         <v>25</v>
@@ -4680,16 +4659,16 @@
     </row>
     <row r="103" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B103" s="5" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F103" s="10">
         <v>15</v>
@@ -4697,16 +4676,16 @@
     </row>
     <row r="104" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B104" s="5" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F104" s="10">
         <v>15</v>
@@ -4714,16 +4693,16 @@
     </row>
     <row r="105" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B105" s="5" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F105" s="10">
         <v>15</v>
@@ -4731,16 +4710,16 @@
     </row>
     <row r="106" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B106" s="5" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F106" s="10">
         <v>15</v>
@@ -4748,16 +4727,16 @@
     </row>
     <row r="107" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B107" s="5" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F107" s="10">
         <v>25</v>
@@ -4765,16 +4744,16 @@
     </row>
     <row r="108" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B108" s="5" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F108" s="10">
         <v>15</v>
@@ -4782,16 +4761,16 @@
     </row>
     <row r="109" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B109" s="5" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F109" s="10">
         <v>15</v>
@@ -4799,16 +4778,16 @@
     </row>
     <row r="110" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B110" s="5" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F110" s="10">
         <v>25</v>
@@ -4816,16 +4795,16 @@
     </row>
     <row r="111" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B111" s="5" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F111" s="10">
         <v>25</v>
@@ -4833,16 +4812,16 @@
     </row>
     <row r="112" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B112" s="5" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F112" s="10">
         <v>6</v>
@@ -4850,16 +4829,16 @@
     </row>
     <row r="113" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B113" s="5" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F113" s="10">
         <v>15</v>
@@ -4867,16 +4846,16 @@
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B114" s="5" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="D114" s="10" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F114" s="10">
         <v>18</v>
@@ -4884,16 +4863,16 @@
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B115" s="5" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="D115" s="10" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F115" s="10">
         <v>25</v>
@@ -4901,16 +4880,16 @@
     </row>
     <row r="116" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B116" s="5" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="D116" s="10" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F116" s="10">
         <v>15</v>
@@ -4918,16 +4897,16 @@
     </row>
     <row r="117" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B117" s="5" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D117" s="10" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F117" s="10">
         <v>25</v>
@@ -4935,16 +4914,16 @@
     </row>
     <row r="118" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B118" s="5" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="D118" s="10" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F118" s="10">
         <v>15</v>
@@ -4952,16 +4931,16 @@
     </row>
     <row r="119" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B119" s="5" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="D119" s="10" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F119" s="10">
         <v>25</v>
@@ -4969,16 +4948,16 @@
     </row>
     <row r="120" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B120" s="5" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="D120" s="10" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F120" s="10">
         <v>25</v>
@@ -4986,16 +4965,16 @@
     </row>
     <row r="121" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B121" s="5" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="D121" s="10" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F121" s="10">
         <v>15</v>
@@ -5003,16 +4982,16 @@
     </row>
     <row r="122" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B122" s="5" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="D122" s="10" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F122" s="10">
         <v>15</v>
@@ -5020,16 +4999,16 @@
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B123" s="5" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="D123" s="10" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F123" s="10">
         <v>9</v>
@@ -5037,16 +5016,16 @@
     </row>
     <row r="124" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B124" s="5" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="D124" s="10" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F124" s="10">
         <v>15</v>
@@ -5054,16 +5033,16 @@
     </row>
     <row r="125" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B125" s="5" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="D125" s="10" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F125" s="10">
         <v>25</v>
@@ -5071,16 +5050,16 @@
     </row>
     <row r="126" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B126" s="5" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="D126" s="10" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F126" s="10">
         <v>15</v>
@@ -5088,16 +5067,16 @@
     </row>
     <row r="127" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B127" s="5" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="D127" s="10" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F127" s="10">
         <v>25</v>
@@ -5105,16 +5084,16 @@
     </row>
     <row r="128" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B128" s="5" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="D128" s="10" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F128" s="10">
         <v>15</v>
@@ -5122,16 +5101,16 @@
     </row>
     <row r="129" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B129" s="5" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="D129" s="10" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F129" s="10">
         <v>15</v>
@@ -5139,16 +5118,16 @@
     </row>
     <row r="130" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B130" s="11" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="D130" s="10" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F130" s="10">
         <v>15</v>
@@ -5156,16 +5135,16 @@
     </row>
     <row r="131" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B131" s="5" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F131" s="6">
         <v>15</v>
@@ -5173,16 +5152,16 @@
     </row>
     <row r="132" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B132" s="5" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F132" s="6">
         <v>15</v>
@@ -5190,16 +5169,16 @@
     </row>
     <row r="133" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B133" s="5" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E133" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F133" s="6">
         <v>15</v>
@@ -5207,16 +5186,16 @@
     </row>
     <row r="134" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B134" s="5" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F134" s="6">
         <v>15</v>
@@ -5224,16 +5203,16 @@
     </row>
     <row r="135" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B135" s="5" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F135" s="6">
         <v>15</v>
@@ -5241,16 +5220,16 @@
     </row>
     <row r="136" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B136" s="5" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F136" s="6">
         <v>15</v>
@@ -5258,16 +5237,16 @@
     </row>
     <row r="137" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B137" s="5" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F137" s="6">
         <v>25</v>
@@ -5275,16 +5254,16 @@
     </row>
     <row r="138" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B138" s="5" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F138" s="6">
         <v>15</v>
@@ -5292,16 +5271,16 @@
     </row>
     <row r="139" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B139" s="5" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E139" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F139" s="6">
         <v>15</v>
@@ -5309,16 +5288,16 @@
     </row>
     <row r="140" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B140" s="5" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F140" s="6">
         <v>15</v>
@@ -5326,16 +5305,16 @@
     </row>
     <row r="141" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B141" s="5" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E141" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F141" s="6">
         <v>15</v>
@@ -5343,16 +5322,16 @@
     </row>
     <row r="142" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B142" s="5" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F142" s="6">
         <v>25</v>
@@ -5360,16 +5339,16 @@
     </row>
     <row r="143" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B143" s="5" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E143" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F143" s="6">
         <v>15</v>
@@ -5377,16 +5356,16 @@
     </row>
     <row r="144" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B144" s="5" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F144" s="6">
         <v>15</v>
@@ -5394,16 +5373,16 @@
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B145" s="5" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E145" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F145" s="6">
         <v>15</v>
@@ -5411,16 +5390,16 @@
     </row>
     <row r="146" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B146" s="5" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F146" s="6">
         <v>15</v>
@@ -5428,16 +5407,16 @@
     </row>
     <row r="147" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B147" s="5" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F147" s="6">
         <v>15</v>
@@ -5445,16 +5424,16 @@
     </row>
     <row r="148" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B148" s="5" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F148" s="6">
         <v>15</v>
@@ -5462,16 +5441,16 @@
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B149" s="5" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E149" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F149" s="6">
         <v>15</v>
@@ -5479,16 +5458,16 @@
     </row>
     <row r="150" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B150" s="5" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F150" s="6">
         <v>25</v>
@@ -5496,16 +5475,16 @@
     </row>
     <row r="151" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B151" s="5" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E151" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F151" s="6">
         <v>15</v>
@@ -5513,16 +5492,16 @@
     </row>
     <row r="152" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B152" s="5" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F152" s="6">
         <v>15</v>
@@ -5530,16 +5509,16 @@
     </row>
     <row r="153" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B153" s="5" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E153" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F153" s="6">
         <v>18</v>
@@ -5547,16 +5526,16 @@
     </row>
     <row r="154" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B154" s="5" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F154" s="6">
         <v>25</v>
@@ -5564,16 +5543,16 @@
     </row>
     <row r="155" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B155" s="5" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E155" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F155" s="6">
         <v>15</v>
@@ -5581,16 +5560,16 @@
     </row>
     <row r="156" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B156" s="5" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F156" s="6">
         <v>15</v>
@@ -5598,16 +5577,16 @@
     </row>
     <row r="157" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B157" s="5" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="D157" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E157" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F157" s="6">
         <v>15</v>
@@ -5615,16 +5594,16 @@
     </row>
     <row r="158" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B158" s="5" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F158" s="6">
         <v>15</v>
@@ -5632,16 +5611,16 @@
     </row>
     <row r="159" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B159" s="5" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E159" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F159" s="6">
         <v>15</v>
@@ -5649,16 +5628,16 @@
     </row>
     <row r="160" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B160" s="5" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F160" s="6">
         <v>15</v>
@@ -5666,16 +5645,16 @@
     </row>
     <row r="161" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B161" s="5" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E161" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F161" s="6">
         <v>4</v>
@@ -5683,16 +5662,16 @@
     </row>
     <row r="162" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B162" s="5" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F162" s="6">
         <v>9</v>
@@ -5700,16 +5679,16 @@
     </row>
     <row r="163" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B163" s="5" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E163" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F163" s="6">
         <v>9</v>
@@ -5717,16 +5696,16 @@
     </row>
     <row r="164" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B164" s="5" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F164" s="6">
         <v>9</v>
@@ -5734,16 +5713,16 @@
     </row>
     <row r="165" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B165" s="5" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E165" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F165" s="6">
         <v>4</v>
@@ -5751,16 +5730,16 @@
     </row>
     <row r="166" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B166" s="5" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F166" s="6">
         <v>9</v>
@@ -5768,16 +5747,16 @@
     </row>
     <row r="167" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B167" s="5" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E167" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F167" s="6">
         <v>4</v>
@@ -5785,16 +5764,16 @@
     </row>
     <row r="168" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B168" s="5" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F168" s="6">
         <v>4</v>
@@ -5802,16 +5781,16 @@
     </row>
     <row r="169" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B169" s="5" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E169" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F169" s="6">
         <v>9</v>
@@ -5819,16 +5798,16 @@
     </row>
     <row r="170" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B170" s="5" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F170" s="6">
         <v>4</v>
@@ -5836,16 +5815,16 @@
     </row>
     <row r="171" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B171" s="5" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="D171" s="6" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E171" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F171" s="6">
         <v>9</v>
@@ -5853,16 +5832,16 @@
     </row>
     <row r="172" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B172" s="5" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="D172" s="6" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F172" s="6">
         <v>20</v>
@@ -5870,16 +5849,16 @@
     </row>
     <row r="173" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B173" s="5" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="D173" s="6" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E173" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F173" s="6">
         <v>4</v>
@@ -5887,16 +5866,16 @@
     </row>
     <row r="174" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B174" s="5" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="D174" s="6" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F174" s="6">
         <v>4</v>
@@ -5904,16 +5883,16 @@
     </row>
     <row r="175" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B175" s="5" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="D175" s="6" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E175" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F175" s="6">
         <v>9</v>
@@ -5921,16 +5900,16 @@
     </row>
     <row r="176" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B176" s="5" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F176" s="6">
         <v>4</v>
@@ -5938,16 +5917,16 @@
     </row>
     <row r="177" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B177" s="5" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E177" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F177" s="6">
         <v>12</v>
@@ -5955,16 +5934,16 @@
     </row>
     <row r="178" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B178" s="5" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="D178" s="6" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F178" s="6">
         <v>4</v>
@@ -5972,16 +5951,16 @@
     </row>
     <row r="179" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B179" s="5" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="D179" s="6" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E179" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F179" s="6">
         <v>9</v>
@@ -5989,16 +5968,16 @@
     </row>
     <row r="180" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B180" s="5" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="D180" s="6" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F180" s="6">
         <v>4</v>
@@ -6006,16 +5985,16 @@
     </row>
     <row r="181" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B181" s="5" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E181" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F181" s="6">
         <v>9</v>
@@ -6023,16 +6002,16 @@
     </row>
     <row r="182" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B182" s="5" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F182" s="6">
         <v>4</v>
@@ -6040,16 +6019,16 @@
     </row>
     <row r="183" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B183" s="5" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E183" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F183" s="6">
         <v>4</v>
@@ -6057,16 +6036,16 @@
     </row>
     <row r="184" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B184" s="5" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="D184" s="6" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F184" s="6">
         <v>9</v>
@@ -6074,16 +6053,16 @@
     </row>
     <row r="185" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B185" s="5" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E185" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F185" s="6">
         <v>4</v>
@@ -6091,16 +6070,16 @@
     </row>
     <row r="186" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B186" s="5" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F186" s="6">
         <v>4</v>
@@ -6108,16 +6087,16 @@
     </row>
     <row r="187" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B187" s="5" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E187" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F187" s="6">
         <v>4</v>
@@ -6125,16 +6104,16 @@
     </row>
     <row r="188" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B188" s="5" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F188" s="6">
         <v>9</v>
@@ -6142,16 +6121,16 @@
     </row>
     <row r="189" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B189" s="5" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E189" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F189" s="6">
         <v>4</v>
@@ -6159,16 +6138,16 @@
     </row>
     <row r="190" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B190" s="5" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="D190" s="6" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F190" s="6">
         <v>4</v>
@@ -6176,16 +6155,16 @@
     </row>
     <row r="191" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B191" s="5" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="D191" s="6" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E191" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F191" s="6">
         <v>9</v>
@@ -6193,16 +6172,16 @@
     </row>
     <row r="192" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B192" s="5" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F192" s="6">
         <v>9</v>
@@ -6210,16 +6189,16 @@
     </row>
     <row r="193" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B193" s="5" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E193" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F193" s="6">
         <v>9</v>
@@ -6227,16 +6206,16 @@
     </row>
     <row r="194" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B194" s="5" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F194" s="6">
         <v>4</v>
@@ -6244,16 +6223,16 @@
     </row>
     <row r="195" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B195" s="5" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="D195" s="6" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E195" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F195" s="6">
         <v>4</v>
@@ -6261,16 +6240,16 @@
     </row>
     <row r="196" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B196" s="5" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="D196" s="6" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F196" s="6">
         <v>4</v>
@@ -6278,16 +6257,16 @@
     </row>
     <row r="197" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B197" s="5" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="D197" s="6" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E197" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F197" s="6">
         <v>4</v>
@@ -6295,16 +6274,16 @@
     </row>
     <row r="198" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B198" s="5" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="D198" s="6" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F198" s="6">
         <v>4</v>
@@ -6312,16 +6291,16 @@
     </row>
     <row r="199" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B199" s="5" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="D199" s="6" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E199" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F199" s="6">
         <v>9</v>
@@ -6329,7 +6308,7 @@
     </row>
     <row r="200" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B200" s="5" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="C200" s="4"/>
       <c r="D200" s="6"/>
@@ -6338,7 +6317,7 @@
     </row>
     <row r="201" spans="2:6" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B201" s="12" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="C201" s="12"/>
       <c r="D201" s="13"/>
@@ -6415,48 +6394,24 @@
         <f>A2+1</f>
         <v>2</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="21">
-        <v>6</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="20" t="s">
-        <v>11</v>
-      </c>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="20"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="20">
         <f t="shared" ref="A4:A60" si="0">A3+1</f>
         <v>3</v>
       </c>
-      <c r="B4" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="21">
-        <v>6.5</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="20" t="s">
-        <v>11</v>
-      </c>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="20"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="20">
@@ -6467,7 +6422,7 @@
         <v>7</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>9</v>
@@ -6491,7 +6446,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D6" s="20" t="s">
         <v>9</v>
@@ -6515,7 +6470,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>9</v>
@@ -6539,7 +6494,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D8" s="20" t="s">
         <v>9</v>
@@ -6563,7 +6518,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D9" s="20" t="s">
         <v>9</v>
@@ -6587,7 +6542,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D10" s="20" t="s">
         <v>9</v>
@@ -6611,7 +6566,7 @@
         <v>7</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D11" s="20" t="s">
         <v>9</v>
@@ -6635,7 +6590,7 @@
         <v>7</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D12" s="20" t="s">
         <v>9</v>
@@ -6659,7 +6614,7 @@
         <v>7</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D13" s="20" t="s">
         <v>9</v>
@@ -6683,7 +6638,7 @@
         <v>7</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D14" s="20" t="s">
         <v>9</v>
@@ -6707,7 +6662,7 @@
         <v>7</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D15" s="20" t="s">
         <v>9</v>
@@ -6731,7 +6686,7 @@
         <v>7</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D16" s="20" t="s">
         <v>9</v>
@@ -6755,7 +6710,7 @@
         <v>7</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D17" s="20" t="s">
         <v>9</v>
@@ -6779,7 +6734,7 @@
         <v>7</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D18" s="20" t="s">
         <v>9</v>
@@ -6803,7 +6758,7 @@
         <v>7</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D19" s="20" t="s">
         <v>9</v>
@@ -6827,7 +6782,7 @@
         <v>7</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D20" s="20" t="s">
         <v>9</v>
@@ -6851,7 +6806,7 @@
         <v>7</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D21" s="20" t="s">
         <v>9</v>
@@ -6875,7 +6830,7 @@
         <v>7</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D22" s="20" t="s">
         <v>9</v>
@@ -6899,7 +6854,7 @@
         <v>7</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D23" s="20" t="s">
         <v>9</v>
@@ -6923,7 +6878,7 @@
         <v>7</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D24" s="20" t="s">
         <v>9</v>
@@ -6947,7 +6902,7 @@
         <v>7</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D25" s="20" t="s">
         <v>9</v>
@@ -6971,7 +6926,7 @@
         <v>7</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D26" s="20" t="s">
         <v>9</v>
@@ -6995,7 +6950,7 @@
         <v>7</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D27" s="20" t="s">
         <v>9</v>
@@ -7019,7 +6974,7 @@
         <v>7</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D28" s="20" t="s">
         <v>9</v>
@@ -7043,7 +6998,7 @@
         <v>7</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D29" s="20" t="s">
         <v>9</v>
@@ -7067,7 +7022,7 @@
         <v>7</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D30" s="20" t="s">
         <v>9</v>
@@ -7091,7 +7046,7 @@
         <v>7</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D31" s="20" t="s">
         <v>9</v>
@@ -7115,7 +7070,7 @@
         <v>7</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D32" s="20" t="s">
         <v>9</v>
@@ -7139,7 +7094,7 @@
         <v>7</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D33" s="20" t="s">
         <v>9</v>
@@ -7156,27 +7111,15 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="20">
-        <f t="shared" si="0"/>
+        <f>A33+1</f>
         <v>33</v>
       </c>
-      <c r="B34" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D34" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" s="21">
-        <v>9</v>
-      </c>
-      <c r="F34" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G34" s="20" t="s">
-        <v>11</v>
-      </c>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="20"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="20">
@@ -7187,7 +7130,7 @@
         <v>7</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D35" s="20" t="s">
         <v>9</v>
@@ -7211,7 +7154,7 @@
         <v>7</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D36" s="20" t="s">
         <v>9</v>
@@ -7235,7 +7178,7 @@
         <v>7</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D37" s="20" t="s">
         <v>9</v>
@@ -7259,7 +7202,7 @@
         <v>7</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D38" s="20" t="s">
         <v>9</v>
@@ -7283,7 +7226,7 @@
         <v>7</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D39" s="20" t="s">
         <v>9</v>
@@ -7307,7 +7250,7 @@
         <v>7</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D40" s="20" t="s">
         <v>9</v>
@@ -7327,24 +7270,12 @@
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B41" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="D41" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="E41" s="21">
-        <v>15</v>
-      </c>
-      <c r="F41" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G41" s="20" t="s">
-        <v>11</v>
-      </c>
+      <c r="B41" s="20"/>
+      <c r="C41" s="20"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="20"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="20">
@@ -7355,7 +7286,7 @@
         <v>7</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D42" s="20" t="s">
         <v>9</v>
@@ -7379,7 +7310,7 @@
         <v>7</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D43" s="20" t="s">
         <v>9</v>
@@ -7403,7 +7334,7 @@
         <v>7</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D44" s="20" t="s">
         <v>9</v>
@@ -7423,24 +7354,12 @@
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="B45" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="D45" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="E45" s="21">
-        <v>15.5</v>
-      </c>
-      <c r="F45" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G45" s="20" t="s">
-        <v>11</v>
-      </c>
+      <c r="B45" s="20"/>
+      <c r="C45" s="20"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="21"/>
+      <c r="G45" s="20"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="20">
@@ -7451,7 +7370,7 @@
         <v>7</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D46" s="20" t="s">
         <v>9</v>
@@ -7475,7 +7394,7 @@
         <v>7</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D47" s="20" t="s">
         <v>9</v>
@@ -7499,7 +7418,7 @@
         <v>7</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D48" s="20" t="s">
         <v>9</v>
@@ -7523,7 +7442,7 @@
         <v>7</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D49" s="20" t="s">
         <v>9</v>
@@ -7543,24 +7462,12 @@
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="B50" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="D50" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="E50" s="21">
-        <v>3.7</v>
-      </c>
-      <c r="F50" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G50" s="20" t="s">
-        <v>11</v>
-      </c>
+      <c r="B50" s="20"/>
+      <c r="C50" s="20"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="21"/>
+      <c r="F50" s="21"/>
+      <c r="G50" s="20"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="20">
@@ -7571,7 +7478,7 @@
         <v>7</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D51" s="20" t="s">
         <v>9</v>
@@ -7595,7 +7502,7 @@
         <v>7</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D52" s="20" t="s">
         <v>9</v>
@@ -7619,7 +7526,7 @@
         <v>7</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D53" s="20" t="s">
         <v>9</v>
@@ -7643,7 +7550,7 @@
         <v>7</v>
       </c>
       <c r="C54" s="20" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D54" s="20" t="s">
         <v>9</v>
@@ -7667,7 +7574,7 @@
         <v>7</v>
       </c>
       <c r="C55" s="20" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D55" s="20" t="s">
         <v>9</v>
@@ -7687,24 +7594,12 @@
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="B56" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="D56" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="E56" s="21">
-        <v>6</v>
-      </c>
-      <c r="F56" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G56" s="20" t="s">
-        <v>11</v>
-      </c>
+      <c r="B56" s="20"/>
+      <c r="C56" s="20"/>
+      <c r="D56" s="20"/>
+      <c r="E56" s="21"/>
+      <c r="F56" s="21"/>
+      <c r="G56" s="20"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" s="20">
@@ -7715,7 +7610,7 @@
         <v>7</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D57" s="20" t="s">
         <v>9</v>
@@ -7735,24 +7630,12 @@
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="B58" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="D58" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="E58" s="21">
-        <v>7</v>
-      </c>
-      <c r="F58" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G58" s="20" t="s">
-        <v>11</v>
-      </c>
+      <c r="B58" s="20"/>
+      <c r="C58" s="20"/>
+      <c r="D58" s="20"/>
+      <c r="E58" s="21"/>
+      <c r="F58" s="21"/>
+      <c r="G58" s="20"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" s="20">
@@ -7763,7 +7646,7 @@
         <v>7</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D59" s="20" t="s">
         <v>9</v>
@@ -7787,7 +7670,7 @@
         <v>7</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D60" s="20" t="s">
         <v>9</v>
@@ -8277,15 +8160,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="27" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="23" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="B2" s="24">
         <v>1200</v>
@@ -8293,7 +8176,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="B3">
         <v>1000</v>
@@ -8301,7 +8184,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="23" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="B4" s="24">
         <v>800</v>
@@ -8309,7 +8192,7 @@
     </row>
     <row r="5" spans="1:2" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="B5" s="24">
         <v>600</v>
@@ -8317,7 +8200,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="25" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="B6" s="26">
         <v>350</v>
@@ -8325,34 +8208,34 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="29" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="17" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="17" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="17" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -8372,55 +8255,55 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
+        <v>470</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>471</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>472</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>473</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>474</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>475</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>476</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>477</v>
+      </c>
+      <c r="I1" s="14" t="s">
         <v>478</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="J1" s="14" t="s">
         <v>479</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="K1" s="14" t="s">
         <v>480</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="L1" s="14" t="s">
         <v>481</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="M1" s="14" t="s">
         <v>482</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="N1" s="14" t="s">
         <v>483</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="O1" s="14" t="s">
         <v>484</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="P1" s="14" t="s">
         <v>485</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="Q1" s="14" t="s">
         <v>486</v>
-      </c>
-      <c r="J1" s="14" t="s">
-        <v>487</v>
-      </c>
-      <c r="K1" s="14" t="s">
-        <v>488</v>
-      </c>
-      <c r="L1" s="14" t="s">
-        <v>489</v>
-      </c>
-      <c r="M1" s="14" t="s">
-        <v>490</v>
-      </c>
-      <c r="N1" s="14" t="s">
-        <v>491</v>
-      </c>
-      <c r="O1" s="14" t="s">
-        <v>492</v>
-      </c>
-      <c r="P1" s="14" t="s">
-        <v>493</v>
-      </c>
-      <c r="Q1" s="14" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
@@ -8428,16 +8311,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F2" s="16">
         <v>57000</v>
@@ -8481,16 +8364,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F3" s="15">
         <v>600</v>
@@ -8534,16 +8417,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F4" s="16">
         <v>4000</v>
@@ -8587,16 +8470,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F5" s="16">
         <v>26000</v>
@@ -8640,16 +8523,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F6" s="16">
         <v>25000</v>
@@ -8693,16 +8576,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F7" s="16">
         <v>60000</v>
@@ -8746,16 +8629,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F8" s="16">
         <v>30000</v>
@@ -8799,16 +8682,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F9" s="16">
         <v>1900</v>
@@ -8852,16 +8735,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F10" s="16">
         <v>21000</v>
@@ -8905,16 +8788,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F11" s="16">
         <v>5000</v>
@@ -8958,16 +8841,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F12" s="16">
         <v>4600</v>
@@ -9011,16 +8894,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F13" s="16">
         <v>17500</v>
@@ -9064,16 +8947,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F14" s="16">
         <v>6900</v>
@@ -9117,16 +9000,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F15" s="16">
         <v>2200</v>
@@ -9170,16 +9053,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F16" s="16">
         <v>5600</v>
@@ -9223,16 +9106,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F17" s="16">
         <v>3100</v>
@@ -9276,16 +9159,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F18" s="16">
         <v>4400</v>
@@ -9329,16 +9212,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F19" s="16">
         <v>1000</v>
@@ -9382,16 +9265,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F20" s="16">
         <v>13700</v>
@@ -9435,16 +9318,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F21" s="16">
         <v>2900</v>
@@ -9488,16 +9371,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F22" s="16">
         <v>13000</v>
@@ -9541,16 +9424,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F23" s="16">
         <v>8000</v>
@@ -9594,16 +9477,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F24" s="16">
         <v>5300</v>
@@ -9647,16 +9530,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F25" s="15">
         <v>800</v>
@@ -9700,16 +9583,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F26" s="16">
         <v>4000</v>
@@ -9753,16 +9636,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F27" s="16">
         <v>1700</v>
@@ -9806,16 +9689,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F28" s="16">
         <v>14500</v>
@@ -9859,16 +9742,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F29" s="16">
         <v>5500</v>
@@ -9912,16 +9795,16 @@
         <v>29</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F30" s="16">
         <v>10000</v>
@@ -9965,16 +9848,16 @@
         <v>30</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F31" s="16">
         <v>7000</v>
@@ -10018,16 +9901,16 @@
         <v>31</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F32" s="16">
         <v>11100</v>
@@ -10071,16 +9954,16 @@
         <v>32</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F33" s="16">
         <v>6000</v>
@@ -10124,16 +10007,16 @@
         <v>33</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F34" s="16">
         <v>42000</v>
@@ -10177,16 +10060,16 @@
         <v>34</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F35" s="16">
         <v>2800</v>
@@ -10230,16 +10113,16 @@
         <v>35</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F36" s="16">
         <v>1500</v>
@@ -10283,16 +10166,16 @@
         <v>36</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F37" s="16">
         <v>4900</v>
@@ -10336,16 +10219,16 @@
         <v>37</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F38" s="16">
         <v>5000</v>
@@ -10378,7 +10261,7 @@
         <v>9900</v>
       </c>
       <c r="P38" s="15" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="Q38" s="16">
         <v>6600</v>
@@ -10389,16 +10272,16 @@
         <v>38</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F39" s="18"/>
       <c r="G39" s="18"/>
@@ -10411,7 +10294,7 @@
       <c r="N39" s="18"/>
       <c r="O39" s="18"/>
       <c r="P39" s="15" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="Q39" s="18"/>
     </row>
@@ -10420,16 +10303,16 @@
         <v>39</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F40" s="16">
         <v>8000</v>
@@ -10473,16 +10356,16 @@
         <v>40</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F41" s="16">
         <v>9500</v>
@@ -10526,16 +10409,16 @@
         <v>41</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="E42" s="15" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F42" s="16">
         <v>3800</v>
@@ -10579,16 +10462,16 @@
         <v>42</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F43" s="16">
         <v>3800</v>
@@ -10632,16 +10515,16 @@
         <v>43</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F44" s="16">
         <v>9200</v>
@@ -10685,16 +10568,16 @@
         <v>44</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F45" s="16">
         <v>1200</v>
@@ -10738,16 +10621,16 @@
         <v>45</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F46" s="16">
         <v>13000</v>
@@ -10791,16 +10674,16 @@
         <v>46</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="D47" s="15" t="s">
         <v>7</v>
       </c>
       <c r="E47" s="15" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F47" s="16">
         <v>9600</v>
@@ -10844,16 +10727,16 @@
         <v>47</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F48" s="16">
         <v>6600</v>
@@ -10897,16 +10780,16 @@
         <v>48</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="E49" s="15" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F49" s="16">
         <v>1000</v>
@@ -10950,16 +10833,16 @@
         <v>49</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F50" s="16">
         <v>2700</v>
@@ -11003,16 +10886,16 @@
         <v>50</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F51" s="16">
         <v>3500</v>
@@ -11056,16 +10939,16 @@
         <v>51</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F52" s="16">
         <v>6000</v>
@@ -11109,16 +10992,16 @@
         <v>52</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F53" s="16">
         <v>8400</v>
@@ -11162,16 +11045,16 @@
         <v>53</v>
       </c>
       <c r="B54" s="15" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F54" s="16">
         <v>5000</v>
@@ -11215,16 +11098,16 @@
         <v>54</v>
       </c>
       <c r="B55" s="15" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="E55" s="15" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F55" s="16">
         <v>8500</v>
@@ -11268,16 +11151,16 @@
         <v>55</v>
       </c>
       <c r="B56" s="15" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E56" s="15" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F56" s="16">
         <v>9600</v>
@@ -11321,16 +11204,16 @@
         <v>56</v>
       </c>
       <c r="B57" s="15" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="E57" s="15" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F57" s="16">
         <v>4900</v>
@@ -11374,16 +11257,16 @@
         <v>57</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="E58" s="15" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F58" s="16">
         <v>8900</v>
@@ -11427,16 +11310,16 @@
         <v>58</v>
       </c>
       <c r="B59" s="15" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="E59" s="15" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F59" s="16">
         <v>12000</v>
@@ -11480,16 +11363,16 @@
         <v>59</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F60" s="16">
         <v>3000</v>
@@ -11533,16 +11416,16 @@
         <v>60</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="E61" s="15" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F61" s="18"/>
       <c r="G61" s="18"/>
@@ -11562,16 +11445,16 @@
         <v>61</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="E62" s="15" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F62" s="16">
         <v>4400</v>
@@ -11615,16 +11498,16 @@
         <v>62</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="E63" s="15" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F63" s="16">
         <v>5000</v>
@@ -11668,16 +11551,16 @@
         <v>63</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="E64" s="15" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="F64" s="16">
         <v>6000</v>
@@ -11721,16 +11604,16 @@
         <v>64</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E65" s="15" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F65" s="18"/>
       <c r="G65" s="18"/>
@@ -11750,16 +11633,16 @@
         <v>65</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="E66" s="15" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="F66" s="16">
         <v>3100</v>
@@ -11803,16 +11686,16 @@
         <v>66</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="E67" s="15" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="F67" s="16">
         <v>15000</v>
@@ -11856,16 +11739,16 @@
         <v>67</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="D68" s="15" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="E68" s="15" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="F68" s="16">
         <v>6300</v>
@@ -11909,16 +11792,16 @@
         <v>68</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="E69" s="15" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="F69" s="16">
         <v>5400</v>
@@ -11962,16 +11845,16 @@
         <v>69</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="C70" s="15" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D70" s="15" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="F70" s="16">
         <v>10000</v>
@@ -12015,16 +11898,16 @@
         <v>70</v>
       </c>
       <c r="B71" s="15" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="F71" s="16">
         <v>4700</v>
@@ -12068,16 +11951,16 @@
         <v>71</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="D72" s="15" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="F72" s="16">
         <v>6300</v>
@@ -12121,16 +12004,16 @@
         <v>72</v>
       </c>
       <c r="B73" s="15" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="C73" s="15" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="D73" s="15" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="E73" s="15" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="F73" s="16">
         <v>5000</v>
@@ -12174,16 +12057,16 @@
         <v>73</v>
       </c>
       <c r="B74" s="15" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="D74" s="15" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="E74" s="15" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="F74" s="16">
         <v>1400</v>
@@ -12227,16 +12110,16 @@
         <v>74</v>
       </c>
       <c r="B75" s="15" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="E75" s="15" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="F75" s="16">
         <v>5000</v>
@@ -12280,16 +12163,16 @@
         <v>75</v>
       </c>
       <c r="B76" s="15" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="C76" s="15" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="D76" s="15" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="E76" s="15" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="F76" s="16">
         <v>7000</v>
@@ -12333,16 +12216,16 @@
         <v>76</v>
       </c>
       <c r="B77" s="15" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D77" s="15" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="E77" s="15" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="F77" s="16">
         <v>5900</v>
@@ -12386,16 +12269,16 @@
         <v>77</v>
       </c>
       <c r="B78" s="15" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="C78" s="15" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="D78" s="15" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="E78" s="15" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="F78" s="16">
         <v>6400</v>
@@ -12439,16 +12322,16 @@
         <v>78</v>
       </c>
       <c r="B79" s="15" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="D79" s="15" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="E79" s="15" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="F79" s="16">
         <v>8000</v>
@@ -12492,16 +12375,16 @@
         <v>79</v>
       </c>
       <c r="B80" s="15" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="D80" s="15" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="E80" s="15" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="F80" s="16">
         <v>5800</v>
@@ -12545,16 +12428,16 @@
         <v>80</v>
       </c>
       <c r="B81" s="15" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="C81" s="15" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="D81" s="15" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="E81" s="15" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="F81" s="16">
         <v>11000</v>
@@ -12598,16 +12481,16 @@
         <v>81</v>
       </c>
       <c r="B82" s="15" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="C82" s="15" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="D82" s="15" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="E82" s="15" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="F82" s="16">
         <v>4900</v>
@@ -12651,16 +12534,16 @@
         <v>82</v>
       </c>
       <c r="B83" s="15" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="D83" s="15" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="E83" s="15" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="F83" s="16">
         <v>5100</v>
@@ -12704,16 +12587,16 @@
         <v>83</v>
       </c>
       <c r="B84" s="15" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="C84" s="15" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="D84" s="15" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="E84" s="15" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="F84" s="16">
         <v>2800</v>
@@ -12757,16 +12640,16 @@
         <v>84</v>
       </c>
       <c r="B85" s="15" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="D85" s="15" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="E85" s="15" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="F85" s="16">
         <v>5900</v>
@@ -12810,16 +12693,16 @@
         <v>85</v>
       </c>
       <c r="B86" s="15" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="C86" s="15" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="D86" s="15" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="E86" s="15" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="F86" s="16">
         <v>5000</v>
@@ -12863,16 +12746,16 @@
         <v>86</v>
       </c>
       <c r="B87" s="15" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="D87" s="15" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="E87" s="15" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="F87" s="16">
         <v>8000</v>
@@ -12916,16 +12799,16 @@
         <v>87</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="C88" s="15" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="D88" s="15" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="E88" s="15" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="F88" s="16">
         <v>2900</v>
@@ -12969,16 +12852,16 @@
         <v>88</v>
       </c>
       <c r="B89" s="15" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="D89" s="15" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E89" s="15" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F89" s="16">
         <v>29000</v>
@@ -13022,52 +12905,52 @@
         <v>89</v>
       </c>
       <c r="B90" s="15" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="C90" s="15" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="D90" s="15" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="E90" s="15" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F90" s="15" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="G90" s="15" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="H90" s="15" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="I90" s="15" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="J90" s="15" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="K90" s="15" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="L90" s="15" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="M90" s="15" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="N90" s="15" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="O90" s="15" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="P90" s="16">
         <v>1600</v>
       </c>
       <c r="Q90" s="15" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.2">
@@ -13075,16 +12958,16 @@
         <v>90</v>
       </c>
       <c r="B91" s="15" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="C91" s="15" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="D91" s="15" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="E91" s="15" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F91" s="16">
         <v>2700</v>
@@ -13128,16 +13011,16 @@
         <v>91</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="C92" s="15" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="D92" s="15" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="E92" s="15" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F92" s="16">
         <v>2900</v>
@@ -13181,16 +13064,16 @@
         <v>92</v>
       </c>
       <c r="B93" s="15" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="D93" s="15" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="E93" s="15" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F93" s="16">
         <v>2700</v>
@@ -13234,16 +13117,16 @@
         <v>93</v>
       </c>
       <c r="B94" s="15" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="D94" s="15" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="E94" s="15" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F94" s="16">
         <v>6000</v>
@@ -13287,16 +13170,16 @@
         <v>94</v>
       </c>
       <c r="B95" s="15" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="C95" s="15" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="D95" s="15" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="E95" s="15" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F95" s="16">
         <v>8800</v>
@@ -13340,16 +13223,16 @@
         <v>95</v>
       </c>
       <c r="B96" s="15" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="D96" s="15" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="E96" s="15" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F96" s="16">
         <v>3500</v>
@@ -13393,16 +13276,16 @@
         <v>96</v>
       </c>
       <c r="B97" s="15" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="C97" s="15" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="D97" s="15" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="E97" s="15" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F97" s="16">
         <v>1500</v>
@@ -13446,16 +13329,16 @@
         <v>97</v>
       </c>
       <c r="B98" s="15" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="C98" s="15" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="D98" s="15" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E98" s="15" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F98" s="16">
         <v>2000</v>
@@ -13499,16 +13382,16 @@
         <v>98</v>
       </c>
       <c r="B99" s="15" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="D99" s="15" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="E99" s="15" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F99" s="16">
         <v>9200</v>
@@ -13552,16 +13435,16 @@
         <v>99</v>
       </c>
       <c r="B100" s="15" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="C100" s="15" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="D100" s="15" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="E100" s="15" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F100" s="16">
         <v>8600</v>
@@ -13605,16 +13488,16 @@
         <v>100</v>
       </c>
       <c r="B101" s="15" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="C101" s="15" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="D101" s="15" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="E101" s="15" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F101" s="16">
         <v>10500</v>
@@ -13658,16 +13541,16 @@
         <v>101</v>
       </c>
       <c r="B102" s="15" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="C102" s="15" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="D102" s="15" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="E102" s="15" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F102" s="16">
         <v>3400</v>
@@ -13711,16 +13594,16 @@
         <v>102</v>
       </c>
       <c r="B103" s="15" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="C103" s="15" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="D103" s="15" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="E103" s="15" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F103" s="16">
         <v>2800</v>
@@ -13764,16 +13647,16 @@
         <v>103</v>
       </c>
       <c r="B104" s="15" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="C104" s="15" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="D104" s="15" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="E104" s="15" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F104" s="15">
         <v>700</v>
@@ -13817,16 +13700,16 @@
         <v>104</v>
       </c>
       <c r="B105" s="15" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="C105" s="15" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="D105" s="15" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="E105" s="15" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F105" s="16">
         <v>9500</v>
@@ -13870,16 +13753,16 @@
         <v>105</v>
       </c>
       <c r="B106" s="15" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="C106" s="15" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="D106" s="15" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="E106" s="15" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F106" s="16">
         <v>6000</v>
@@ -13923,16 +13806,16 @@
         <v>106</v>
       </c>
       <c r="B107" s="15" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="C107" s="15" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="D107" s="15" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="E107" s="15" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F107" s="16">
         <v>8500</v>
@@ -13976,16 +13859,16 @@
         <v>107</v>
       </c>
       <c r="B108" s="15" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="C108" s="15" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="D108" s="15" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="E108" s="15" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F108" s="16">
         <v>7700</v>
@@ -14029,16 +13912,16 @@
         <v>108</v>
       </c>
       <c r="B109" s="15" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="C109" s="15" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="D109" s="15" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="E109" s="15" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F109" s="16">
         <v>2300</v>
@@ -14082,16 +13965,16 @@
         <v>109</v>
       </c>
       <c r="B110" s="15" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="C110" s="15" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="D110" s="15" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="E110" s="15" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F110" s="16">
         <v>12000</v>
@@ -14135,16 +14018,16 @@
         <v>110</v>
       </c>
       <c r="B111" s="15" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="C111" s="15" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="D111" s="15" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="E111" s="15" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F111" s="16">
         <v>2300</v>
@@ -14188,16 +14071,16 @@
         <v>111</v>
       </c>
       <c r="B112" s="15" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D112" s="15" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="E112" s="15" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F112" s="16">
         <v>2000</v>
@@ -14241,16 +14124,16 @@
         <v>112</v>
       </c>
       <c r="B113" s="15" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="C113" s="15" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="D113" s="15" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="E113" s="15" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F113" s="16">
         <v>7000</v>
@@ -14294,16 +14177,16 @@
         <v>113</v>
       </c>
       <c r="B114" s="15" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="C114" s="15" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="D114" s="15" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="E114" s="15" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F114" s="16">
         <v>1500</v>
@@ -14347,16 +14230,16 @@
         <v>114</v>
       </c>
       <c r="B115" s="15" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="C115" s="15" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="D115" s="15" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="E115" s="15" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F115" s="16">
         <v>1500</v>
@@ -14400,16 +14283,16 @@
         <v>115</v>
       </c>
       <c r="B116" s="15" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="C116" s="15" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="D116" s="15" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="E116" s="15" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F116" s="16">
         <v>1100</v>
@@ -14453,16 +14336,16 @@
         <v>116</v>
       </c>
       <c r="B117" s="15" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="C117" s="15" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="D117" s="15" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="E117" s="15" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F117" s="16">
         <v>3000</v>
@@ -14506,16 +14389,16 @@
         <v>117</v>
       </c>
       <c r="B118" s="15" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="D118" s="15" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="E118" s="15" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F118" s="16">
         <v>1500</v>
@@ -14559,16 +14442,16 @@
         <v>118</v>
       </c>
       <c r="B119" s="15" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="C119" s="15" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="D119" s="15" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="E119" s="15" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F119" s="16">
         <v>6900</v>
@@ -14612,16 +14495,16 @@
         <v>119</v>
       </c>
       <c r="B120" s="15" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="C120" s="15" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="D120" s="15" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="E120" s="15" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F120" s="16">
         <v>9000</v>
@@ -14665,16 +14548,16 @@
         <v>120</v>
       </c>
       <c r="B121" s="15" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="C121" s="15" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="D121" s="15" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E121" s="15" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F121" s="16">
         <v>5200</v>
@@ -14718,16 +14601,16 @@
         <v>121</v>
       </c>
       <c r="B122" s="15" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="C122" s="15" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="D122" s="15" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="E122" s="15" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F122" s="16">
         <v>4300</v>
@@ -14771,16 +14654,16 @@
         <v>122</v>
       </c>
       <c r="B123" s="15" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="C123" s="15" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="D123" s="15" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="E123" s="15" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F123" s="16">
         <v>1800</v>
@@ -14824,16 +14707,16 @@
         <v>123</v>
       </c>
       <c r="B124" s="15" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="C124" s="15" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="D124" s="15" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="E124" s="15" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F124" s="16">
         <v>14000</v>
@@ -14877,16 +14760,16 @@
         <v>124</v>
       </c>
       <c r="B125" s="15" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="C125" s="15" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="D125" s="15" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="E125" s="15" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F125" s="16">
         <v>8600</v>
@@ -14930,16 +14813,16 @@
         <v>125</v>
       </c>
       <c r="B126" s="15" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="C126" s="15" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="D126" s="15" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E126" s="15" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F126" s="16">
         <v>8000</v>
@@ -14983,16 +14866,16 @@
         <v>126</v>
       </c>
       <c r="B127" s="15" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="C127" s="15" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="D127" s="15" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="E127" s="15" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F127" s="16">
         <v>1500</v>
@@ -15036,16 +14919,16 @@
         <v>127</v>
       </c>
       <c r="B128" s="15" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="C128" s="15" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="D128" s="15" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="E128" s="15" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F128" s="16">
         <v>3900</v>
@@ -15089,16 +14972,16 @@
         <v>128</v>
       </c>
       <c r="B129" s="15" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="C129" s="15" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="D129" s="15" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="E129" s="15" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F129" s="16">
         <v>2400</v>
@@ -15142,16 +15025,16 @@
         <v>129</v>
       </c>
       <c r="B130" s="15" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="C130" s="15" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="D130" s="15" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="E130" s="15" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F130" s="16">
         <v>10000</v>
@@ -15195,16 +15078,16 @@
         <v>130</v>
       </c>
       <c r="B131" s="15" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="C131" s="15" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="D131" s="15" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="E131" s="15" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F131" s="16">
         <v>10500</v>
@@ -15248,16 +15131,16 @@
         <v>131</v>
       </c>
       <c r="B132" s="15" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="C132" s="15" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="D132" s="15" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="E132" s="15" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F132" s="16">
         <v>1200</v>
@@ -15301,16 +15184,16 @@
         <v>132</v>
       </c>
       <c r="B133" s="15" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="C133" s="15" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="D133" s="15" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="E133" s="15" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F133" s="16">
         <v>7800</v>
@@ -15354,16 +15237,16 @@
         <v>133</v>
       </c>
       <c r="B134" s="15" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="C134" s="15" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="D134" s="15" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="E134" s="15" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F134" s="16">
         <v>5000</v>
@@ -15407,16 +15290,16 @@
         <v>134</v>
       </c>
       <c r="B135" s="15" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="C135" s="15" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="D135" s="15" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="E135" s="15" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F135" s="16">
         <v>5200</v>
@@ -15460,16 +15343,16 @@
         <v>135</v>
       </c>
       <c r="B136" s="15" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="C136" s="15" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="D136" s="15" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="E136" s="15" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F136" s="16">
         <v>2700</v>
@@ -15513,16 +15396,16 @@
         <v>136</v>
       </c>
       <c r="B137" s="15" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="C137" s="15" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="D137" s="15" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="E137" s="15" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F137" s="16">
         <v>2500</v>
@@ -15566,16 +15449,16 @@
         <v>137</v>
       </c>
       <c r="B138" s="15" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="C138" s="15" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="D138" s="15" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="E138" s="15" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F138" s="16">
         <v>2100</v>
@@ -15619,16 +15502,16 @@
         <v>138</v>
       </c>
       <c r="B139" s="15" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="C139" s="15" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="D139" s="15" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="E139" s="15" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F139" s="16">
         <v>7700</v>
@@ -15672,16 +15555,16 @@
         <v>139</v>
       </c>
       <c r="B140" s="15" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="C140" s="15" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="D140" s="15" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="E140" s="15" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F140" s="16">
         <v>2400</v>
@@ -15725,16 +15608,16 @@
         <v>140</v>
       </c>
       <c r="B141" s="15" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="C141" s="15" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="D141" s="15" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="E141" s="15" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F141" s="16">
         <v>3400</v>
@@ -15778,16 +15661,16 @@
         <v>141</v>
       </c>
       <c r="B142" s="15" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="C142" s="15" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="D142" s="15" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="E142" s="15" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F142" s="16">
         <v>2800</v>
@@ -15831,16 +15714,16 @@
         <v>142</v>
       </c>
       <c r="B143" s="15" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="C143" s="15" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="D143" s="15" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="E143" s="15" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F143" s="16">
         <v>6900</v>
@@ -15884,16 +15767,16 @@
         <v>143</v>
       </c>
       <c r="B144" s="15" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
       <c r="C144" s="15" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="D144" s="15" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="E144" s="15" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F144" s="16">
         <v>3000</v>
@@ -15937,16 +15820,16 @@
         <v>144</v>
       </c>
       <c r="B145" s="15" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="C145" s="15" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="D145" s="15" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="E145" s="15" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F145" s="16">
         <v>2300</v>
@@ -15990,16 +15873,16 @@
         <v>145</v>
       </c>
       <c r="B146" s="15" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="C146" s="15" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="D146" s="15" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="E146" s="15" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F146" s="16">
         <v>4400</v>
@@ -16043,16 +15926,16 @@
         <v>146</v>
       </c>
       <c r="B147" s="15" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="C147" s="15" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="D147" s="15" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="E147" s="15" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F147" s="16">
         <v>27500</v>
@@ -16096,16 +15979,16 @@
         <v>147</v>
       </c>
       <c r="B148" s="15" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="C148" s="15" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="D148" s="15" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="E148" s="15" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F148" s="15">
         <v>100</v>
@@ -16149,16 +16032,16 @@
         <v>148</v>
       </c>
       <c r="B149" s="15" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="C149" s="15" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D149" s="15" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="E149" s="15" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F149" s="16">
         <v>4800</v>
@@ -16202,16 +16085,16 @@
         <v>149</v>
       </c>
       <c r="B150" s="15" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="C150" s="15" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="D150" s="15" t="s">
-        <v>680</v>
+        <v>672</v>
       </c>
       <c r="E150" s="15" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F150" s="16">
         <v>4300</v>
@@ -16255,16 +16138,16 @@
         <v>150</v>
       </c>
       <c r="B151" s="15" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="C151" s="15" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="D151" s="15" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="E151" s="15" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F151" s="16">
         <v>6000</v>
@@ -16308,16 +16191,16 @@
         <v>151</v>
       </c>
       <c r="B152" s="15" t="s">
-        <v>682</v>
+        <v>674</v>
       </c>
       <c r="C152" s="15" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="D152" s="15" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="E152" s="15" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F152" s="16">
         <v>1500</v>
@@ -16361,52 +16244,52 @@
         <v>152</v>
       </c>
       <c r="B153" s="15" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="C153" s="15" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="D153" s="15" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="E153" s="15" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F153" s="15" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="G153" s="15" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="H153" s="15" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="I153" s="15" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="J153" s="15" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="K153" s="15" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="L153" s="15" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="M153" s="15" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="N153" s="15" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="O153" s="15" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="P153" s="15">
         <v>300</v>
       </c>
       <c r="Q153" s="15" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.2">
@@ -16414,16 +16297,16 @@
         <v>153</v>
       </c>
       <c r="B154" s="15" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="C154" s="15" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="D154" s="15" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="E154" s="15" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F154" s="16">
         <v>4000</v>
@@ -16467,16 +16350,16 @@
         <v>154</v>
       </c>
       <c r="B155" s="15" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="C155" s="15" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="D155" s="15" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="E155" s="15" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F155" s="16">
         <v>7000</v>
@@ -16520,16 +16403,16 @@
         <v>155</v>
       </c>
       <c r="B156" s="15" t="s">
-        <v>688</v>
+        <v>680</v>
       </c>
       <c r="C156" s="15" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="D156" s="15" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="E156" s="15" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F156" s="16">
         <v>10700</v>
@@ -16573,16 +16456,16 @@
         <v>156</v>
       </c>
       <c r="B157" s="15" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="C157" s="15" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="D157" s="15" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="E157" s="15" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F157" s="16">
         <v>31000</v>
@@ -16626,16 +16509,16 @@
         <v>157</v>
       </c>
       <c r="B158" s="15" t="s">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="C158" s="15" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="D158" s="15" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="E158" s="15" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F158" s="16">
         <v>4500</v>
@@ -16679,16 +16562,16 @@
         <v>158</v>
       </c>
       <c r="B159" s="15" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="C159" s="15" t="s">
-        <v>693</v>
+        <v>685</v>
       </c>
       <c r="D159" s="15" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E159" s="15" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F159" s="16">
         <v>2900</v>
@@ -16732,16 +16615,16 @@
         <v>159</v>
       </c>
       <c r="B160" s="15" t="s">
-        <v>694</v>
+        <v>686</v>
       </c>
       <c r="C160" s="15" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="D160" s="15" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="E160" s="15" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F160" s="16">
         <v>3300</v>
@@ -16785,16 +16668,16 @@
         <v>160</v>
       </c>
       <c r="B161" s="15" t="s">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="C161" s="15" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="D161" s="15" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="E161" s="15" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F161" s="16">
         <v>6600</v>
@@ -16838,16 +16721,16 @@
         <v>161</v>
       </c>
       <c r="B162" s="15" t="s">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="C162" s="15" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="D162" s="15" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="E162" s="15" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F162" s="16">
         <v>11500</v>
@@ -16891,16 +16774,16 @@
         <v>162</v>
       </c>
       <c r="B163" s="15" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="C163" s="15" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="D163" s="15" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="E163" s="15" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F163" s="16">
         <v>4000</v>
@@ -16944,16 +16827,16 @@
         <v>163</v>
       </c>
       <c r="B164" s="15" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="C164" s="15" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="D164" s="15" t="s">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="E164" s="15" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F164" s="16">
         <v>1000</v>
@@ -16997,16 +16880,16 @@
         <v>164</v>
       </c>
       <c r="B165" s="15" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="C165" s="15" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="D165" s="15" t="s">
-        <v>702</v>
+        <v>694</v>
       </c>
       <c r="E165" s="15" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F165" s="16">
         <v>8400</v>
@@ -17050,16 +16933,16 @@
         <v>165</v>
       </c>
       <c r="B166" s="15" t="s">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="C166" s="15" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="D166" s="15" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="E166" s="15" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F166" s="16">
         <v>9900</v>
@@ -17103,16 +16986,16 @@
         <v>166</v>
       </c>
       <c r="B167" s="15" t="s">
-        <v>704</v>
+        <v>696</v>
       </c>
       <c r="C167" s="15" t="s">
-        <v>705</v>
+        <v>697</v>
       </c>
       <c r="D167" s="15" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="E167" s="15" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F167" s="16">
         <v>5500</v>
@@ -17156,16 +17039,16 @@
         <v>167</v>
       </c>
       <c r="B168" s="15" t="s">
-        <v>706</v>
+        <v>698</v>
       </c>
       <c r="C168" s="15" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="D168" s="15" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="E168" s="15" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F168" s="16">
         <v>3000</v>
@@ -17209,16 +17092,16 @@
         <v>168</v>
       </c>
       <c r="B169" s="15" t="s">
-        <v>707</v>
+        <v>699</v>
       </c>
       <c r="C169" s="15" t="s">
-        <v>708</v>
+        <v>700</v>
       </c>
       <c r="D169" s="15" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="E169" s="15" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="F169" s="16">
         <v>9200</v>
@@ -17262,16 +17145,16 @@
         <v>169</v>
       </c>
       <c r="B170" s="15" t="s">
-        <v>709</v>
+        <v>701</v>
       </c>
       <c r="C170" s="15" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="D170" s="15" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="E170" s="15" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="F170" s="16">
         <v>2100</v>
@@ -17315,16 +17198,16 @@
         <v>170</v>
       </c>
       <c r="B171" s="15" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C171" s="15" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="D171" s="15" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="E171" s="15" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="F171" s="16">
         <v>2100</v>
@@ -17368,16 +17251,16 @@
         <v>171</v>
       </c>
       <c r="B172" s="15" t="s">
-        <v>711</v>
+        <v>703</v>
       </c>
       <c r="C172" s="15" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="D172" s="15" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E172" s="15" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="F172" s="16">
         <v>2300</v>
@@ -17421,16 +17304,16 @@
         <v>172</v>
       </c>
       <c r="B173" s="15" t="s">
-        <v>712</v>
+        <v>704</v>
       </c>
       <c r="C173" s="15" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="D173" s="15" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="E173" s="15" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="F173" s="16">
         <v>6800</v>
@@ -17474,16 +17357,16 @@
         <v>173</v>
       </c>
       <c r="B174" s="15" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="C174" s="15" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D174" s="15" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="E174" s="15" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="F174" s="16">
         <v>2100</v>
@@ -17527,16 +17410,16 @@
         <v>174</v>
       </c>
       <c r="B175" s="15" t="s">
-        <v>714</v>
+        <v>706</v>
       </c>
       <c r="C175" s="15" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="D175" s="15" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="E175" s="15" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="F175" s="16">
         <v>5600</v>
@@ -17580,16 +17463,16 @@
         <v>175</v>
       </c>
       <c r="B176" s="15" t="s">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="C176" s="15" t="s">
-        <v>716</v>
+        <v>708</v>
       </c>
       <c r="D176" s="15" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="E176" s="15" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="F176" s="16">
         <v>6200</v>
@@ -17633,16 +17516,16 @@
         <v>176</v>
       </c>
       <c r="B177" s="15" t="s">
-        <v>717</v>
+        <v>709</v>
       </c>
       <c r="C177" s="15" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="D177" s="15" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="E177" s="15" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="F177" s="16">
         <v>6600</v>
@@ -17686,16 +17569,16 @@
         <v>177</v>
       </c>
       <c r="B178" s="15" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
       <c r="C178" s="15" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D178" s="15" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="E178" s="15" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="F178" s="15">
         <v>500</v>
@@ -17739,16 +17622,16 @@
         <v>178</v>
       </c>
       <c r="B179" s="15" t="s">
-        <v>719</v>
+        <v>711</v>
       </c>
       <c r="C179" s="15" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="D179" s="15" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="E179" s="15" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="F179" s="16">
         <v>2800</v>
@@ -17792,16 +17675,16 @@
         <v>179</v>
       </c>
       <c r="B180" s="15" t="s">
-        <v>720</v>
+        <v>712</v>
       </c>
       <c r="C180" s="15" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="D180" s="15" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="E180" s="15" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="F180" s="16">
         <v>2800</v>
@@ -17825,7 +17708,7 @@
         <v>500</v>
       </c>
       <c r="M180" s="15" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="N180" s="15">
         <v>400</v>
@@ -17845,16 +17728,16 @@
         <v>180</v>
       </c>
       <c r="B181" s="15" t="s">
-        <v>721</v>
+        <v>713</v>
       </c>
       <c r="C181" s="15" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="D181" s="15" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="E181" s="15" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="F181" s="16">
         <v>1000</v>
@@ -17898,16 +17781,16 @@
         <v>181</v>
       </c>
       <c r="B182" s="15" t="s">
-        <v>722</v>
+        <v>714</v>
       </c>
       <c r="C182" s="15" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="D182" s="15" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="E182" s="15" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="F182" s="16">
         <v>3300</v>
@@ -17951,16 +17834,16 @@
         <v>182</v>
       </c>
       <c r="B183" s="15" t="s">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="C183" s="15" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="D183" s="15" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E183" s="15" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="F183" s="16">
         <v>9300</v>
@@ -18004,16 +17887,16 @@
         <v>183</v>
       </c>
       <c r="B184" s="15" t="s">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="C184" s="15" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="D184" s="15" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E184" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F184" s="18"/>
       <c r="G184" s="18"/>
@@ -18026,7 +17909,7 @@
       <c r="N184" s="18"/>
       <c r="O184" s="18"/>
       <c r="P184" s="15" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="Q184" s="18"/>
     </row>
@@ -18035,16 +17918,16 @@
         <v>184</v>
       </c>
       <c r="B185" s="15" t="s">
-        <v>725</v>
+        <v>717</v>
       </c>
       <c r="C185" s="15" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="D185" s="15" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="E185" s="15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F185" s="18"/>
       <c r="G185" s="18"/>
@@ -18057,7 +17940,7 @@
       <c r="N185" s="18"/>
       <c r="O185" s="18"/>
       <c r="P185" s="15" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="Q185" s="18"/>
     </row>
@@ -18066,16 +17949,16 @@
         <v>185</v>
       </c>
       <c r="B186" s="15" t="s">
-        <v>726</v>
+        <v>718</v>
       </c>
       <c r="C186" s="15" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="D186" s="15" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E186" s="15" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F186" s="18"/>
       <c r="G186" s="18"/>
@@ -18088,7 +17971,7 @@
       <c r="N186" s="18"/>
       <c r="O186" s="18"/>
       <c r="P186" s="15" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="Q186" s="18"/>
     </row>

--- a/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
+++ b/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dee/Desktop/GitHub- Repo/tms/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{801888A7-6AD2-AD41-95CA-508518243C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCFA319A-C032-4F47-BB29-17015EAA7216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17540" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DB capacity" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="DB Target" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vehicle Database'!$A$1:$G$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vehicle Database'!$A$1:$H$60</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1853" uniqueCount="719">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1953" uniqueCount="731">
   <si>
     <t>S. N.</t>
   </si>
@@ -2196,6 +2196,42 @@
   </si>
   <si>
     <t>LKFLVD000398</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>UP32AN3938</t>
+  </si>
+  <si>
+    <t>UP32AN6958</t>
+  </si>
+  <si>
+    <t>UP41AT4026</t>
+  </si>
+  <si>
+    <t>UP41T8559</t>
+  </si>
+  <si>
+    <t>UP32BN4925</t>
+  </si>
+  <si>
+    <t>UP32HN2137</t>
+  </si>
+  <si>
+    <t>UP41T6902</t>
+  </si>
+  <si>
+    <t>UP41T5263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle Breakdown </t>
+  </si>
+  <si>
+    <t>Driver not avaialble</t>
+  </si>
+  <si>
+    <t>operational</t>
   </si>
 </sst>
 </file>
@@ -2316,7 +2352,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -2543,6 +2579,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2550,7 +2599,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2615,6 +2664,13 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma 4 4 2 2 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
@@ -6331,7 +6387,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:H111"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
@@ -6341,9 +6397,10 @@
     <col min="5" max="5" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -6365,8 +6422,11 @@
       <c r="G1" s="19" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H1" s="19" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="20">
         <v>1</v>
       </c>
@@ -6388,32 +6448,65 @@
       <c r="G2" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H2" s="32" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="20">
         <f>A2+1</f>
         <v>2</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="20"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B3" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>720</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="21">
+        <v>6</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="32" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="20">
         <f t="shared" ref="A4:A60" si="0">A3+1</f>
         <v>3</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="20"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B4" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>721</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="21">
+        <v>6.5</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="32" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="20">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -6436,8 +6529,11 @@
       <c r="G5" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H5" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="20">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -6460,8 +6556,11 @@
       <c r="G6" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H6" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="20">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -6484,8 +6583,11 @@
       <c r="G7" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H7" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="20">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -6508,8 +6610,11 @@
       <c r="G8" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H8" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="20">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -6532,8 +6637,11 @@
       <c r="G9" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H9" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="20">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -6556,8 +6664,11 @@
       <c r="G10" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H10" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="20">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -6580,8 +6691,11 @@
       <c r="G11" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H11" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="20">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -6604,8 +6718,11 @@
       <c r="G12" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H12" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="20">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -6628,8 +6745,11 @@
       <c r="G13" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H13" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="20">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -6652,8 +6772,11 @@
       <c r="G14" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H14" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="20">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -6676,8 +6799,11 @@
       <c r="G15" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H15" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="20">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -6700,8 +6826,11 @@
       <c r="G16" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H16" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="20">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -6724,8 +6853,11 @@
       <c r="G17" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H17" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="20">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -6748,8 +6880,11 @@
       <c r="G18" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H18" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="20">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -6772,8 +6907,11 @@
       <c r="G19" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H19" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="20">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -6796,8 +6934,11 @@
       <c r="G20" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H20" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="20">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -6820,8 +6961,11 @@
       <c r="G21" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H21" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="20">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -6844,8 +6988,11 @@
       <c r="G22" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H22" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="20">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -6868,8 +7015,11 @@
       <c r="G23" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H23" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="20">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -6892,8 +7042,11 @@
       <c r="G24" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H24" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="20">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -6916,8 +7069,11 @@
       <c r="G25" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H25" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="20">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -6940,8 +7096,11 @@
       <c r="G26" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H26" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="20">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -6964,8 +7123,11 @@
       <c r="G27" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H27" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="20">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -6988,8 +7150,11 @@
       <c r="G28" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H28" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="20">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -7012,8 +7177,11 @@
       <c r="G29" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H29" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="20">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -7036,8 +7204,11 @@
       <c r="G30" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H30" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="20">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -7060,8 +7231,11 @@
       <c r="G31" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H31" s="32" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="20">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -7084,8 +7258,11 @@
       <c r="G32" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H32" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="20">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -7108,20 +7285,38 @@
       <c r="G33" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H33" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="20">
         <f>A33+1</f>
         <v>33</v>
       </c>
-      <c r="B34" s="20"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21"/>
-      <c r="G34" s="20"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B34" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>722</v>
+      </c>
+      <c r="D34" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" s="21">
+        <v>9</v>
+      </c>
+      <c r="F34" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H34" s="32" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="20">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -7144,8 +7339,11 @@
       <c r="G35" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H35" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="20">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -7168,8 +7366,11 @@
       <c r="G36" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H36" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="20">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -7192,8 +7393,11 @@
       <c r="G37" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H37" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="20">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -7216,8 +7420,11 @@
       <c r="G38" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H38" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="20">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -7240,8 +7447,11 @@
       <c r="G39" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H39" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="20">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -7264,20 +7474,38 @@
       <c r="G40" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H40" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="20">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B41" s="20"/>
-      <c r="C41" s="20"/>
-      <c r="D41" s="20"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="21"/>
-      <c r="G41" s="20"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B41" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>723</v>
+      </c>
+      <c r="D41" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" s="21">
+        <v>15</v>
+      </c>
+      <c r="F41" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G41" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H41" s="32" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="20">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -7300,8 +7528,11 @@
       <c r="G42" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H42" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="20">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -7324,8 +7555,11 @@
       <c r="G43" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H43" s="32" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="20">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -7348,20 +7582,38 @@
       <c r="G44" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H44" s="32" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="20">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="B45" s="20"/>
-      <c r="C45" s="20"/>
-      <c r="D45" s="20"/>
-      <c r="E45" s="21"/>
-      <c r="F45" s="21"/>
-      <c r="G45" s="20"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B45" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="20" t="s">
+        <v>724</v>
+      </c>
+      <c r="D45" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E45" s="21">
+        <v>15.5</v>
+      </c>
+      <c r="F45" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H45" s="32" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="20">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -7384,8 +7636,11 @@
       <c r="G46" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H46" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="20">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -7408,8 +7663,11 @@
       <c r="G47" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H47" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="20">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -7432,8 +7690,11 @@
       <c r="G48" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H48" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="20">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -7456,20 +7717,38 @@
       <c r="G49" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H49" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="20">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="B50" s="20"/>
-      <c r="C50" s="20"/>
-      <c r="D50" s="20"/>
-      <c r="E50" s="21"/>
-      <c r="F50" s="21"/>
-      <c r="G50" s="20"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B50" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="20" t="s">
+        <v>725</v>
+      </c>
+      <c r="D50" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50" s="21">
+        <v>3.7</v>
+      </c>
+      <c r="F50" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G50" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H50" s="32" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="20">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -7492,8 +7771,11 @@
       <c r="G51" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H51" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="20">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -7516,8 +7798,11 @@
       <c r="G52" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H52" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="20">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -7540,8 +7825,11 @@
       <c r="G53" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H53" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="20">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -7564,8 +7852,11 @@
       <c r="G54" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H54" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="20">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -7588,20 +7879,38 @@
       <c r="G55" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H55" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="20">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="B56" s="20"/>
-      <c r="C56" s="20"/>
-      <c r="D56" s="20"/>
-      <c r="E56" s="21"/>
-      <c r="F56" s="21"/>
-      <c r="G56" s="20"/>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B56" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="20" t="s">
+        <v>726</v>
+      </c>
+      <c r="D56" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E56" s="21">
+        <v>6</v>
+      </c>
+      <c r="F56" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G56" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H56" s="32" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="20">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -7624,20 +7933,38 @@
       <c r="G57" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H57" s="32" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="20">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="B58" s="20"/>
-      <c r="C58" s="20"/>
-      <c r="D58" s="20"/>
-      <c r="E58" s="21"/>
-      <c r="F58" s="21"/>
-      <c r="G58" s="20"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B58" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="20" t="s">
+        <v>727</v>
+      </c>
+      <c r="D58" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E58" s="21">
+        <v>7</v>
+      </c>
+      <c r="F58" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G58" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H58" s="32" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="20">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -7660,8 +7987,11 @@
       <c r="G59" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H59" s="32" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="20">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -7684,17 +8014,20 @@
       <c r="G60" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A61" s="21"/>
-      <c r="B61" s="20"/>
-      <c r="C61" s="20"/>
-      <c r="D61" s="20"/>
-      <c r="E61" s="21"/>
-      <c r="F61" s="21"/>
-      <c r="G61" s="20"/>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H60" s="32" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A61" s="30"/>
+      <c r="B61" s="31"/>
+      <c r="C61" s="31"/>
+      <c r="D61" s="31"/>
+      <c r="E61" s="30"/>
+      <c r="F61" s="30"/>
+      <c r="G61" s="31"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="21"/>
       <c r="B62" s="20"/>
       <c r="C62" s="20"/>
@@ -7703,7 +8036,7 @@
       <c r="F62" s="21"/>
       <c r="G62" s="20"/>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="21"/>
       <c r="B63" s="20"/>
       <c r="C63" s="20"/>
@@ -7712,7 +8045,7 @@
       <c r="F63" s="21"/>
       <c r="G63" s="20"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="21"/>
       <c r="B64" s="20"/>
       <c r="C64" s="20"/>

--- a/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
+++ b/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dee/Desktop/GitHub- Repo/tms/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dee/Downloads/tms/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCFA319A-C032-4F47-BB29-17015EAA7216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5721B61C-B435-3B40-B7C4-A0748F703A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17540" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8026,6 +8026,7 @@
       <c r="E61" s="30"/>
       <c r="F61" s="30"/>
       <c r="G61" s="31"/>
+      <c r="H61" s="32"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="21"/>
@@ -8035,6 +8036,7 @@
       <c r="E62" s="21"/>
       <c r="F62" s="21"/>
       <c r="G62" s="20"/>
+      <c r="H62" s="32"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="21"/>
@@ -8044,6 +8046,7 @@
       <c r="E63" s="21"/>
       <c r="F63" s="21"/>
       <c r="G63" s="20"/>
+      <c r="H63" s="32"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="21"/>
@@ -8053,8 +8056,9 @@
       <c r="E64" s="21"/>
       <c r="F64" s="21"/>
       <c r="G64" s="20"/>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H64" s="32"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="21"/>
       <c r="B65" s="20"/>
       <c r="C65" s="20"/>
@@ -8062,8 +8066,9 @@
       <c r="E65" s="21"/>
       <c r="F65" s="21"/>
       <c r="G65" s="20"/>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H65" s="32"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="21"/>
       <c r="B66" s="20"/>
       <c r="C66" s="20"/>
@@ -8071,8 +8076,9 @@
       <c r="E66" s="21"/>
       <c r="F66" s="21"/>
       <c r="G66" s="20"/>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H66" s="32"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="21"/>
       <c r="B67" s="20"/>
       <c r="C67" s="20"/>
@@ -8080,8 +8086,9 @@
       <c r="E67" s="21"/>
       <c r="F67" s="21"/>
       <c r="G67" s="20"/>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H67" s="32"/>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="21"/>
       <c r="B68" s="20"/>
       <c r="C68" s="20"/>
@@ -8089,8 +8096,9 @@
       <c r="E68" s="21"/>
       <c r="F68" s="21"/>
       <c r="G68" s="20"/>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H68" s="32"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="21"/>
       <c r="B69" s="20"/>
       <c r="C69" s="20"/>
@@ -8098,8 +8106,9 @@
       <c r="E69" s="21"/>
       <c r="F69" s="21"/>
       <c r="G69" s="20"/>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H69" s="32"/>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="21"/>
       <c r="B70" s="20"/>
       <c r="C70" s="20"/>
@@ -8107,8 +8116,9 @@
       <c r="E70" s="21"/>
       <c r="F70" s="21"/>
       <c r="G70" s="20"/>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H70" s="32"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="21"/>
       <c r="B71" s="20"/>
       <c r="C71" s="20"/>
@@ -8116,8 +8126,9 @@
       <c r="E71" s="21"/>
       <c r="F71" s="21"/>
       <c r="G71" s="20"/>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H71" s="32"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="21"/>
       <c r="B72" s="20"/>
       <c r="C72" s="20"/>
@@ -8125,8 +8136,9 @@
       <c r="E72" s="21"/>
       <c r="F72" s="21"/>
       <c r="G72" s="20"/>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H72" s="32"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="21"/>
       <c r="B73" s="20"/>
       <c r="C73" s="20"/>
@@ -8134,8 +8146,9 @@
       <c r="E73" s="21"/>
       <c r="F73" s="21"/>
       <c r="G73" s="20"/>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H73" s="32"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="21"/>
       <c r="B74" s="20"/>
       <c r="C74" s="20"/>
@@ -8143,8 +8156,9 @@
       <c r="E74" s="21"/>
       <c r="F74" s="21"/>
       <c r="G74" s="20"/>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H74" s="32"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="21"/>
       <c r="B75" s="20"/>
       <c r="C75" s="20"/>
@@ -8152,8 +8166,9 @@
       <c r="E75" s="21"/>
       <c r="F75" s="21"/>
       <c r="G75" s="20"/>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H75" s="32"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="21"/>
       <c r="B76" s="20"/>
       <c r="C76" s="20"/>
@@ -8161,8 +8176,9 @@
       <c r="E76" s="21"/>
       <c r="F76" s="21"/>
       <c r="G76" s="20"/>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H76" s="32"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="21"/>
       <c r="B77" s="20"/>
       <c r="C77" s="20"/>
@@ -8170,8 +8186,9 @@
       <c r="E77" s="21"/>
       <c r="F77" s="21"/>
       <c r="G77" s="20"/>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H77" s="32"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="21"/>
       <c r="B78" s="20"/>
       <c r="C78" s="20"/>
@@ -8179,8 +8196,9 @@
       <c r="E78" s="21"/>
       <c r="F78" s="21"/>
       <c r="G78" s="20"/>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H78" s="32"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="21"/>
       <c r="B79" s="20"/>
       <c r="C79" s="20"/>
@@ -8188,8 +8206,9 @@
       <c r="E79" s="21"/>
       <c r="F79" s="21"/>
       <c r="G79" s="20"/>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H79" s="32"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="21"/>
       <c r="B80" s="20"/>
       <c r="C80" s="20"/>
@@ -8197,8 +8216,9 @@
       <c r="E80" s="21"/>
       <c r="F80" s="21"/>
       <c r="G80" s="20"/>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H80" s="32"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="21"/>
       <c r="B81" s="20"/>
       <c r="C81" s="20"/>
@@ -8206,8 +8226,9 @@
       <c r="E81" s="21"/>
       <c r="F81" s="21"/>
       <c r="G81" s="20"/>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H81" s="32"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="21"/>
       <c r="B82" s="20"/>
       <c r="C82" s="20"/>
@@ -8215,8 +8236,9 @@
       <c r="E82" s="21"/>
       <c r="F82" s="21"/>
       <c r="G82" s="20"/>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H82" s="32"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="21"/>
       <c r="B83" s="20"/>
       <c r="C83" s="20"/>
@@ -8224,8 +8246,9 @@
       <c r="E83" s="21"/>
       <c r="F83" s="21"/>
       <c r="G83" s="20"/>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H83" s="32"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="21"/>
       <c r="B84" s="20"/>
       <c r="C84" s="20"/>
@@ -8233,8 +8256,9 @@
       <c r="E84" s="21"/>
       <c r="F84" s="21"/>
       <c r="G84" s="20"/>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H84" s="32"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="21"/>
       <c r="B85" s="20"/>
       <c r="C85" s="20"/>
@@ -8242,8 +8266,9 @@
       <c r="E85" s="21"/>
       <c r="F85" s="21"/>
       <c r="G85" s="20"/>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H85" s="32"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="21"/>
       <c r="B86" s="20"/>
       <c r="C86" s="20"/>
@@ -8251,8 +8276,9 @@
       <c r="E86" s="21"/>
       <c r="F86" s="21"/>
       <c r="G86" s="20"/>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H86" s="32"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="21"/>
       <c r="B87" s="20"/>
       <c r="C87" s="20"/>
@@ -8260,8 +8286,9 @@
       <c r="E87" s="21"/>
       <c r="F87" s="21"/>
       <c r="G87" s="20"/>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H87" s="32"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="21"/>
       <c r="B88" s="20"/>
       <c r="C88" s="20"/>
@@ -8269,8 +8296,9 @@
       <c r="E88" s="21"/>
       <c r="F88" s="21"/>
       <c r="G88" s="20"/>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H88" s="32"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="21"/>
       <c r="B89" s="20"/>
       <c r="C89" s="20"/>
@@ -8278,8 +8306,9 @@
       <c r="E89" s="21"/>
       <c r="F89" s="21"/>
       <c r="G89" s="20"/>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H89" s="32"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="21"/>
       <c r="B90" s="20"/>
       <c r="C90" s="20"/>
@@ -8287,8 +8316,9 @@
       <c r="E90" s="21"/>
       <c r="F90" s="21"/>
       <c r="G90" s="20"/>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H90" s="32"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="21"/>
       <c r="B91" s="20"/>
       <c r="C91" s="20"/>
@@ -8296,8 +8326,9 @@
       <c r="E91" s="21"/>
       <c r="F91" s="21"/>
       <c r="G91" s="20"/>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H91" s="32"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="21"/>
       <c r="B92" s="20"/>
       <c r="C92" s="20"/>
@@ -8305,8 +8336,9 @@
       <c r="E92" s="21"/>
       <c r="F92" s="21"/>
       <c r="G92" s="20"/>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H92" s="32"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="21"/>
       <c r="B93" s="20"/>
       <c r="C93" s="20"/>
@@ -8314,8 +8346,9 @@
       <c r="E93" s="21"/>
       <c r="F93" s="21"/>
       <c r="G93" s="20"/>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H93" s="32"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="21"/>
       <c r="B94" s="20"/>
       <c r="C94" s="20"/>
@@ -8323,8 +8356,9 @@
       <c r="E94" s="21"/>
       <c r="F94" s="21"/>
       <c r="G94" s="20"/>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H94" s="32"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="21"/>
       <c r="B95" s="20"/>
       <c r="C95" s="20"/>
@@ -8332,8 +8366,9 @@
       <c r="E95" s="21"/>
       <c r="F95" s="21"/>
       <c r="G95" s="20"/>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H95" s="32"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="21"/>
       <c r="B96" s="20"/>
       <c r="C96" s="20"/>
@@ -8341,8 +8376,9 @@
       <c r="E96" s="21"/>
       <c r="F96" s="21"/>
       <c r="G96" s="20"/>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H96" s="32"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="21"/>
       <c r="B97" s="20"/>
       <c r="C97" s="20"/>
@@ -8350,8 +8386,9 @@
       <c r="E97" s="21"/>
       <c r="F97" s="21"/>
       <c r="G97" s="20"/>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H97" s="32"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="21"/>
       <c r="B98" s="20"/>
       <c r="C98" s="20"/>
@@ -8359,8 +8396,9 @@
       <c r="E98" s="21"/>
       <c r="F98" s="21"/>
       <c r="G98" s="20"/>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H98" s="32"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="21"/>
       <c r="B99" s="20"/>
       <c r="C99" s="20"/>
@@ -8368,8 +8406,9 @@
       <c r="E99" s="21"/>
       <c r="F99" s="21"/>
       <c r="G99" s="20"/>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H99" s="32"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="21"/>
       <c r="B100" s="20"/>
       <c r="C100" s="20"/>
@@ -8377,8 +8416,9 @@
       <c r="E100" s="21"/>
       <c r="F100" s="21"/>
       <c r="G100" s="20"/>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H100" s="32"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="21"/>
       <c r="B101" s="20"/>
       <c r="C101" s="20"/>
@@ -8386,8 +8426,9 @@
       <c r="E101" s="21"/>
       <c r="F101" s="21"/>
       <c r="G101" s="20"/>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H101" s="32"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="21"/>
       <c r="B102" s="20"/>
       <c r="C102" s="20"/>
@@ -8395,8 +8436,9 @@
       <c r="E102" s="21"/>
       <c r="F102" s="21"/>
       <c r="G102" s="20"/>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H102" s="32"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="21"/>
       <c r="B103" s="20"/>
       <c r="C103" s="20"/>
@@ -8404,8 +8446,9 @@
       <c r="E103" s="21"/>
       <c r="F103" s="21"/>
       <c r="G103" s="20"/>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H103" s="32"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="21"/>
       <c r="B104" s="20"/>
       <c r="C104" s="20"/>
@@ -8413,8 +8456,9 @@
       <c r="E104" s="21"/>
       <c r="F104" s="21"/>
       <c r="G104" s="20"/>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H104" s="32"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" s="21"/>
       <c r="B105" s="20"/>
       <c r="C105" s="20"/>
@@ -8422,8 +8466,9 @@
       <c r="E105" s="21"/>
       <c r="F105" s="21"/>
       <c r="G105" s="20"/>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H105" s="32"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" s="21"/>
       <c r="B106" s="20"/>
       <c r="C106" s="20"/>
@@ -8431,8 +8476,9 @@
       <c r="E106" s="21"/>
       <c r="F106" s="21"/>
       <c r="G106" s="20"/>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H106" s="32"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" s="21"/>
       <c r="B107" s="20"/>
       <c r="C107" s="20"/>
@@ -8440,8 +8486,9 @@
       <c r="E107" s="21"/>
       <c r="F107" s="21"/>
       <c r="G107" s="20"/>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H107" s="32"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" s="21"/>
       <c r="B108" s="20"/>
       <c r="C108" s="20"/>
@@ -8449,8 +8496,9 @@
       <c r="E108" s="21"/>
       <c r="F108" s="21"/>
       <c r="G108" s="20"/>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H108" s="32"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" s="21"/>
       <c r="B109" s="20"/>
       <c r="C109" s="20"/>
@@ -8458,8 +8506,9 @@
       <c r="E109" s="21"/>
       <c r="F109" s="21"/>
       <c r="G109" s="20"/>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H109" s="32"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" s="21"/>
       <c r="B110" s="20"/>
       <c r="C110" s="20"/>
@@ -8467,8 +8516,9 @@
       <c r="E110" s="21"/>
       <c r="F110" s="21"/>
       <c r="G110" s="20"/>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H110" s="32"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" s="21"/>
       <c r="B111" s="20"/>
       <c r="C111" s="20"/>
@@ -8476,6 +8526,7 @@
       <c r="E111" s="21"/>
       <c r="F111" s="21"/>
       <c r="G111" s="20"/>
+      <c r="H111" s="32"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
+++ b/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dee/Downloads/tms/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dee/Desktop/GitHub- Repo/tms/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5721B61C-B435-3B40-B7C4-A0748F703A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EFCED16-3A68-2546-B5B2-BCD3452CEBDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17540" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DB capacity" sheetId="1" r:id="rId1"/>

--- a/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
+++ b/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dee/Desktop/GitHub- Repo/tms/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EFCED16-3A68-2546-B5B2-BCD3452CEBDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B89EDD-254F-0247-BB4E-620FD8E63B51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1953" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1953" uniqueCount="733">
   <si>
     <t>S. N.</t>
   </si>
@@ -2232,6 +2232,12 @@
   </si>
   <si>
     <t>operational</t>
+  </si>
+  <si>
+    <t>Maintenance</t>
+  </si>
+  <si>
+    <t>Non-Operational</t>
   </si>
 </sst>
 </file>
@@ -6530,7 +6536,7 @@
         <v>11</v>
       </c>
       <c r="H5" s="32" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -7421,7 +7427,7 @@
         <v>11</v>
       </c>
       <c r="H38" s="32" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">

--- a/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
+++ b/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dee/Desktop/GitHub- Repo/tms/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B89EDD-254F-0247-BB4E-620FD8E63B51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D279B46-A20B-6944-B05A-6B5D1E0EF277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DB capacity" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,8 @@
     <sheet name="DB Target" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DB capacity'!$B$3:$F$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DB Target'!$A$1:$Q$186</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vehicle Database'!$A$1:$H$60</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1953" uniqueCount="733">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1956" uniqueCount="734">
   <si>
     <t>S. N.</t>
   </si>
@@ -1400,9 +1402,6 @@
     <t>R S Deals</t>
   </si>
   <si>
-    <t>Other's</t>
-  </si>
-  <si>
     <t>FRANCHISE</t>
   </si>
   <si>
@@ -2238,6 +2237,12 @@
   </si>
   <si>
     <t>Non-Operational</t>
+  </si>
+  <si>
+    <t>Walmart</t>
+  </si>
+  <si>
+    <t>SHAHEED PATH</t>
   </si>
 </sst>
 </file>
@@ -6370,16 +6375,24 @@
     </row>
     <row r="200" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B200" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="C200" s="4"/>
-      <c r="D200" s="6"/>
-      <c r="E200" s="6"/>
-      <c r="F200" s="6"/>
+        <v>732</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="D200" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E200" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F200" s="6">
+        <v>20</v>
+      </c>
     </row>
     <row r="201" spans="2:6" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B201" s="12" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C201" s="12"/>
       <c r="D201" s="13"/>
@@ -6387,6 +6400,7 @@
       <c r="F201" s="13"/>
     </row>
   </sheetData>
+  <autoFilter ref="B3:F201" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6429,7 +6443,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="19" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -6455,7 +6469,7 @@
         <v>11</v>
       </c>
       <c r="H2" s="32" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -6467,7 +6481,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D3" s="20" t="s">
         <v>9</v>
@@ -6482,7 +6496,7 @@
         <v>11</v>
       </c>
       <c r="H3" s="32" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -6494,7 +6508,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>9</v>
@@ -6509,7 +6523,7 @@
         <v>11</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -6536,7 +6550,7 @@
         <v>11</v>
       </c>
       <c r="H5" s="32" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -6563,7 +6577,7 @@
         <v>11</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -6590,7 +6604,7 @@
         <v>11</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -6617,7 +6631,7 @@
         <v>11</v>
       </c>
       <c r="H8" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -6644,7 +6658,7 @@
         <v>11</v>
       </c>
       <c r="H9" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -6671,7 +6685,7 @@
         <v>11</v>
       </c>
       <c r="H10" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -6698,7 +6712,7 @@
         <v>11</v>
       </c>
       <c r="H11" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -6725,7 +6739,7 @@
         <v>11</v>
       </c>
       <c r="H12" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -6752,7 +6766,7 @@
         <v>11</v>
       </c>
       <c r="H13" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -6779,7 +6793,7 @@
         <v>11</v>
       </c>
       <c r="H14" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -6806,7 +6820,7 @@
         <v>11</v>
       </c>
       <c r="H15" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -6833,7 +6847,7 @@
         <v>11</v>
       </c>
       <c r="H16" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
@@ -6860,7 +6874,7 @@
         <v>11</v>
       </c>
       <c r="H17" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -6887,7 +6901,7 @@
         <v>11</v>
       </c>
       <c r="H18" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -6914,7 +6928,7 @@
         <v>11</v>
       </c>
       <c r="H19" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -6941,7 +6955,7 @@
         <v>11</v>
       </c>
       <c r="H20" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
@@ -6968,7 +6982,7 @@
         <v>11</v>
       </c>
       <c r="H21" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
@@ -6995,7 +7009,7 @@
         <v>11</v>
       </c>
       <c r="H22" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
@@ -7022,7 +7036,7 @@
         <v>11</v>
       </c>
       <c r="H23" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
@@ -7049,7 +7063,7 @@
         <v>11</v>
       </c>
       <c r="H24" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
@@ -7076,7 +7090,7 @@
         <v>11</v>
       </c>
       <c r="H25" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
@@ -7103,7 +7117,7 @@
         <v>11</v>
       </c>
       <c r="H26" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -7130,7 +7144,7 @@
         <v>11</v>
       </c>
       <c r="H27" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
@@ -7157,7 +7171,7 @@
         <v>11</v>
       </c>
       <c r="H28" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
@@ -7184,7 +7198,7 @@
         <v>11</v>
       </c>
       <c r="H29" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
@@ -7211,7 +7225,7 @@
         <v>11</v>
       </c>
       <c r="H30" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -7238,7 +7252,7 @@
         <v>11</v>
       </c>
       <c r="H31" s="32" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
@@ -7265,7 +7279,7 @@
         <v>11</v>
       </c>
       <c r="H32" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
@@ -7292,7 +7306,7 @@
         <v>11</v>
       </c>
       <c r="H33" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
@@ -7304,7 +7318,7 @@
         <v>7</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D34" s="20" t="s">
         <v>9</v>
@@ -7319,7 +7333,7 @@
         <v>11</v>
       </c>
       <c r="H34" s="32" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
@@ -7346,7 +7360,7 @@
         <v>11</v>
       </c>
       <c r="H35" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
@@ -7373,7 +7387,7 @@
         <v>11</v>
       </c>
       <c r="H36" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -7400,7 +7414,7 @@
         <v>11</v>
       </c>
       <c r="H37" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
@@ -7427,7 +7441,7 @@
         <v>11</v>
       </c>
       <c r="H38" s="32" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
@@ -7454,7 +7468,7 @@
         <v>11</v>
       </c>
       <c r="H39" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
@@ -7481,7 +7495,7 @@
         <v>11</v>
       </c>
       <c r="H40" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
@@ -7493,7 +7507,7 @@
         <v>7</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D41" s="20" t="s">
         <v>9</v>
@@ -7508,7 +7522,7 @@
         <v>11</v>
       </c>
       <c r="H41" s="32" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
@@ -7535,7 +7549,7 @@
         <v>11</v>
       </c>
       <c r="H42" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
@@ -7562,7 +7576,7 @@
         <v>11</v>
       </c>
       <c r="H43" s="32" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
@@ -7589,7 +7603,7 @@
         <v>11</v>
       </c>
       <c r="H44" s="32" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
@@ -7601,7 +7615,7 @@
         <v>7</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D45" s="20" t="s">
         <v>9</v>
@@ -7616,7 +7630,7 @@
         <v>11</v>
       </c>
       <c r="H45" s="32" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
@@ -7643,7 +7657,7 @@
         <v>11</v>
       </c>
       <c r="H46" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
@@ -7670,7 +7684,7 @@
         <v>11</v>
       </c>
       <c r="H47" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
@@ -7697,7 +7711,7 @@
         <v>11</v>
       </c>
       <c r="H48" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
@@ -7724,7 +7738,7 @@
         <v>11</v>
       </c>
       <c r="H49" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
@@ -7736,7 +7750,7 @@
         <v>7</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D50" s="20" t="s">
         <v>9</v>
@@ -7751,7 +7765,7 @@
         <v>11</v>
       </c>
       <c r="H50" s="32" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
@@ -7778,7 +7792,7 @@
         <v>11</v>
       </c>
       <c r="H51" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
@@ -7805,7 +7819,7 @@
         <v>11</v>
       </c>
       <c r="H52" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
@@ -7832,7 +7846,7 @@
         <v>11</v>
       </c>
       <c r="H53" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
@@ -7859,7 +7873,7 @@
         <v>11</v>
       </c>
       <c r="H54" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
@@ -7886,7 +7900,7 @@
         <v>11</v>
       </c>
       <c r="H55" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
@@ -7898,7 +7912,7 @@
         <v>7</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D56" s="20" t="s">
         <v>9</v>
@@ -7913,7 +7927,7 @@
         <v>11</v>
       </c>
       <c r="H56" s="32" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
@@ -7940,7 +7954,7 @@
         <v>11</v>
       </c>
       <c r="H57" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
@@ -7952,7 +7966,7 @@
         <v>7</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D58" s="20" t="s">
         <v>9</v>
@@ -7967,7 +7981,7 @@
         <v>11</v>
       </c>
       <c r="H58" s="32" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
@@ -7994,7 +8008,7 @@
         <v>11</v>
       </c>
       <c r="H59" s="32" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
@@ -8021,7 +8035,7 @@
         <v>11</v>
       </c>
       <c r="H60" s="32" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
@@ -8550,15 +8564,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="27" t="s">
+        <v>454</v>
+      </c>
+      <c r="B1" s="28" t="s">
         <v>455</v>
-      </c>
-      <c r="B1" s="28" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="23" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B2" s="24">
         <v>1200</v>
@@ -8566,7 +8580,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B3">
         <v>1000</v>
@@ -8574,7 +8588,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="23" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B4" s="24">
         <v>800</v>
@@ -8582,7 +8596,7 @@
     </row>
     <row r="5" spans="1:2" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B5" s="24">
         <v>600</v>
@@ -8590,7 +8604,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="25" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B6" s="26">
         <v>350</v>
@@ -8598,34 +8612,34 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="29" t="s">
+        <v>461</v>
+      </c>
+      <c r="B12" s="29" t="s">
         <v>462</v>
-      </c>
-      <c r="B12" s="29" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="17" t="s">
+        <v>463</v>
+      </c>
+      <c r="B13" s="17" t="s">
         <v>464</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="17" t="s">
+        <v>465</v>
+      </c>
+      <c r="B14" s="17" t="s">
         <v>466</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="17" t="s">
+        <v>467</v>
+      </c>
+      <c r="B15" s="17" t="s">
         <v>468</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -8645,55 +8659,55 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
+        <v>469</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>470</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="C1" s="14" t="s">
         <v>471</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="D1" s="14" t="s">
         <v>472</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="E1" s="14" t="s">
         <v>473</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="F1" s="14" t="s">
         <v>474</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="G1" s="14" t="s">
         <v>475</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="H1" s="14" t="s">
         <v>476</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="I1" s="14" t="s">
         <v>477</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="J1" s="14" t="s">
         <v>478</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="K1" s="14" t="s">
         <v>479</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="L1" s="14" t="s">
         <v>480</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="M1" s="14" t="s">
         <v>481</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="N1" s="14" t="s">
         <v>482</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="O1" s="14" t="s">
         <v>483</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="P1" s="14" t="s">
         <v>484</v>
       </c>
-      <c r="P1" s="14" t="s">
+      <c r="Q1" s="14" t="s">
         <v>485</v>
-      </c>
-      <c r="Q1" s="14" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
@@ -8701,7 +8715,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>67</v>
@@ -8754,7 +8768,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>73</v>
@@ -8807,10 +8821,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>489</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>490</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>76</v>
@@ -8860,7 +8874,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>77</v>
@@ -8913,7 +8927,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>79</v>
@@ -8966,7 +8980,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>81</v>
@@ -9019,7 +9033,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>87</v>
@@ -9072,7 +9086,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>89</v>
@@ -9125,7 +9139,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>91</v>
@@ -9178,10 +9192,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="15" t="s">
+        <v>496</v>
+      </c>
+      <c r="C11" s="15" t="s">
         <v>497</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>498</v>
       </c>
       <c r="D11" s="15" t="s">
         <v>94</v>
@@ -9231,7 +9245,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>95</v>
@@ -9284,13 +9298,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>97</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E13" s="15" t="s">
         <v>69</v>
@@ -9337,7 +9351,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>99</v>
@@ -9390,7 +9404,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C15" s="15" t="s">
         <v>101</v>
@@ -9443,10 +9457,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="15" t="s">
+        <v>503</v>
+      </c>
+      <c r="C16" s="15" t="s">
         <v>504</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>505</v>
       </c>
       <c r="D16" s="15" t="s">
         <v>104</v>
@@ -9496,7 +9510,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>105</v>
@@ -9549,7 +9563,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C18" s="15" t="s">
         <v>107</v>
@@ -9602,13 +9616,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>111</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E19" s="15" t="s">
         <v>69</v>
@@ -9655,7 +9669,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C20" s="15" t="s">
         <v>113</v>
@@ -9708,7 +9722,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>115</v>
@@ -9761,7 +9775,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C22" s="15" t="s">
         <v>117</v>
@@ -9814,7 +9828,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>121</v>
@@ -9867,13 +9881,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C24" s="15" t="s">
         <v>123</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E24" s="15" t="s">
         <v>69</v>
@@ -9920,7 +9934,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C25" s="15" t="s">
         <v>128</v>
@@ -9973,7 +9987,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C26" s="15" t="s">
         <v>130</v>
@@ -10026,7 +10040,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C27" s="15" t="s">
         <v>134</v>
@@ -10079,7 +10093,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C28" s="15" t="s">
         <v>136</v>
@@ -10132,7 +10146,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>138</v>
@@ -10185,7 +10199,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>140</v>
@@ -10238,7 +10252,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C31" s="15" t="s">
         <v>142</v>
@@ -10291,7 +10305,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C32" s="15" t="s">
         <v>144</v>
@@ -10344,7 +10358,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>146</v>
@@ -10397,13 +10411,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>152</v>
+        <v>732</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>153</v>
+        <v>69</v>
       </c>
       <c r="E34" s="15" t="s">
         <v>69</v>
@@ -10450,7 +10464,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C35" s="15" t="s">
         <v>154</v>
@@ -10503,7 +10517,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C36" s="15" t="s">
         <v>156</v>
@@ -10556,7 +10570,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C37" s="15" t="s">
         <v>157</v>
@@ -10609,10 +10623,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="15" t="s">
+        <v>528</v>
+      </c>
+      <c r="C38" s="15" t="s">
         <v>529</v>
-      </c>
-      <c r="C38" s="15" t="s">
-        <v>530</v>
       </c>
       <c r="D38" s="15" t="s">
         <v>155</v>
@@ -10651,7 +10665,7 @@
         <v>9900</v>
       </c>
       <c r="P38" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="Q38" s="16">
         <v>6600</v>
@@ -10662,10 +10676,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="15" t="s">
+        <v>531</v>
+      </c>
+      <c r="C39" s="15" t="s">
         <v>532</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>533</v>
       </c>
       <c r="D39" s="15" t="s">
         <v>155</v>
@@ -10684,7 +10698,7 @@
       <c r="N39" s="18"/>
       <c r="O39" s="18"/>
       <c r="P39" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="Q39" s="18"/>
     </row>
@@ -10693,7 +10707,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C40" s="15" t="s">
         <v>166</v>
@@ -10746,7 +10760,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C41" s="15" t="s">
         <v>168</v>
@@ -10799,7 +10813,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C42" s="15" t="s">
         <v>171</v>
@@ -10852,7 +10866,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>173</v>
@@ -10905,7 +10919,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C44" s="15" t="s">
         <v>175</v>
@@ -10958,13 +10972,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="15" t="s">
+        <v>538</v>
+      </c>
+      <c r="C45" s="15" t="s">
         <v>539</v>
       </c>
-      <c r="C45" s="15" t="s">
+      <c r="D45" s="15" t="s">
         <v>540</v>
-      </c>
-      <c r="D45" s="15" t="s">
-        <v>541</v>
       </c>
       <c r="E45" s="15" t="s">
         <v>170</v>
@@ -11011,7 +11025,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C46" s="15" t="s">
         <v>177</v>
@@ -11064,7 +11078,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C47" s="15" t="s">
         <v>181</v>
@@ -11117,7 +11131,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C48" s="15" t="s">
         <v>182</v>
@@ -11170,7 +11184,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C49" s="15" t="s">
         <v>184</v>
@@ -11223,7 +11237,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C50" s="15" t="s">
         <v>186</v>
@@ -11276,7 +11290,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C51" s="15" t="s">
         <v>188</v>
@@ -11329,7 +11343,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C52" s="15" t="s">
         <v>190</v>
@@ -11382,7 +11396,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C53" s="15" t="s">
         <v>192</v>
@@ -11435,10 +11449,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="15" t="s">
+        <v>549</v>
+      </c>
+      <c r="C54" s="15" t="s">
         <v>550</v>
-      </c>
-      <c r="C54" s="15" t="s">
-        <v>551</v>
       </c>
       <c r="D54" s="15" t="s">
         <v>195</v>
@@ -11488,13 +11502,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="15" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C55" s="15" t="s">
         <v>196</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E55" s="15" t="s">
         <v>170</v>
@@ -11541,7 +11555,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="15" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C56" s="15" t="s">
         <v>198</v>
@@ -11594,7 +11608,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="15" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C57" s="15" t="s">
         <v>200</v>
@@ -11647,7 +11661,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C58" s="15" t="s">
         <v>202</v>
@@ -11700,7 +11714,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="15" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C59" s="15" t="s">
         <v>204</v>
@@ -11753,7 +11767,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C60" s="15" t="s">
         <v>206</v>
@@ -11806,13 +11820,13 @@
         <v>60</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C61" s="15" t="s">
         <v>209</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="E61" s="15" t="s">
         <v>170</v>
@@ -11835,7 +11849,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C62" s="15" t="s">
         <v>211</v>
@@ -11888,13 +11902,13 @@
         <v>62</v>
       </c>
       <c r="B63" s="15" t="s">
+        <v>561</v>
+      </c>
+      <c r="C63" s="15" t="s">
         <v>562</v>
       </c>
-      <c r="C63" s="15" t="s">
+      <c r="D63" s="15" t="s">
         <v>563</v>
-      </c>
-      <c r="D63" s="15" t="s">
-        <v>564</v>
       </c>
       <c r="E63" s="15" t="s">
         <v>170</v>
@@ -11941,16 +11955,16 @@
         <v>63</v>
       </c>
       <c r="B64" s="15" t="s">
+        <v>564</v>
+      </c>
+      <c r="C64" s="15" t="s">
         <v>565</v>
       </c>
-      <c r="C64" s="15" t="s">
+      <c r="D64" s="15" t="s">
         <v>566</v>
       </c>
-      <c r="D64" s="15" t="s">
+      <c r="E64" s="15" t="s">
         <v>567</v>
-      </c>
-      <c r="E64" s="15" t="s">
-        <v>568</v>
       </c>
       <c r="F64" s="16">
         <v>6000</v>
@@ -11994,7 +12008,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C65" s="15" t="s">
         <v>216</v>
@@ -12023,7 +12037,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C66" s="15" t="s">
         <v>219</v>
@@ -12032,7 +12046,7 @@
         <v>220</v>
       </c>
       <c r="E66" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F66" s="16">
         <v>3100</v>
@@ -12076,7 +12090,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C67" s="15" t="s">
         <v>221</v>
@@ -12085,7 +12099,7 @@
         <v>222</v>
       </c>
       <c r="E67" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F67" s="16">
         <v>15000</v>
@@ -12129,7 +12143,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C68" s="15" t="s">
         <v>223</v>
@@ -12138,7 +12152,7 @@
         <v>224</v>
       </c>
       <c r="E68" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F68" s="16">
         <v>6300</v>
@@ -12182,7 +12196,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C69" s="15" t="s">
         <v>225</v>
@@ -12191,7 +12205,7 @@
         <v>226</v>
       </c>
       <c r="E69" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F69" s="16">
         <v>5400</v>
@@ -12235,16 +12249,16 @@
         <v>69</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C70" s="15" t="s">
         <v>227</v>
       </c>
       <c r="D70" s="15" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F70" s="16">
         <v>10000</v>
@@ -12288,7 +12302,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="15" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C71" s="15" t="s">
         <v>229</v>
@@ -12297,7 +12311,7 @@
         <v>230</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F71" s="16">
         <v>4700</v>
@@ -12341,7 +12355,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C72" s="15" t="s">
         <v>231</v>
@@ -12350,7 +12364,7 @@
         <v>232</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F72" s="16">
         <v>6300</v>
@@ -12394,7 +12408,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="15" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C73" s="15" t="s">
         <v>233</v>
@@ -12403,7 +12417,7 @@
         <v>234</v>
       </c>
       <c r="E73" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F73" s="16">
         <v>5000</v>
@@ -12447,7 +12461,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="15" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C74" s="15" t="s">
         <v>235</v>
@@ -12456,7 +12470,7 @@
         <v>236</v>
       </c>
       <c r="E74" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F74" s="16">
         <v>1400</v>
@@ -12500,7 +12514,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="15" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C75" s="15" t="s">
         <v>237</v>
@@ -12509,7 +12523,7 @@
         <v>238</v>
       </c>
       <c r="E75" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F75" s="16">
         <v>5000</v>
@@ -12553,16 +12567,16 @@
         <v>75</v>
       </c>
       <c r="B76" s="15" t="s">
+        <v>580</v>
+      </c>
+      <c r="C76" s="15" t="s">
         <v>581</v>
       </c>
-      <c r="C76" s="15" t="s">
+      <c r="D76" s="15" t="s">
         <v>582</v>
       </c>
-      <c r="D76" s="15" t="s">
-        <v>583</v>
-      </c>
       <c r="E76" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F76" s="16">
         <v>7000</v>
@@ -12606,7 +12620,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="15" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C77" s="15" t="s">
         <v>105</v>
@@ -12615,7 +12629,7 @@
         <v>241</v>
       </c>
       <c r="E77" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F77" s="16">
         <v>5900</v>
@@ -12659,7 +12673,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="15" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C78" s="15" t="s">
         <v>242</v>
@@ -12668,7 +12682,7 @@
         <v>243</v>
       </c>
       <c r="E78" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F78" s="16">
         <v>6400</v>
@@ -12712,16 +12726,16 @@
         <v>78</v>
       </c>
       <c r="B79" s="15" t="s">
+        <v>585</v>
+      </c>
+      <c r="C79" s="15" t="s">
         <v>586</v>
-      </c>
-      <c r="C79" s="15" t="s">
-        <v>587</v>
       </c>
       <c r="D79" s="15" t="s">
         <v>245</v>
       </c>
       <c r="E79" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F79" s="16">
         <v>8000</v>
@@ -12765,16 +12779,16 @@
         <v>79</v>
       </c>
       <c r="B80" s="15" t="s">
+        <v>587</v>
+      </c>
+      <c r="C80" s="15" t="s">
         <v>588</v>
-      </c>
-      <c r="C80" s="15" t="s">
-        <v>589</v>
       </c>
       <c r="D80" s="15" t="s">
         <v>247</v>
       </c>
       <c r="E80" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F80" s="16">
         <v>5800</v>
@@ -12818,16 +12832,16 @@
         <v>80</v>
       </c>
       <c r="B81" s="15" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C81" s="15" t="s">
         <v>248</v>
       </c>
       <c r="D81" s="15" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E81" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F81" s="16">
         <v>11000</v>
@@ -12871,7 +12885,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="15" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C82" s="15" t="s">
         <v>250</v>
@@ -12880,7 +12894,7 @@
         <v>251</v>
       </c>
       <c r="E82" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F82" s="16">
         <v>4900</v>
@@ -12924,7 +12938,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="15" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C83" s="15" t="s">
         <v>252</v>
@@ -12933,7 +12947,7 @@
         <v>253</v>
       </c>
       <c r="E83" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F83" s="16">
         <v>5100</v>
@@ -12977,7 +12991,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="15" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C84" s="15" t="s">
         <v>254</v>
@@ -12986,7 +13000,7 @@
         <v>255</v>
       </c>
       <c r="E84" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F84" s="16">
         <v>2800</v>
@@ -13030,16 +13044,16 @@
         <v>84</v>
       </c>
       <c r="B85" s="15" t="s">
+        <v>594</v>
+      </c>
+      <c r="C85" s="15" t="s">
         <v>595</v>
-      </c>
-      <c r="C85" s="15" t="s">
-        <v>596</v>
       </c>
       <c r="D85" s="15" t="s">
         <v>257</v>
       </c>
       <c r="E85" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F85" s="16">
         <v>5900</v>
@@ -13083,16 +13097,16 @@
         <v>85</v>
       </c>
       <c r="B86" s="15" t="s">
+        <v>596</v>
+      </c>
+      <c r="C86" s="15" t="s">
         <v>597</v>
-      </c>
-      <c r="C86" s="15" t="s">
-        <v>598</v>
       </c>
       <c r="D86" s="15" t="s">
         <v>259</v>
       </c>
       <c r="E86" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F86" s="16">
         <v>5000</v>
@@ -13136,7 +13150,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="15" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C87" s="15" t="s">
         <v>260</v>
@@ -13145,7 +13159,7 @@
         <v>261</v>
       </c>
       <c r="E87" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F87" s="16">
         <v>8000</v>
@@ -13189,7 +13203,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C88" s="15" t="s">
         <v>262</v>
@@ -13198,7 +13212,7 @@
         <v>263</v>
       </c>
       <c r="E88" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F88" s="16">
         <v>2900</v>
@@ -13242,7 +13256,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="15" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C89" s="15" t="s">
         <v>264</v>
@@ -13295,7 +13309,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="15" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C90" s="15" t="s">
         <v>266</v>
@@ -13307,40 +13321,40 @@
         <v>265</v>
       </c>
       <c r="F90" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="G90" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H90" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I90" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="J90" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="K90" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="L90" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="M90" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="N90" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="O90" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="P90" s="16">
         <v>1600</v>
       </c>
       <c r="Q90" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.2">
@@ -13348,7 +13362,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="15" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C91" s="15" t="s">
         <v>268</v>
@@ -13401,7 +13415,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C92" s="15" t="s">
         <v>270</v>
@@ -13454,7 +13468,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="15" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C93" s="15" t="s">
         <v>272</v>
@@ -13507,7 +13521,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="15" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C94" s="15" t="s">
         <v>274</v>
@@ -13560,7 +13574,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="15" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C95" s="15" t="s">
         <v>276</v>
@@ -13613,7 +13627,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="15" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C96" s="15" t="s">
         <v>278</v>
@@ -13666,13 +13680,13 @@
         <v>96</v>
       </c>
       <c r="B97" s="15" t="s">
+        <v>608</v>
+      </c>
+      <c r="C97" s="15" t="s">
         <v>609</v>
       </c>
-      <c r="C97" s="15" t="s">
+      <c r="D97" s="15" t="s">
         <v>610</v>
-      </c>
-      <c r="D97" s="15" t="s">
-        <v>611</v>
       </c>
       <c r="E97" s="15" t="s">
         <v>265</v>
@@ -13719,7 +13733,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="15" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C98" s="15" t="s">
         <v>280</v>
@@ -13772,7 +13786,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="15" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C99" s="15" t="s">
         <v>282</v>
@@ -13825,7 +13839,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="15" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C100" s="15" t="s">
         <v>284</v>
@@ -13878,7 +13892,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="15" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C101" s="15" t="s">
         <v>286</v>
@@ -13931,10 +13945,10 @@
         <v>101</v>
       </c>
       <c r="B102" s="15" t="s">
+        <v>615</v>
+      </c>
+      <c r="C102" s="15" t="s">
         <v>616</v>
-      </c>
-      <c r="C102" s="15" t="s">
-        <v>617</v>
       </c>
       <c r="D102" s="15" t="s">
         <v>289</v>
@@ -13984,7 +13998,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="15" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C103" s="15" t="s">
         <v>290</v>
@@ -14037,7 +14051,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="15" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C104" s="15" t="s">
         <v>292</v>
@@ -14090,7 +14104,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="15" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C105" s="15" t="s">
         <v>294</v>
@@ -14143,7 +14157,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="15" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C106" s="15" t="s">
         <v>296</v>
@@ -14196,7 +14210,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C107" s="15" t="s">
         <v>298</v>
@@ -14249,7 +14263,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="15" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C108" s="15" t="s">
         <v>300</v>
@@ -14302,7 +14316,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="15" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C109" s="15" t="s">
         <v>302</v>
@@ -14355,7 +14369,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="15" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C110" s="15" t="s">
         <v>304</v>
@@ -14408,7 +14422,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="15" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C111" s="15" t="s">
         <v>308</v>
@@ -14461,7 +14475,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="15" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C112" s="15" t="s">
         <v>310</v>
@@ -14514,7 +14528,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="15" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C113" s="15" t="s">
         <v>312</v>
@@ -14567,7 +14581,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="15" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C114" s="15" t="s">
         <v>314</v>
@@ -14620,7 +14634,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="15" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C115" s="15" t="s">
         <v>316</v>
@@ -14673,7 +14687,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="15" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C116" s="15" t="s">
         <v>318</v>
@@ -14726,7 +14740,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="15" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C117" s="15" t="s">
         <v>320</v>
@@ -14779,7 +14793,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="15" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C118" s="15" t="s">
         <v>322</v>
@@ -14832,7 +14846,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="15" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C119" s="15" t="s">
         <v>325</v>
@@ -14885,7 +14899,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="15" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C120" s="15" t="s">
         <v>327</v>
@@ -14938,7 +14952,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="15" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C121" s="15" t="s">
         <v>329</v>
@@ -14991,7 +15005,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="15" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C122" s="15" t="s">
         <v>331</v>
@@ -15044,7 +15058,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="15" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C123" s="15" t="s">
         <v>333</v>
@@ -15097,7 +15111,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="15" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C124" s="15" t="s">
         <v>335</v>
@@ -15150,7 +15164,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="15" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C125" s="15" t="s">
         <v>337</v>
@@ -15203,7 +15217,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="15" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C126" s="15" t="s">
         <v>339</v>
@@ -15256,7 +15270,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="15" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C127" s="15" t="s">
         <v>340</v>
@@ -15309,7 +15323,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="15" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C128" s="15" t="s">
         <v>342</v>
@@ -15362,7 +15376,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="15" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C129" s="15" t="s">
         <v>344</v>
@@ -15415,7 +15429,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="15" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C130" s="15" t="s">
         <v>346</v>
@@ -15468,7 +15482,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="15" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C131" s="15" t="s">
         <v>349</v>
@@ -15521,7 +15535,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="15" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C132" s="15" t="s">
         <v>351</v>
@@ -15574,7 +15588,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="15" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C133" s="15" t="s">
         <v>354</v>
@@ -15627,7 +15641,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="15" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C134" s="15" t="s">
         <v>356</v>
@@ -15680,7 +15694,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="15" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C135" s="15" t="s">
         <v>358</v>
@@ -15733,7 +15747,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="15" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C136" s="15" t="s">
         <v>360</v>
@@ -15786,7 +15800,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="15" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C137" s="15" t="s">
         <v>362</v>
@@ -15839,7 +15853,7 @@
         <v>137</v>
       </c>
       <c r="B138" s="15" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C138" s="15" t="s">
         <v>364</v>
@@ -15892,7 +15906,7 @@
         <v>138</v>
       </c>
       <c r="B139" s="15" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C139" s="15" t="s">
         <v>366</v>
@@ -15945,7 +15959,7 @@
         <v>139</v>
       </c>
       <c r="B140" s="15" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C140" s="15" t="s">
         <v>368</v>
@@ -15998,7 +16012,7 @@
         <v>140</v>
       </c>
       <c r="B141" s="15" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C141" s="15" t="s">
         <v>370</v>
@@ -16051,13 +16065,13 @@
         <v>141</v>
       </c>
       <c r="B142" s="15" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C142" s="15" t="s">
         <v>372</v>
       </c>
       <c r="D142" s="15" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E142" s="15" t="s">
         <v>324</v>
@@ -16104,10 +16118,10 @@
         <v>142</v>
       </c>
       <c r="B143" s="15" t="s">
+        <v>658</v>
+      </c>
+      <c r="C143" s="15" t="s">
         <v>659</v>
-      </c>
-      <c r="C143" s="15" t="s">
-        <v>660</v>
       </c>
       <c r="D143" s="15" t="s">
         <v>375</v>
@@ -16157,7 +16171,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="15" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C144" s="15" t="s">
         <v>378</v>
@@ -16210,7 +16224,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="15" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C145" s="15" t="s">
         <v>380</v>
@@ -16263,13 +16277,13 @@
         <v>145</v>
       </c>
       <c r="B146" s="15" t="s">
+        <v>662</v>
+      </c>
+      <c r="C146" s="15" t="s">
         <v>663</v>
       </c>
-      <c r="C146" s="15" t="s">
+      <c r="D146" s="15" t="s">
         <v>664</v>
-      </c>
-      <c r="D146" s="15" t="s">
-        <v>665</v>
       </c>
       <c r="E146" s="15" t="s">
         <v>162</v>
@@ -16316,13 +16330,13 @@
         <v>146</v>
       </c>
       <c r="B147" s="15" t="s">
+        <v>665</v>
+      </c>
+      <c r="C147" s="15" t="s">
         <v>666</v>
       </c>
-      <c r="C147" s="15" t="s">
+      <c r="D147" s="15" t="s">
         <v>667</v>
-      </c>
-      <c r="D147" s="15" t="s">
-        <v>668</v>
       </c>
       <c r="E147" s="15" t="s">
         <v>162</v>
@@ -16369,7 +16383,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="15" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C148" s="15" t="s">
         <v>385</v>
@@ -16422,7 +16436,7 @@
         <v>148</v>
       </c>
       <c r="B149" s="15" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C149" s="15" t="s">
         <v>160</v>
@@ -16475,13 +16489,13 @@
         <v>149</v>
       </c>
       <c r="B150" s="15" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C150" s="15" t="s">
         <v>387</v>
       </c>
       <c r="D150" s="15" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E150" s="15" t="s">
         <v>162</v>
@@ -16528,7 +16542,7 @@
         <v>150</v>
       </c>
       <c r="B151" s="15" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C151" s="15" t="s">
         <v>389</v>
@@ -16581,7 +16595,7 @@
         <v>151</v>
       </c>
       <c r="B152" s="15" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C152" s="15" t="s">
         <v>391</v>
@@ -16634,52 +16648,52 @@
         <v>152</v>
       </c>
       <c r="B153" s="15" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C153" s="15" t="s">
         <v>393</v>
       </c>
       <c r="D153" s="15" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E153" s="15" t="s">
         <v>162</v>
       </c>
       <c r="F153" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="G153" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H153" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I153" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="J153" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="K153" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="L153" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="M153" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="N153" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="O153" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="P153" s="15">
         <v>300</v>
       </c>
       <c r="Q153" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.2">
@@ -16687,7 +16701,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="15" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C154" s="15" t="s">
         <v>395</v>
@@ -16740,10 +16754,10 @@
         <v>154</v>
       </c>
       <c r="B155" s="15" t="s">
+        <v>677</v>
+      </c>
+      <c r="C155" s="15" t="s">
         <v>678</v>
-      </c>
-      <c r="C155" s="15" t="s">
-        <v>679</v>
       </c>
       <c r="D155" s="15" t="s">
         <v>397</v>
@@ -16793,13 +16807,13 @@
         <v>155</v>
       </c>
       <c r="B156" s="15" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C156" s="15" t="s">
         <v>398</v>
       </c>
       <c r="D156" s="15" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E156" s="15" t="s">
         <v>162</v>
@@ -16846,7 +16860,7 @@
         <v>156</v>
       </c>
       <c r="B157" s="15" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C157" s="15" t="s">
         <v>400</v>
@@ -16899,7 +16913,7 @@
         <v>157</v>
       </c>
       <c r="B158" s="15" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C158" s="15" t="s">
         <v>402</v>
@@ -16952,10 +16966,10 @@
         <v>158</v>
       </c>
       <c r="B159" s="15" t="s">
+        <v>683</v>
+      </c>
+      <c r="C159" s="15" t="s">
         <v>684</v>
-      </c>
-      <c r="C159" s="15" t="s">
-        <v>685</v>
       </c>
       <c r="D159" s="15" t="s">
         <v>405</v>
@@ -17005,7 +17019,7 @@
         <v>159</v>
       </c>
       <c r="B160" s="15" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C160" s="15" t="s">
         <v>406</v>
@@ -17058,7 +17072,7 @@
         <v>160</v>
       </c>
       <c r="B161" s="15" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C161" s="15" t="s">
         <v>408</v>
@@ -17111,7 +17125,7 @@
         <v>161</v>
       </c>
       <c r="B162" s="15" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C162" s="15" t="s">
         <v>410</v>
@@ -17164,10 +17178,10 @@
         <v>162</v>
       </c>
       <c r="B163" s="15" t="s">
+        <v>688</v>
+      </c>
+      <c r="C163" s="15" t="s">
         <v>689</v>
-      </c>
-      <c r="C163" s="15" t="s">
-        <v>690</v>
       </c>
       <c r="D163" s="15" t="s">
         <v>413</v>
@@ -17217,13 +17231,13 @@
         <v>163</v>
       </c>
       <c r="B164" s="15" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C164" s="15" t="s">
         <v>414</v>
       </c>
       <c r="D164" s="15" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E164" s="15" t="s">
         <v>162</v>
@@ -17270,13 +17284,13 @@
         <v>164</v>
       </c>
       <c r="B165" s="15" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C165" s="15" t="s">
         <v>416</v>
       </c>
       <c r="D165" s="15" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E165" s="15" t="s">
         <v>162</v>
@@ -17323,7 +17337,7 @@
         <v>165</v>
       </c>
       <c r="B166" s="15" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C166" s="15" t="s">
         <v>418</v>
@@ -17376,10 +17390,10 @@
         <v>166</v>
       </c>
       <c r="B167" s="15" t="s">
+        <v>695</v>
+      </c>
+      <c r="C167" s="15" t="s">
         <v>696</v>
-      </c>
-      <c r="C167" s="15" t="s">
-        <v>697</v>
       </c>
       <c r="D167" s="15" t="s">
         <v>421</v>
@@ -17429,7 +17443,7 @@
         <v>167</v>
       </c>
       <c r="B168" s="15" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C168" s="15" t="s">
         <v>422</v>
@@ -17482,10 +17496,10 @@
         <v>168</v>
       </c>
       <c r="B169" s="15" t="s">
+        <v>698</v>
+      </c>
+      <c r="C169" s="15" t="s">
         <v>699</v>
-      </c>
-      <c r="C169" s="15" t="s">
-        <v>700</v>
       </c>
       <c r="D169" s="15" t="s">
         <v>425</v>
@@ -17535,7 +17549,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="15" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C170" s="15" t="s">
         <v>166</v>
@@ -17588,7 +17602,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="15" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C171" s="15" t="s">
         <v>427</v>
@@ -17641,7 +17655,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="15" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C172" s="15" t="s">
         <v>429</v>
@@ -17694,7 +17708,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="15" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C173" s="15" t="s">
         <v>431</v>
@@ -17747,7 +17761,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="15" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C174" s="15" t="s">
         <v>433</v>
@@ -17800,7 +17814,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="15" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C175" s="15" t="s">
         <v>437</v>
@@ -17853,10 +17867,10 @@
         <v>175</v>
       </c>
       <c r="B176" s="15" t="s">
+        <v>706</v>
+      </c>
+      <c r="C176" s="15" t="s">
         <v>707</v>
-      </c>
-      <c r="C176" s="15" t="s">
-        <v>708</v>
       </c>
       <c r="D176" s="15" t="s">
         <v>440</v>
@@ -17906,7 +17920,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="15" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C177" s="15" t="s">
         <v>441</v>
@@ -17959,7 +17973,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="15" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C178" s="15" t="s">
         <v>95</v>
@@ -18012,7 +18026,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="15" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C179" s="15" t="s">
         <v>444</v>
@@ -18065,7 +18079,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="15" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C180" s="15" t="s">
         <v>446</v>
@@ -18098,7 +18112,7 @@
         <v>500</v>
       </c>
       <c r="M180" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="N180" s="15">
         <v>400</v>
@@ -18118,7 +18132,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="15" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C181" s="15" t="s">
         <v>448</v>
@@ -18171,7 +18185,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="15" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C182" s="15" t="s">
         <v>450</v>
@@ -18224,7 +18238,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="15" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C183" s="15" t="s">
         <v>452</v>
@@ -18277,7 +18291,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="15" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C184" s="15" t="s">
         <v>148</v>
@@ -18299,7 +18313,7 @@
       <c r="N184" s="18"/>
       <c r="O184" s="18"/>
       <c r="P184" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="Q184" s="18"/>
     </row>
@@ -18308,7 +18322,7 @@
         <v>184</v>
       </c>
       <c r="B185" s="15" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C185" s="15" t="s">
         <v>150</v>
@@ -18330,7 +18344,7 @@
       <c r="N185" s="18"/>
       <c r="O185" s="18"/>
       <c r="P185" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="Q185" s="18"/>
     </row>
@@ -18339,7 +18353,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="15" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C186" s="15" t="s">
         <v>215</v>
@@ -18361,11 +18375,12 @@
       <c r="N186" s="18"/>
       <c r="O186" s="18"/>
       <c r="P186" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="Q186" s="18"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:Q186" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
+++ b/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dee/Desktop/GitHub- Repo/tms/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dee/Downloads/tms/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D279B46-A20B-6944-B05A-6B5D1E0EF277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A2724AE-3709-DD4C-8F7F-5A02C5B5C04D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,8 +19,6 @@
     <sheet name="DB Target" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DB capacity'!$B$3:$F$201</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DB Target'!$A$1:$Q$186</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vehicle Database'!$A$1:$H$60</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -41,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1956" uniqueCount="734">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1953" uniqueCount="731">
   <si>
     <t>S. N.</t>
   </si>
@@ -1402,6 +1400,9 @@
     <t>R S Deals</t>
   </si>
   <si>
+    <t>Other's</t>
+  </si>
+  <si>
     <t>FRANCHISE</t>
   </si>
   <si>
@@ -2231,18 +2232,6 @@
   </si>
   <si>
     <t>operational</t>
-  </si>
-  <si>
-    <t>Maintenance</t>
-  </si>
-  <si>
-    <t>Non-Operational</t>
-  </si>
-  <si>
-    <t>Walmart</t>
-  </si>
-  <si>
-    <t>SHAHEED PATH</t>
   </si>
 </sst>
 </file>
@@ -6375,24 +6364,16 @@
     </row>
     <row r="200" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B200" s="5" t="s">
-        <v>732</v>
-      </c>
-      <c r="C200" s="4" t="s">
-        <v>733</v>
-      </c>
-      <c r="D200" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="E200" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F200" s="6">
-        <v>20</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="C200" s="4"/>
+      <c r="D200" s="6"/>
+      <c r="E200" s="6"/>
+      <c r="F200" s="6"/>
     </row>
     <row r="201" spans="2:6" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B201" s="12" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C201" s="12"/>
       <c r="D201" s="13"/>
@@ -6400,7 +6381,6 @@
       <c r="F201" s="13"/>
     </row>
   </sheetData>
-  <autoFilter ref="B3:F201" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6443,7 +6423,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="19" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -6469,7 +6449,7 @@
         <v>11</v>
       </c>
       <c r="H2" s="32" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -6481,7 +6461,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D3" s="20" t="s">
         <v>9</v>
@@ -6496,7 +6476,7 @@
         <v>11</v>
       </c>
       <c r="H3" s="32" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -6508,7 +6488,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>9</v>
@@ -6523,7 +6503,7 @@
         <v>11</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -6577,7 +6557,7 @@
         <v>11</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -6604,7 +6584,7 @@
         <v>11</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -6631,7 +6611,7 @@
         <v>11</v>
       </c>
       <c r="H8" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -6658,7 +6638,7 @@
         <v>11</v>
       </c>
       <c r="H9" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -6685,7 +6665,7 @@
         <v>11</v>
       </c>
       <c r="H10" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -6712,7 +6692,7 @@
         <v>11</v>
       </c>
       <c r="H11" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -6739,7 +6719,7 @@
         <v>11</v>
       </c>
       <c r="H12" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -6766,7 +6746,7 @@
         <v>11</v>
       </c>
       <c r="H13" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -6793,7 +6773,7 @@
         <v>11</v>
       </c>
       <c r="H14" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -6820,7 +6800,7 @@
         <v>11</v>
       </c>
       <c r="H15" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -6847,7 +6827,7 @@
         <v>11</v>
       </c>
       <c r="H16" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
@@ -6874,7 +6854,7 @@
         <v>11</v>
       </c>
       <c r="H17" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -6901,7 +6881,7 @@
         <v>11</v>
       </c>
       <c r="H18" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -6928,7 +6908,7 @@
         <v>11</v>
       </c>
       <c r="H19" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -6955,7 +6935,7 @@
         <v>11</v>
       </c>
       <c r="H20" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
@@ -6982,7 +6962,7 @@
         <v>11</v>
       </c>
       <c r="H21" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
@@ -7009,7 +6989,7 @@
         <v>11</v>
       </c>
       <c r="H22" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
@@ -7036,7 +7016,7 @@
         <v>11</v>
       </c>
       <c r="H23" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
@@ -7063,7 +7043,7 @@
         <v>11</v>
       </c>
       <c r="H24" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
@@ -7090,7 +7070,7 @@
         <v>11</v>
       </c>
       <c r="H25" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
@@ -7117,7 +7097,7 @@
         <v>11</v>
       </c>
       <c r="H26" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -7144,7 +7124,7 @@
         <v>11</v>
       </c>
       <c r="H27" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
@@ -7171,7 +7151,7 @@
         <v>11</v>
       </c>
       <c r="H28" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
@@ -7198,7 +7178,7 @@
         <v>11</v>
       </c>
       <c r="H29" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
@@ -7225,7 +7205,7 @@
         <v>11</v>
       </c>
       <c r="H30" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -7252,7 +7232,7 @@
         <v>11</v>
       </c>
       <c r="H31" s="32" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
@@ -7279,7 +7259,7 @@
         <v>11</v>
       </c>
       <c r="H32" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
@@ -7306,7 +7286,7 @@
         <v>11</v>
       </c>
       <c r="H33" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
@@ -7318,7 +7298,7 @@
         <v>7</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D34" s="20" t="s">
         <v>9</v>
@@ -7333,7 +7313,7 @@
         <v>11</v>
       </c>
       <c r="H34" s="32" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
@@ -7360,7 +7340,7 @@
         <v>11</v>
       </c>
       <c r="H35" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
@@ -7387,7 +7367,7 @@
         <v>11</v>
       </c>
       <c r="H36" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -7414,7 +7394,7 @@
         <v>11</v>
       </c>
       <c r="H37" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
@@ -7441,7 +7421,7 @@
         <v>11</v>
       </c>
       <c r="H38" s="32" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
@@ -7468,7 +7448,7 @@
         <v>11</v>
       </c>
       <c r="H39" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
@@ -7495,7 +7475,7 @@
         <v>11</v>
       </c>
       <c r="H40" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
@@ -7507,7 +7487,7 @@
         <v>7</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="D41" s="20" t="s">
         <v>9</v>
@@ -7522,7 +7502,7 @@
         <v>11</v>
       </c>
       <c r="H41" s="32" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
@@ -7549,7 +7529,7 @@
         <v>11</v>
       </c>
       <c r="H42" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
@@ -7576,7 +7556,7 @@
         <v>11</v>
       </c>
       <c r="H43" s="32" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
@@ -7603,7 +7583,7 @@
         <v>11</v>
       </c>
       <c r="H44" s="32" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
@@ -7615,7 +7595,7 @@
         <v>7</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D45" s="20" t="s">
         <v>9</v>
@@ -7630,7 +7610,7 @@
         <v>11</v>
       </c>
       <c r="H45" s="32" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
@@ -7657,7 +7637,7 @@
         <v>11</v>
       </c>
       <c r="H46" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
@@ -7684,7 +7664,7 @@
         <v>11</v>
       </c>
       <c r="H47" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
@@ -7711,7 +7691,7 @@
         <v>11</v>
       </c>
       <c r="H48" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
@@ -7738,7 +7718,7 @@
         <v>11</v>
       </c>
       <c r="H49" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
@@ -7750,7 +7730,7 @@
         <v>7</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="D50" s="20" t="s">
         <v>9</v>
@@ -7765,7 +7745,7 @@
         <v>11</v>
       </c>
       <c r="H50" s="32" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
@@ -7792,7 +7772,7 @@
         <v>11</v>
       </c>
       <c r="H51" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
@@ -7819,7 +7799,7 @@
         <v>11</v>
       </c>
       <c r="H52" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
@@ -7846,7 +7826,7 @@
         <v>11</v>
       </c>
       <c r="H53" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
@@ -7873,7 +7853,7 @@
         <v>11</v>
       </c>
       <c r="H54" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
@@ -7900,7 +7880,7 @@
         <v>11</v>
       </c>
       <c r="H55" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
@@ -7912,7 +7892,7 @@
         <v>7</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D56" s="20" t="s">
         <v>9</v>
@@ -7927,7 +7907,7 @@
         <v>11</v>
       </c>
       <c r="H56" s="32" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
@@ -7954,7 +7934,7 @@
         <v>11</v>
       </c>
       <c r="H57" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
@@ -7966,7 +7946,7 @@
         <v>7</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D58" s="20" t="s">
         <v>9</v>
@@ -7981,7 +7961,7 @@
         <v>11</v>
       </c>
       <c r="H58" s="32" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
@@ -8008,7 +7988,7 @@
         <v>11</v>
       </c>
       <c r="H59" s="32" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
@@ -8035,7 +8015,7 @@
         <v>11</v>
       </c>
       <c r="H60" s="32" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
@@ -8564,15 +8544,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="27" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="23" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B2" s="24">
         <v>1200</v>
@@ -8580,7 +8560,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B3">
         <v>1000</v>
@@ -8588,7 +8568,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B4" s="24">
         <v>800</v>
@@ -8596,7 +8576,7 @@
     </row>
     <row r="5" spans="1:2" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B5" s="24">
         <v>600</v>
@@ -8604,7 +8584,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="25" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B6" s="26">
         <v>350</v>
@@ -8612,34 +8592,34 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="29" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="17" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="17" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="17" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -8659,55 +8639,55 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="P1" s="14" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="Q1" s="14" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
@@ -8715,7 +8695,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>67</v>
@@ -8768,7 +8748,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>73</v>
@@ -8821,10 +8801,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>76</v>
@@ -8874,7 +8854,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>77</v>
@@ -8927,7 +8907,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>79</v>
@@ -8980,7 +8960,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>81</v>
@@ -9033,7 +9013,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>87</v>
@@ -9086,7 +9066,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>89</v>
@@ -9139,7 +9119,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>91</v>
@@ -9192,10 +9172,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D11" s="15" t="s">
         <v>94</v>
@@ -9245,7 +9225,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>95</v>
@@ -9298,13 +9278,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>97</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E13" s="15" t="s">
         <v>69</v>
@@ -9351,7 +9331,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>99</v>
@@ -9404,7 +9384,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C15" s="15" t="s">
         <v>101</v>
@@ -9457,10 +9437,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D16" s="15" t="s">
         <v>104</v>
@@ -9510,7 +9490,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>105</v>
@@ -9563,7 +9543,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C18" s="15" t="s">
         <v>107</v>
@@ -9616,13 +9596,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>111</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E19" s="15" t="s">
         <v>69</v>
@@ -9669,7 +9649,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C20" s="15" t="s">
         <v>113</v>
@@ -9722,7 +9702,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>115</v>
@@ -9775,7 +9755,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C22" s="15" t="s">
         <v>117</v>
@@ -9828,7 +9808,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>121</v>
@@ -9881,13 +9861,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C24" s="15" t="s">
         <v>123</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E24" s="15" t="s">
         <v>69</v>
@@ -9934,7 +9914,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C25" s="15" t="s">
         <v>128</v>
@@ -9987,7 +9967,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C26" s="15" t="s">
         <v>130</v>
@@ -10040,7 +10020,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C27" s="15" t="s">
         <v>134</v>
@@ -10093,7 +10073,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C28" s="15" t="s">
         <v>136</v>
@@ -10146,7 +10126,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>138</v>
@@ -10199,7 +10179,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>140</v>
@@ -10252,7 +10232,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C31" s="15" t="s">
         <v>142</v>
@@ -10305,7 +10285,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C32" s="15" t="s">
         <v>144</v>
@@ -10358,7 +10338,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>146</v>
@@ -10411,13 +10391,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>732</v>
+        <v>152</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>69</v>
+        <v>153</v>
       </c>
       <c r="E34" s="15" t="s">
         <v>69</v>
@@ -10464,7 +10444,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C35" s="15" t="s">
         <v>154</v>
@@ -10517,7 +10497,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C36" s="15" t="s">
         <v>156</v>
@@ -10570,7 +10550,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C37" s="15" t="s">
         <v>157</v>
@@ -10623,10 +10603,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D38" s="15" t="s">
         <v>155</v>
@@ -10665,7 +10645,7 @@
         <v>9900</v>
       </c>
       <c r="P38" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="Q38" s="16">
         <v>6600</v>
@@ -10676,10 +10656,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D39" s="15" t="s">
         <v>155</v>
@@ -10698,7 +10678,7 @@
       <c r="N39" s="18"/>
       <c r="O39" s="18"/>
       <c r="P39" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="Q39" s="18"/>
     </row>
@@ -10707,7 +10687,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C40" s="15" t="s">
         <v>166</v>
@@ -10760,7 +10740,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C41" s="15" t="s">
         <v>168</v>
@@ -10813,7 +10793,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C42" s="15" t="s">
         <v>171</v>
@@ -10866,7 +10846,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>173</v>
@@ -10919,7 +10899,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C44" s="15" t="s">
         <v>175</v>
@@ -10972,13 +10952,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E45" s="15" t="s">
         <v>170</v>
@@ -11025,7 +11005,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C46" s="15" t="s">
         <v>177</v>
@@ -11078,7 +11058,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C47" s="15" t="s">
         <v>181</v>
@@ -11131,7 +11111,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C48" s="15" t="s">
         <v>182</v>
@@ -11184,7 +11164,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C49" s="15" t="s">
         <v>184</v>
@@ -11237,7 +11217,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C50" s="15" t="s">
         <v>186</v>
@@ -11290,7 +11270,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C51" s="15" t="s">
         <v>188</v>
@@ -11343,7 +11323,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C52" s="15" t="s">
         <v>190</v>
@@ -11396,7 +11376,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C53" s="15" t="s">
         <v>192</v>
@@ -11449,10 +11429,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="15" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D54" s="15" t="s">
         <v>195</v>
@@ -11502,13 +11482,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="15" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C55" s="15" t="s">
         <v>196</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E55" s="15" t="s">
         <v>170</v>
@@ -11555,7 +11535,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="15" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C56" s="15" t="s">
         <v>198</v>
@@ -11608,7 +11588,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="15" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C57" s="15" t="s">
         <v>200</v>
@@ -11661,7 +11641,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C58" s="15" t="s">
         <v>202</v>
@@ -11714,7 +11694,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="15" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C59" s="15" t="s">
         <v>204</v>
@@ -11767,7 +11747,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C60" s="15" t="s">
         <v>206</v>
@@ -11820,13 +11800,13 @@
         <v>60</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C61" s="15" t="s">
         <v>209</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E61" s="15" t="s">
         <v>170</v>
@@ -11849,7 +11829,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C62" s="15" t="s">
         <v>211</v>
@@ -11902,13 +11882,13 @@
         <v>62</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E63" s="15" t="s">
         <v>170</v>
@@ -11955,16 +11935,16 @@
         <v>63</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E64" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F64" s="16">
         <v>6000</v>
@@ -12008,7 +11988,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C65" s="15" t="s">
         <v>216</v>
@@ -12037,7 +12017,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C66" s="15" t="s">
         <v>219</v>
@@ -12046,7 +12026,7 @@
         <v>220</v>
       </c>
       <c r="E66" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F66" s="16">
         <v>3100</v>
@@ -12090,7 +12070,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C67" s="15" t="s">
         <v>221</v>
@@ -12099,7 +12079,7 @@
         <v>222</v>
       </c>
       <c r="E67" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F67" s="16">
         <v>15000</v>
@@ -12143,7 +12123,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C68" s="15" t="s">
         <v>223</v>
@@ -12152,7 +12132,7 @@
         <v>224</v>
       </c>
       <c r="E68" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F68" s="16">
         <v>6300</v>
@@ -12196,7 +12176,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C69" s="15" t="s">
         <v>225</v>
@@ -12205,7 +12185,7 @@
         <v>226</v>
       </c>
       <c r="E69" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F69" s="16">
         <v>5400</v>
@@ -12249,16 +12229,16 @@
         <v>69</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C70" s="15" t="s">
         <v>227</v>
       </c>
       <c r="D70" s="15" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F70" s="16">
         <v>10000</v>
@@ -12302,7 +12282,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="15" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C71" s="15" t="s">
         <v>229</v>
@@ -12311,7 +12291,7 @@
         <v>230</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F71" s="16">
         <v>4700</v>
@@ -12355,7 +12335,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C72" s="15" t="s">
         <v>231</v>
@@ -12364,7 +12344,7 @@
         <v>232</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F72" s="16">
         <v>6300</v>
@@ -12408,7 +12388,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="15" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C73" s="15" t="s">
         <v>233</v>
@@ -12417,7 +12397,7 @@
         <v>234</v>
       </c>
       <c r="E73" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F73" s="16">
         <v>5000</v>
@@ -12461,7 +12441,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="15" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C74" s="15" t="s">
         <v>235</v>
@@ -12470,7 +12450,7 @@
         <v>236</v>
       </c>
       <c r="E74" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F74" s="16">
         <v>1400</v>
@@ -12514,7 +12494,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="15" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C75" s="15" t="s">
         <v>237</v>
@@ -12523,7 +12503,7 @@
         <v>238</v>
       </c>
       <c r="E75" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F75" s="16">
         <v>5000</v>
@@ -12567,16 +12547,16 @@
         <v>75</v>
       </c>
       <c r="B76" s="15" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C76" s="15" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D76" s="15" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E76" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F76" s="16">
         <v>7000</v>
@@ -12620,7 +12600,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="15" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C77" s="15" t="s">
         <v>105</v>
@@ -12629,7 +12609,7 @@
         <v>241</v>
       </c>
       <c r="E77" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F77" s="16">
         <v>5900</v>
@@ -12673,7 +12653,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="15" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C78" s="15" t="s">
         <v>242</v>
@@ -12682,7 +12662,7 @@
         <v>243</v>
       </c>
       <c r="E78" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F78" s="16">
         <v>6400</v>
@@ -12726,16 +12706,16 @@
         <v>78</v>
       </c>
       <c r="B79" s="15" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D79" s="15" t="s">
         <v>245</v>
       </c>
       <c r="E79" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F79" s="16">
         <v>8000</v>
@@ -12779,16 +12759,16 @@
         <v>79</v>
       </c>
       <c r="B80" s="15" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D80" s="15" t="s">
         <v>247</v>
       </c>
       <c r="E80" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F80" s="16">
         <v>5800</v>
@@ -12832,16 +12812,16 @@
         <v>80</v>
       </c>
       <c r="B81" s="15" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C81" s="15" t="s">
         <v>248</v>
       </c>
       <c r="D81" s="15" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E81" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F81" s="16">
         <v>11000</v>
@@ -12885,7 +12865,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="15" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C82" s="15" t="s">
         <v>250</v>
@@ -12894,7 +12874,7 @@
         <v>251</v>
       </c>
       <c r="E82" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F82" s="16">
         <v>4900</v>
@@ -12938,7 +12918,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="15" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C83" s="15" t="s">
         <v>252</v>
@@ -12947,7 +12927,7 @@
         <v>253</v>
       </c>
       <c r="E83" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F83" s="16">
         <v>5100</v>
@@ -12991,7 +12971,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="15" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C84" s="15" t="s">
         <v>254</v>
@@ -13000,7 +12980,7 @@
         <v>255</v>
       </c>
       <c r="E84" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F84" s="16">
         <v>2800</v>
@@ -13044,16 +13024,16 @@
         <v>84</v>
       </c>
       <c r="B85" s="15" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D85" s="15" t="s">
         <v>257</v>
       </c>
       <c r="E85" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F85" s="16">
         <v>5900</v>
@@ -13097,16 +13077,16 @@
         <v>85</v>
       </c>
       <c r="B86" s="15" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C86" s="15" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D86" s="15" t="s">
         <v>259</v>
       </c>
       <c r="E86" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F86" s="16">
         <v>5000</v>
@@ -13150,7 +13130,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="15" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C87" s="15" t="s">
         <v>260</v>
@@ -13159,7 +13139,7 @@
         <v>261</v>
       </c>
       <c r="E87" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F87" s="16">
         <v>8000</v>
@@ -13203,7 +13183,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C88" s="15" t="s">
         <v>262</v>
@@ -13212,7 +13192,7 @@
         <v>263</v>
       </c>
       <c r="E88" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F88" s="16">
         <v>2900</v>
@@ -13256,7 +13236,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="15" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C89" s="15" t="s">
         <v>264</v>
@@ -13309,7 +13289,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="15" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C90" s="15" t="s">
         <v>266</v>
@@ -13321,40 +13301,40 @@
         <v>265</v>
       </c>
       <c r="F90" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="G90" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H90" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="I90" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="J90" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="K90" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="L90" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M90" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N90" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O90" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P90" s="16">
         <v>1600</v>
       </c>
       <c r="Q90" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.2">
@@ -13362,7 +13342,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="15" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C91" s="15" t="s">
         <v>268</v>
@@ -13415,7 +13395,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C92" s="15" t="s">
         <v>270</v>
@@ -13468,7 +13448,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="15" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C93" s="15" t="s">
         <v>272</v>
@@ -13521,7 +13501,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="15" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C94" s="15" t="s">
         <v>274</v>
@@ -13574,7 +13554,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="15" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C95" s="15" t="s">
         <v>276</v>
@@ -13627,7 +13607,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="15" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C96" s="15" t="s">
         <v>278</v>
@@ -13680,13 +13660,13 @@
         <v>96</v>
       </c>
       <c r="B97" s="15" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C97" s="15" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D97" s="15" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E97" s="15" t="s">
         <v>265</v>
@@ -13733,7 +13713,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="15" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C98" s="15" t="s">
         <v>280</v>
@@ -13786,7 +13766,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="15" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C99" s="15" t="s">
         <v>282</v>
@@ -13839,7 +13819,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="15" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C100" s="15" t="s">
         <v>284</v>
@@ -13892,7 +13872,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="15" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C101" s="15" t="s">
         <v>286</v>
@@ -13945,10 +13925,10 @@
         <v>101</v>
       </c>
       <c r="B102" s="15" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C102" s="15" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D102" s="15" t="s">
         <v>289</v>
@@ -13998,7 +13978,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="15" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C103" s="15" t="s">
         <v>290</v>
@@ -14051,7 +14031,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="15" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C104" s="15" t="s">
         <v>292</v>
@@ -14104,7 +14084,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="15" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C105" s="15" t="s">
         <v>294</v>
@@ -14157,7 +14137,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="15" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C106" s="15" t="s">
         <v>296</v>
@@ -14210,7 +14190,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="15" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C107" s="15" t="s">
         <v>298</v>
@@ -14263,7 +14243,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="15" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C108" s="15" t="s">
         <v>300</v>
@@ -14316,7 +14296,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="15" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C109" s="15" t="s">
         <v>302</v>
@@ -14369,7 +14349,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="15" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C110" s="15" t="s">
         <v>304</v>
@@ -14422,7 +14402,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="15" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C111" s="15" t="s">
         <v>308</v>
@@ -14475,7 +14455,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="15" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C112" s="15" t="s">
         <v>310</v>
@@ -14528,7 +14508,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="15" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C113" s="15" t="s">
         <v>312</v>
@@ -14581,7 +14561,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="15" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C114" s="15" t="s">
         <v>314</v>
@@ -14634,7 +14614,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="15" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C115" s="15" t="s">
         <v>316</v>
@@ -14687,7 +14667,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="15" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C116" s="15" t="s">
         <v>318</v>
@@ -14740,7 +14720,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="15" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C117" s="15" t="s">
         <v>320</v>
@@ -14793,7 +14773,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="15" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C118" s="15" t="s">
         <v>322</v>
@@ -14846,7 +14826,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="15" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C119" s="15" t="s">
         <v>325</v>
@@ -14899,7 +14879,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="15" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C120" s="15" t="s">
         <v>327</v>
@@ -14952,7 +14932,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="15" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C121" s="15" t="s">
         <v>329</v>
@@ -15005,7 +14985,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="15" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C122" s="15" t="s">
         <v>331</v>
@@ -15058,7 +15038,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="15" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C123" s="15" t="s">
         <v>333</v>
@@ -15111,7 +15091,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="15" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C124" s="15" t="s">
         <v>335</v>
@@ -15164,7 +15144,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="15" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C125" s="15" t="s">
         <v>337</v>
@@ -15217,7 +15197,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="15" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C126" s="15" t="s">
         <v>339</v>
@@ -15270,7 +15250,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="15" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C127" s="15" t="s">
         <v>340</v>
@@ -15323,7 +15303,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="15" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C128" s="15" t="s">
         <v>342</v>
@@ -15376,7 +15356,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="15" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C129" s="15" t="s">
         <v>344</v>
@@ -15429,7 +15409,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="15" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C130" s="15" t="s">
         <v>346</v>
@@ -15482,7 +15462,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="15" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C131" s="15" t="s">
         <v>349</v>
@@ -15535,7 +15515,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="15" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C132" s="15" t="s">
         <v>351</v>
@@ -15588,7 +15568,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="15" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C133" s="15" t="s">
         <v>354</v>
@@ -15641,7 +15621,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="15" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C134" s="15" t="s">
         <v>356</v>
@@ -15694,7 +15674,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="15" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C135" s="15" t="s">
         <v>358</v>
@@ -15747,7 +15727,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="15" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C136" s="15" t="s">
         <v>360</v>
@@ -15800,7 +15780,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="15" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C137" s="15" t="s">
         <v>362</v>
@@ -15853,7 +15833,7 @@
         <v>137</v>
       </c>
       <c r="B138" s="15" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C138" s="15" t="s">
         <v>364</v>
@@ -15906,7 +15886,7 @@
         <v>138</v>
       </c>
       <c r="B139" s="15" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C139" s="15" t="s">
         <v>366</v>
@@ -15959,7 +15939,7 @@
         <v>139</v>
       </c>
       <c r="B140" s="15" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C140" s="15" t="s">
         <v>368</v>
@@ -16012,7 +15992,7 @@
         <v>140</v>
       </c>
       <c r="B141" s="15" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C141" s="15" t="s">
         <v>370</v>
@@ -16065,13 +16045,13 @@
         <v>141</v>
       </c>
       <c r="B142" s="15" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C142" s="15" t="s">
         <v>372</v>
       </c>
       <c r="D142" s="15" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E142" s="15" t="s">
         <v>324</v>
@@ -16118,10 +16098,10 @@
         <v>142</v>
       </c>
       <c r="B143" s="15" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C143" s="15" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="D143" s="15" t="s">
         <v>375</v>
@@ -16171,7 +16151,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="15" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C144" s="15" t="s">
         <v>378</v>
@@ -16224,7 +16204,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="15" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C145" s="15" t="s">
         <v>380</v>
@@ -16277,13 +16257,13 @@
         <v>145</v>
       </c>
       <c r="B146" s="15" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C146" s="15" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D146" s="15" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="E146" s="15" t="s">
         <v>162</v>
@@ -16330,13 +16310,13 @@
         <v>146</v>
       </c>
       <c r="B147" s="15" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C147" s="15" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D147" s="15" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E147" s="15" t="s">
         <v>162</v>
@@ -16383,7 +16363,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="15" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C148" s="15" t="s">
         <v>385</v>
@@ -16436,7 +16416,7 @@
         <v>148</v>
       </c>
       <c r="B149" s="15" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C149" s="15" t="s">
         <v>160</v>
@@ -16489,13 +16469,13 @@
         <v>149</v>
       </c>
       <c r="B150" s="15" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C150" s="15" t="s">
         <v>387</v>
       </c>
       <c r="D150" s="15" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E150" s="15" t="s">
         <v>162</v>
@@ -16542,7 +16522,7 @@
         <v>150</v>
       </c>
       <c r="B151" s="15" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C151" s="15" t="s">
         <v>389</v>
@@ -16595,7 +16575,7 @@
         <v>151</v>
       </c>
       <c r="B152" s="15" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C152" s="15" t="s">
         <v>391</v>
@@ -16648,52 +16628,52 @@
         <v>152</v>
       </c>
       <c r="B153" s="15" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C153" s="15" t="s">
         <v>393</v>
       </c>
       <c r="D153" s="15" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E153" s="15" t="s">
         <v>162</v>
       </c>
       <c r="F153" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="G153" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H153" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="I153" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="J153" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="K153" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="L153" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M153" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N153" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O153" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P153" s="15">
         <v>300</v>
       </c>
       <c r="Q153" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.2">
@@ -16701,7 +16681,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="15" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C154" s="15" t="s">
         <v>395</v>
@@ -16754,10 +16734,10 @@
         <v>154</v>
       </c>
       <c r="B155" s="15" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C155" s="15" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D155" s="15" t="s">
         <v>397</v>
@@ -16807,13 +16787,13 @@
         <v>155</v>
       </c>
       <c r="B156" s="15" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C156" s="15" t="s">
         <v>398</v>
       </c>
       <c r="D156" s="15" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E156" s="15" t="s">
         <v>162</v>
@@ -16860,7 +16840,7 @@
         <v>156</v>
       </c>
       <c r="B157" s="15" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C157" s="15" t="s">
         <v>400</v>
@@ -16913,7 +16893,7 @@
         <v>157</v>
       </c>
       <c r="B158" s="15" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C158" s="15" t="s">
         <v>402</v>
@@ -16966,10 +16946,10 @@
         <v>158</v>
       </c>
       <c r="B159" s="15" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C159" s="15" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D159" s="15" t="s">
         <v>405</v>
@@ -17019,7 +16999,7 @@
         <v>159</v>
       </c>
       <c r="B160" s="15" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C160" s="15" t="s">
         <v>406</v>
@@ -17072,7 +17052,7 @@
         <v>160</v>
       </c>
       <c r="B161" s="15" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C161" s="15" t="s">
         <v>408</v>
@@ -17125,7 +17105,7 @@
         <v>161</v>
       </c>
       <c r="B162" s="15" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C162" s="15" t="s">
         <v>410</v>
@@ -17178,10 +17158,10 @@
         <v>162</v>
       </c>
       <c r="B163" s="15" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C163" s="15" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D163" s="15" t="s">
         <v>413</v>
@@ -17231,13 +17211,13 @@
         <v>163</v>
       </c>
       <c r="B164" s="15" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C164" s="15" t="s">
         <v>414</v>
       </c>
       <c r="D164" s="15" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E164" s="15" t="s">
         <v>162</v>
@@ -17284,13 +17264,13 @@
         <v>164</v>
       </c>
       <c r="B165" s="15" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C165" s="15" t="s">
         <v>416</v>
       </c>
       <c r="D165" s="15" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E165" s="15" t="s">
         <v>162</v>
@@ -17337,7 +17317,7 @@
         <v>165</v>
       </c>
       <c r="B166" s="15" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C166" s="15" t="s">
         <v>418</v>
@@ -17390,10 +17370,10 @@
         <v>166</v>
       </c>
       <c r="B167" s="15" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C167" s="15" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D167" s="15" t="s">
         <v>421</v>
@@ -17443,7 +17423,7 @@
         <v>167</v>
       </c>
       <c r="B168" s="15" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C168" s="15" t="s">
         <v>422</v>
@@ -17496,10 +17476,10 @@
         <v>168</v>
       </c>
       <c r="B169" s="15" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C169" s="15" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D169" s="15" t="s">
         <v>425</v>
@@ -17549,7 +17529,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="15" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C170" s="15" t="s">
         <v>166</v>
@@ -17602,7 +17582,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="15" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C171" s="15" t="s">
         <v>427</v>
@@ -17655,7 +17635,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="15" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C172" s="15" t="s">
         <v>429</v>
@@ -17708,7 +17688,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="15" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C173" s="15" t="s">
         <v>431</v>
@@ -17761,7 +17741,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="15" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C174" s="15" t="s">
         <v>433</v>
@@ -17814,7 +17794,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="15" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C175" s="15" t="s">
         <v>437</v>
@@ -17867,10 +17847,10 @@
         <v>175</v>
       </c>
       <c r="B176" s="15" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C176" s="15" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D176" s="15" t="s">
         <v>440</v>
@@ -17920,7 +17900,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="15" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C177" s="15" t="s">
         <v>441</v>
@@ -17973,7 +17953,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="15" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C178" s="15" t="s">
         <v>95</v>
@@ -18026,7 +18006,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="15" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C179" s="15" t="s">
         <v>444</v>
@@ -18079,7 +18059,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="15" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C180" s="15" t="s">
         <v>446</v>
@@ -18112,7 +18092,7 @@
         <v>500</v>
       </c>
       <c r="M180" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N180" s="15">
         <v>400</v>
@@ -18132,7 +18112,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="15" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C181" s="15" t="s">
         <v>448</v>
@@ -18185,7 +18165,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="15" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C182" s="15" t="s">
         <v>450</v>
@@ -18238,7 +18218,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="15" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C183" s="15" t="s">
         <v>452</v>
@@ -18291,7 +18271,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="15" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C184" s="15" t="s">
         <v>148</v>
@@ -18313,7 +18293,7 @@
       <c r="N184" s="18"/>
       <c r="O184" s="18"/>
       <c r="P184" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="Q184" s="18"/>
     </row>
@@ -18322,7 +18302,7 @@
         <v>184</v>
       </c>
       <c r="B185" s="15" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C185" s="15" t="s">
         <v>150</v>
@@ -18344,7 +18324,7 @@
       <c r="N185" s="18"/>
       <c r="O185" s="18"/>
       <c r="P185" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="Q185" s="18"/>
     </row>
@@ -18353,7 +18333,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="15" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C186" s="15" t="s">
         <v>215</v>
@@ -18375,12 +18355,11 @@
       <c r="N186" s="18"/>
       <c r="O186" s="18"/>
       <c r="P186" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="Q186" s="18"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q186" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
+++ b/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dee/Downloads/tms/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dee/Desktop/GitHub- Repo/tms/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A2724AE-3709-DD4C-8F7F-5A02C5B5C04D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E0DE0F-385B-0B47-ADD6-2FC15F8108F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,6 +19,7 @@
     <sheet name="DB Target" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DB capacity'!$B$3:$F$201</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vehicle Database'!$A$1:$H$60</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -6274,7 +6275,7 @@
         <v>70</v>
       </c>
       <c r="F194" s="6">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="195" spans="2:6" x14ac:dyDescent="0.2">

--- a/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
+++ b/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dee/Desktop/GitHub- Repo/tms/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E0DE0F-385B-0B47-ADD6-2FC15F8108F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE8E41B-9176-BE42-9AB0-E4D035A9FFAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DB capacity" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1953" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1953" uniqueCount="732">
   <si>
     <t>S. N.</t>
   </si>
@@ -2233,6 +2233,9 @@
   </si>
   <si>
     <t>operational</t>
+  </si>
+  <si>
+    <t>Non Operational</t>
   </si>
 </sst>
 </file>
@@ -6531,7 +6534,7 @@
         <v>11</v>
       </c>
       <c r="H5" s="32" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -7422,7 +7425,7 @@
         <v>11</v>
       </c>
       <c r="H38" s="32" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
@@ -7854,7 +7857,7 @@
         <v>11</v>
       </c>
       <c r="H54" s="32" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
@@ -7881,7 +7884,7 @@
         <v>11</v>
       </c>
       <c r="H55" s="32" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">

--- a/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
+++ b/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dee/Desktop/GitHub- Repo/tms/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE8E41B-9176-BE42-9AB0-E4D035A9FFAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E90CDDFC-0831-BE4B-B482-32C2AC130979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7560,7 +7560,7 @@
         <v>11</v>
       </c>
       <c r="H43" s="32" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">

--- a/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
+++ b/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dee/Desktop/GitHub- Repo/tms/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E90CDDFC-0831-BE4B-B482-32C2AC130979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1A46AA9-DDB5-F448-A62E-73166AB26997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6714,7 +6714,7 @@
         <v>9</v>
       </c>
       <c r="E12" s="21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F12" s="21" t="s">
         <v>10</v>

--- a/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
+++ b/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dee/Desktop/GitHub- Repo/tms/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1A46AA9-DDB5-F448-A62E-73166AB26997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B087415-7EB7-0747-9746-CDB2E47BD445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DB capacity" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,8 @@
     <sheet name="DB Target" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DB capacity'!$B$3:$F$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DB capacity'!$B$3:$F$199</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DB Target'!$A$1:$Q$186</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vehicle Database'!$A$1:$H$60</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1953" uniqueCount="732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1952" uniqueCount="732">
   <si>
     <t>S. N.</t>
   </si>
@@ -1401,9 +1402,6 @@
     <t>R S Deals</t>
   </si>
   <si>
-    <t>Other's</t>
-  </si>
-  <si>
     <t>FRANCHISE</t>
   </si>
   <si>
@@ -2236,6 +2234,9 @@
   </si>
   <si>
     <t>Non Operational</t>
+  </si>
+  <si>
+    <t>GURU KRIPA BEVERAGES</t>
   </si>
 </sst>
 </file>
@@ -6367,9 +6368,7 @@
       </c>
     </row>
     <row r="200" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B200" s="5" t="s">
-        <v>453</v>
-      </c>
+      <c r="B200" s="5"/>
       <c r="C200" s="4"/>
       <c r="D200" s="6"/>
       <c r="E200" s="6"/>
@@ -6377,7 +6376,7 @@
     </row>
     <row r="201" spans="2:6" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B201" s="12" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C201" s="12"/>
       <c r="D201" s="13"/>
@@ -6427,7 +6426,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="19" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -6453,7 +6452,7 @@
         <v>11</v>
       </c>
       <c r="H2" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -6465,7 +6464,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D3" s="20" t="s">
         <v>9</v>
@@ -6480,7 +6479,7 @@
         <v>11</v>
       </c>
       <c r="H3" s="32" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -6492,7 +6491,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>9</v>
@@ -6507,7 +6506,7 @@
         <v>11</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -6534,7 +6533,7 @@
         <v>11</v>
       </c>
       <c r="H5" s="32" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -6561,7 +6560,7 @@
         <v>11</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -6588,7 +6587,7 @@
         <v>11</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -6615,7 +6614,7 @@
         <v>11</v>
       </c>
       <c r="H8" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -6642,7 +6641,7 @@
         <v>11</v>
       </c>
       <c r="H9" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -6669,7 +6668,7 @@
         <v>11</v>
       </c>
       <c r="H10" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -6696,7 +6695,7 @@
         <v>11</v>
       </c>
       <c r="H11" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -6723,7 +6722,7 @@
         <v>11</v>
       </c>
       <c r="H12" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -6750,7 +6749,7 @@
         <v>11</v>
       </c>
       <c r="H13" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -6777,7 +6776,7 @@
         <v>11</v>
       </c>
       <c r="H14" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -6804,7 +6803,7 @@
         <v>11</v>
       </c>
       <c r="H15" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -6831,7 +6830,7 @@
         <v>11</v>
       </c>
       <c r="H16" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
@@ -6858,7 +6857,7 @@
         <v>11</v>
       </c>
       <c r="H17" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -6885,7 +6884,7 @@
         <v>11</v>
       </c>
       <c r="H18" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -6912,7 +6911,7 @@
         <v>11</v>
       </c>
       <c r="H19" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -6939,7 +6938,7 @@
         <v>11</v>
       </c>
       <c r="H20" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
@@ -6966,7 +6965,7 @@
         <v>11</v>
       </c>
       <c r="H21" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
@@ -6993,7 +6992,7 @@
         <v>11</v>
       </c>
       <c r="H22" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
@@ -7020,7 +7019,7 @@
         <v>11</v>
       </c>
       <c r="H23" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
@@ -7047,7 +7046,7 @@
         <v>11</v>
       </c>
       <c r="H24" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
@@ -7074,7 +7073,7 @@
         <v>11</v>
       </c>
       <c r="H25" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
@@ -7101,7 +7100,7 @@
         <v>11</v>
       </c>
       <c r="H26" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -7128,7 +7127,7 @@
         <v>11</v>
       </c>
       <c r="H27" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
@@ -7155,7 +7154,7 @@
         <v>11</v>
       </c>
       <c r="H28" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
@@ -7182,7 +7181,7 @@
         <v>11</v>
       </c>
       <c r="H29" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
@@ -7209,7 +7208,7 @@
         <v>11</v>
       </c>
       <c r="H30" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -7236,7 +7235,7 @@
         <v>11</v>
       </c>
       <c r="H31" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
@@ -7263,7 +7262,7 @@
         <v>11</v>
       </c>
       <c r="H32" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
@@ -7290,7 +7289,7 @@
         <v>11</v>
       </c>
       <c r="H33" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
@@ -7302,7 +7301,7 @@
         <v>7</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D34" s="20" t="s">
         <v>9</v>
@@ -7317,7 +7316,7 @@
         <v>11</v>
       </c>
       <c r="H34" s="32" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
@@ -7344,7 +7343,7 @@
         <v>11</v>
       </c>
       <c r="H35" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
@@ -7371,7 +7370,7 @@
         <v>11</v>
       </c>
       <c r="H36" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -7398,7 +7397,7 @@
         <v>11</v>
       </c>
       <c r="H37" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
@@ -7425,7 +7424,7 @@
         <v>11</v>
       </c>
       <c r="H38" s="32" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
@@ -7452,7 +7451,7 @@
         <v>11</v>
       </c>
       <c r="H39" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
@@ -7479,7 +7478,7 @@
         <v>11</v>
       </c>
       <c r="H40" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
@@ -7491,7 +7490,7 @@
         <v>7</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D41" s="20" t="s">
         <v>9</v>
@@ -7506,7 +7505,7 @@
         <v>11</v>
       </c>
       <c r="H41" s="32" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
@@ -7533,7 +7532,7 @@
         <v>11</v>
       </c>
       <c r="H42" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
@@ -7560,7 +7559,7 @@
         <v>11</v>
       </c>
       <c r="H43" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
@@ -7587,7 +7586,7 @@
         <v>11</v>
       </c>
       <c r="H44" s="32" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
@@ -7599,7 +7598,7 @@
         <v>7</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D45" s="20" t="s">
         <v>9</v>
@@ -7614,7 +7613,7 @@
         <v>11</v>
       </c>
       <c r="H45" s="32" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
@@ -7641,7 +7640,7 @@
         <v>11</v>
       </c>
       <c r="H46" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
@@ -7668,7 +7667,7 @@
         <v>11</v>
       </c>
       <c r="H47" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
@@ -7695,7 +7694,7 @@
         <v>11</v>
       </c>
       <c r="H48" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
@@ -7722,7 +7721,7 @@
         <v>11</v>
       </c>
       <c r="H49" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
@@ -7734,7 +7733,7 @@
         <v>7</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D50" s="20" t="s">
         <v>9</v>
@@ -7749,7 +7748,7 @@
         <v>11</v>
       </c>
       <c r="H50" s="32" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
@@ -7776,7 +7775,7 @@
         <v>11</v>
       </c>
       <c r="H51" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
@@ -7803,7 +7802,7 @@
         <v>11</v>
       </c>
       <c r="H52" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
@@ -7830,7 +7829,7 @@
         <v>11</v>
       </c>
       <c r="H53" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
@@ -7857,7 +7856,7 @@
         <v>11</v>
       </c>
       <c r="H54" s="32" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
@@ -7884,7 +7883,7 @@
         <v>11</v>
       </c>
       <c r="H55" s="32" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
@@ -7896,7 +7895,7 @@
         <v>7</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D56" s="20" t="s">
         <v>9</v>
@@ -7911,7 +7910,7 @@
         <v>11</v>
       </c>
       <c r="H56" s="32" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
@@ -7938,7 +7937,7 @@
         <v>11</v>
       </c>
       <c r="H57" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
@@ -7950,7 +7949,7 @@
         <v>7</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D58" s="20" t="s">
         <v>9</v>
@@ -7965,7 +7964,7 @@
         <v>11</v>
       </c>
       <c r="H58" s="32" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
@@ -7992,7 +7991,7 @@
         <v>11</v>
       </c>
       <c r="H59" s="32" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
@@ -8019,7 +8018,7 @@
         <v>11</v>
       </c>
       <c r="H60" s="32" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
@@ -8548,15 +8547,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="27" t="s">
+        <v>454</v>
+      </c>
+      <c r="B1" s="28" t="s">
         <v>455</v>
-      </c>
-      <c r="B1" s="28" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="23" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B2" s="24">
         <v>1200</v>
@@ -8564,7 +8563,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B3">
         <v>1000</v>
@@ -8572,7 +8571,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="23" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B4" s="24">
         <v>800</v>
@@ -8580,7 +8579,7 @@
     </row>
     <row r="5" spans="1:2" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B5" s="24">
         <v>600</v>
@@ -8588,7 +8587,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="25" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B6" s="26">
         <v>350</v>
@@ -8596,34 +8595,34 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="29" t="s">
+        <v>461</v>
+      </c>
+      <c r="B12" s="29" t="s">
         <v>462</v>
-      </c>
-      <c r="B12" s="29" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="17" t="s">
+        <v>463</v>
+      </c>
+      <c r="B13" s="17" t="s">
         <v>464</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="17" t="s">
+        <v>465</v>
+      </c>
+      <c r="B14" s="17" t="s">
         <v>466</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="17" t="s">
+        <v>467</v>
+      </c>
+      <c r="B15" s="17" t="s">
         <v>468</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -8638,60 +8637,61 @@
   <cols>
     <col min="1" max="1" width="4.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
+        <v>469</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>470</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="C1" s="14" t="s">
         <v>471</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="D1" s="14" t="s">
         <v>472</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="E1" s="14" t="s">
         <v>473</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="F1" s="14" t="s">
         <v>474</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="G1" s="14" t="s">
         <v>475</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="H1" s="14" t="s">
         <v>476</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="I1" s="14" t="s">
         <v>477</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="J1" s="14" t="s">
         <v>478</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="K1" s="14" t="s">
         <v>479</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="L1" s="14" t="s">
         <v>480</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="M1" s="14" t="s">
         <v>481</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="N1" s="14" t="s">
         <v>482</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="O1" s="14" t="s">
         <v>483</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="P1" s="14" t="s">
         <v>484</v>
       </c>
-      <c r="P1" s="14" t="s">
+      <c r="Q1" s="14" t="s">
         <v>485</v>
-      </c>
-      <c r="Q1" s="14" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
@@ -8699,7 +8699,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>67</v>
@@ -8752,7 +8752,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>73</v>
@@ -8805,10 +8805,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>489</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>490</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>76</v>
@@ -8858,7 +8858,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>77</v>
@@ -8911,7 +8911,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>79</v>
@@ -8964,7 +8964,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>81</v>
@@ -9017,7 +9017,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>87</v>
@@ -9070,7 +9070,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>89</v>
@@ -9123,7 +9123,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>91</v>
@@ -9176,10 +9176,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="15" t="s">
+        <v>496</v>
+      </c>
+      <c r="C11" s="15" t="s">
         <v>497</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>498</v>
       </c>
       <c r="D11" s="15" t="s">
         <v>94</v>
@@ -9229,7 +9229,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>95</v>
@@ -9282,13 +9282,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>97</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E13" s="15" t="s">
         <v>69</v>
@@ -9335,7 +9335,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>99</v>
@@ -9388,7 +9388,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C15" s="15" t="s">
         <v>101</v>
@@ -9441,10 +9441,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="15" t="s">
+        <v>503</v>
+      </c>
+      <c r="C16" s="15" t="s">
         <v>504</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>505</v>
       </c>
       <c r="D16" s="15" t="s">
         <v>104</v>
@@ -9494,7 +9494,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>105</v>
@@ -9547,7 +9547,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C18" s="15" t="s">
         <v>107</v>
@@ -9600,13 +9600,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>111</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E19" s="15" t="s">
         <v>69</v>
@@ -9653,7 +9653,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C20" s="15" t="s">
         <v>113</v>
@@ -9706,7 +9706,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>115</v>
@@ -9759,7 +9759,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C22" s="15" t="s">
         <v>117</v>
@@ -9812,7 +9812,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>121</v>
@@ -9865,13 +9865,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C24" s="15" t="s">
         <v>123</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E24" s="15" t="s">
         <v>69</v>
@@ -9918,7 +9918,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C25" s="15" t="s">
         <v>128</v>
@@ -9971,7 +9971,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C26" s="15" t="s">
         <v>130</v>
@@ -10024,7 +10024,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C27" s="15" t="s">
         <v>134</v>
@@ -10077,7 +10077,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C28" s="15" t="s">
         <v>136</v>
@@ -10130,7 +10130,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>138</v>
@@ -10183,7 +10183,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>140</v>
@@ -10236,7 +10236,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C31" s="15" t="s">
         <v>142</v>
@@ -10289,7 +10289,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C32" s="15" t="s">
         <v>144</v>
@@ -10342,7 +10342,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>146</v>
@@ -10395,7 +10395,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C34" s="15" t="s">
         <v>152</v>
@@ -10448,7 +10448,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C35" s="15" t="s">
         <v>154</v>
@@ -10501,7 +10501,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C36" s="15" t="s">
         <v>156</v>
@@ -10554,7 +10554,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C37" s="15" t="s">
         <v>157</v>
@@ -10607,10 +10607,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="15" t="s">
+        <v>528</v>
+      </c>
+      <c r="C38" s="15" t="s">
         <v>529</v>
-      </c>
-      <c r="C38" s="15" t="s">
-        <v>530</v>
       </c>
       <c r="D38" s="15" t="s">
         <v>155</v>
@@ -10649,7 +10649,7 @@
         <v>9900</v>
       </c>
       <c r="P38" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="Q38" s="16">
         <v>6600</v>
@@ -10660,10 +10660,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="15" t="s">
+        <v>531</v>
+      </c>
+      <c r="C39" s="15" t="s">
         <v>532</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>533</v>
       </c>
       <c r="D39" s="15" t="s">
         <v>155</v>
@@ -10682,7 +10682,7 @@
       <c r="N39" s="18"/>
       <c r="O39" s="18"/>
       <c r="P39" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="Q39" s="18"/>
     </row>
@@ -10691,7 +10691,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C40" s="15" t="s">
         <v>166</v>
@@ -10744,7 +10744,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C41" s="15" t="s">
         <v>168</v>
@@ -10797,7 +10797,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C42" s="15" t="s">
         <v>171</v>
@@ -10850,7 +10850,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>173</v>
@@ -10903,7 +10903,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C44" s="15" t="s">
         <v>175</v>
@@ -10956,13 +10956,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="15" t="s">
+        <v>538</v>
+      </c>
+      <c r="C45" s="15" t="s">
         <v>539</v>
       </c>
-      <c r="C45" s="15" t="s">
+      <c r="D45" s="15" t="s">
         <v>540</v>
-      </c>
-      <c r="D45" s="15" t="s">
-        <v>541</v>
       </c>
       <c r="E45" s="15" t="s">
         <v>170</v>
@@ -11009,7 +11009,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C46" s="15" t="s">
         <v>177</v>
@@ -11062,7 +11062,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C47" s="15" t="s">
         <v>181</v>
@@ -11115,7 +11115,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C48" s="15" t="s">
         <v>182</v>
@@ -11168,7 +11168,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C49" s="15" t="s">
         <v>184</v>
@@ -11221,7 +11221,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C50" s="15" t="s">
         <v>186</v>
@@ -11274,7 +11274,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C51" s="15" t="s">
         <v>188</v>
@@ -11327,7 +11327,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C52" s="15" t="s">
         <v>190</v>
@@ -11380,7 +11380,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C53" s="15" t="s">
         <v>192</v>
@@ -11433,10 +11433,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="15" t="s">
+        <v>549</v>
+      </c>
+      <c r="C54" s="15" t="s">
         <v>550</v>
-      </c>
-      <c r="C54" s="15" t="s">
-        <v>551</v>
       </c>
       <c r="D54" s="15" t="s">
         <v>195</v>
@@ -11486,13 +11486,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="15" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C55" s="15" t="s">
         <v>196</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E55" s="15" t="s">
         <v>170</v>
@@ -11539,7 +11539,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="15" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C56" s="15" t="s">
         <v>198</v>
@@ -11592,7 +11592,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="15" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C57" s="15" t="s">
         <v>200</v>
@@ -11645,7 +11645,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C58" s="15" t="s">
         <v>202</v>
@@ -11698,7 +11698,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="15" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C59" s="15" t="s">
         <v>204</v>
@@ -11751,7 +11751,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C60" s="15" t="s">
         <v>206</v>
@@ -11804,13 +11804,13 @@
         <v>60</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C61" s="15" t="s">
         <v>209</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="E61" s="15" t="s">
         <v>170</v>
@@ -11833,7 +11833,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C62" s="15" t="s">
         <v>211</v>
@@ -11886,13 +11886,13 @@
         <v>62</v>
       </c>
       <c r="B63" s="15" t="s">
+        <v>561</v>
+      </c>
+      <c r="C63" s="15" t="s">
         <v>562</v>
       </c>
-      <c r="C63" s="15" t="s">
+      <c r="D63" s="15" t="s">
         <v>563</v>
-      </c>
-      <c r="D63" s="15" t="s">
-        <v>564</v>
       </c>
       <c r="E63" s="15" t="s">
         <v>170</v>
@@ -11939,16 +11939,16 @@
         <v>63</v>
       </c>
       <c r="B64" s="15" t="s">
+        <v>564</v>
+      </c>
+      <c r="C64" s="15" t="s">
         <v>565</v>
       </c>
-      <c r="C64" s="15" t="s">
+      <c r="D64" s="15" t="s">
         <v>566</v>
       </c>
-      <c r="D64" s="15" t="s">
+      <c r="E64" s="15" t="s">
         <v>567</v>
-      </c>
-      <c r="E64" s="15" t="s">
-        <v>568</v>
       </c>
       <c r="F64" s="16">
         <v>6000</v>
@@ -11992,7 +11992,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C65" s="15" t="s">
         <v>216</v>
@@ -12021,7 +12021,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C66" s="15" t="s">
         <v>219</v>
@@ -12030,7 +12030,7 @@
         <v>220</v>
       </c>
       <c r="E66" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F66" s="16">
         <v>3100</v>
@@ -12074,7 +12074,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C67" s="15" t="s">
         <v>221</v>
@@ -12083,7 +12083,7 @@
         <v>222</v>
       </c>
       <c r="E67" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F67" s="16">
         <v>15000</v>
@@ -12127,7 +12127,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C68" s="15" t="s">
         <v>223</v>
@@ -12136,7 +12136,7 @@
         <v>224</v>
       </c>
       <c r="E68" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F68" s="16">
         <v>6300</v>
@@ -12180,7 +12180,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C69" s="15" t="s">
         <v>225</v>
@@ -12189,7 +12189,7 @@
         <v>226</v>
       </c>
       <c r="E69" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F69" s="16">
         <v>5400</v>
@@ -12233,16 +12233,16 @@
         <v>69</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C70" s="15" t="s">
         <v>227</v>
       </c>
       <c r="D70" s="15" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F70" s="16">
         <v>10000</v>
@@ -12286,7 +12286,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="15" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C71" s="15" t="s">
         <v>229</v>
@@ -12295,7 +12295,7 @@
         <v>230</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F71" s="16">
         <v>4700</v>
@@ -12339,7 +12339,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C72" s="15" t="s">
         <v>231</v>
@@ -12348,7 +12348,7 @@
         <v>232</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F72" s="16">
         <v>6300</v>
@@ -12392,7 +12392,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="15" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C73" s="15" t="s">
         <v>233</v>
@@ -12401,7 +12401,7 @@
         <v>234</v>
       </c>
       <c r="E73" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F73" s="16">
         <v>5000</v>
@@ -12445,7 +12445,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="15" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C74" s="15" t="s">
         <v>235</v>
@@ -12454,7 +12454,7 @@
         <v>236</v>
       </c>
       <c r="E74" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F74" s="16">
         <v>1400</v>
@@ -12498,7 +12498,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="15" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C75" s="15" t="s">
         <v>237</v>
@@ -12507,7 +12507,7 @@
         <v>238</v>
       </c>
       <c r="E75" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F75" s="16">
         <v>5000</v>
@@ -12551,16 +12551,16 @@
         <v>75</v>
       </c>
       <c r="B76" s="15" t="s">
+        <v>580</v>
+      </c>
+      <c r="C76" s="15" t="s">
         <v>581</v>
       </c>
-      <c r="C76" s="15" t="s">
+      <c r="D76" s="15" t="s">
         <v>582</v>
       </c>
-      <c r="D76" s="15" t="s">
-        <v>583</v>
-      </c>
       <c r="E76" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F76" s="16">
         <v>7000</v>
@@ -12604,7 +12604,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="15" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C77" s="15" t="s">
         <v>105</v>
@@ -12613,7 +12613,7 @@
         <v>241</v>
       </c>
       <c r="E77" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F77" s="16">
         <v>5900</v>
@@ -12657,7 +12657,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="15" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C78" s="15" t="s">
         <v>242</v>
@@ -12666,7 +12666,7 @@
         <v>243</v>
       </c>
       <c r="E78" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F78" s="16">
         <v>6400</v>
@@ -12710,16 +12710,16 @@
         <v>78</v>
       </c>
       <c r="B79" s="15" t="s">
+        <v>585</v>
+      </c>
+      <c r="C79" s="15" t="s">
         <v>586</v>
-      </c>
-      <c r="C79" s="15" t="s">
-        <v>587</v>
       </c>
       <c r="D79" s="15" t="s">
         <v>245</v>
       </c>
       <c r="E79" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F79" s="16">
         <v>8000</v>
@@ -12763,16 +12763,16 @@
         <v>79</v>
       </c>
       <c r="B80" s="15" t="s">
+        <v>587</v>
+      </c>
+      <c r="C80" s="15" t="s">
         <v>588</v>
-      </c>
-      <c r="C80" s="15" t="s">
-        <v>589</v>
       </c>
       <c r="D80" s="15" t="s">
         <v>247</v>
       </c>
       <c r="E80" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F80" s="16">
         <v>5800</v>
@@ -12816,16 +12816,16 @@
         <v>80</v>
       </c>
       <c r="B81" s="15" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C81" s="15" t="s">
         <v>248</v>
       </c>
       <c r="D81" s="15" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E81" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F81" s="16">
         <v>11000</v>
@@ -12869,7 +12869,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="15" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C82" s="15" t="s">
         <v>250</v>
@@ -12878,7 +12878,7 @@
         <v>251</v>
       </c>
       <c r="E82" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F82" s="16">
         <v>4900</v>
@@ -12922,7 +12922,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="15" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C83" s="15" t="s">
         <v>252</v>
@@ -12931,7 +12931,7 @@
         <v>253</v>
       </c>
       <c r="E83" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F83" s="16">
         <v>5100</v>
@@ -12975,7 +12975,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="15" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C84" s="15" t="s">
         <v>254</v>
@@ -12984,7 +12984,7 @@
         <v>255</v>
       </c>
       <c r="E84" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F84" s="16">
         <v>2800</v>
@@ -13028,16 +13028,16 @@
         <v>84</v>
       </c>
       <c r="B85" s="15" t="s">
+        <v>594</v>
+      </c>
+      <c r="C85" s="15" t="s">
         <v>595</v>
-      </c>
-      <c r="C85" s="15" t="s">
-        <v>596</v>
       </c>
       <c r="D85" s="15" t="s">
         <v>257</v>
       </c>
       <c r="E85" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F85" s="16">
         <v>5900</v>
@@ -13081,16 +13081,16 @@
         <v>85</v>
       </c>
       <c r="B86" s="15" t="s">
+        <v>596</v>
+      </c>
+      <c r="C86" s="15" t="s">
         <v>597</v>
-      </c>
-      <c r="C86" s="15" t="s">
-        <v>598</v>
       </c>
       <c r="D86" s="15" t="s">
         <v>259</v>
       </c>
       <c r="E86" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F86" s="16">
         <v>5000</v>
@@ -13134,7 +13134,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="15" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C87" s="15" t="s">
         <v>260</v>
@@ -13143,7 +13143,7 @@
         <v>261</v>
       </c>
       <c r="E87" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F87" s="16">
         <v>8000</v>
@@ -13187,7 +13187,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C88" s="15" t="s">
         <v>262</v>
@@ -13196,7 +13196,7 @@
         <v>263</v>
       </c>
       <c r="E88" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F88" s="16">
         <v>2900</v>
@@ -13240,7 +13240,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="15" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C89" s="15" t="s">
         <v>264</v>
@@ -13293,7 +13293,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="15" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C90" s="15" t="s">
         <v>266</v>
@@ -13305,40 +13305,40 @@
         <v>265</v>
       </c>
       <c r="F90" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="G90" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H90" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I90" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="J90" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="K90" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="L90" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="M90" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="N90" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="O90" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="P90" s="16">
         <v>1600</v>
       </c>
       <c r="Q90" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.2">
@@ -13346,7 +13346,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="15" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C91" s="15" t="s">
         <v>268</v>
@@ -13399,7 +13399,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C92" s="15" t="s">
         <v>270</v>
@@ -13452,7 +13452,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="15" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C93" s="15" t="s">
         <v>272</v>
@@ -13505,7 +13505,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="15" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C94" s="15" t="s">
         <v>274</v>
@@ -13558,7 +13558,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="15" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C95" s="15" t="s">
         <v>276</v>
@@ -13611,7 +13611,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="15" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C96" s="15" t="s">
         <v>278</v>
@@ -13664,13 +13664,13 @@
         <v>96</v>
       </c>
       <c r="B97" s="15" t="s">
+        <v>608</v>
+      </c>
+      <c r="C97" s="15" t="s">
         <v>609</v>
       </c>
-      <c r="C97" s="15" t="s">
+      <c r="D97" s="15" t="s">
         <v>610</v>
-      </c>
-      <c r="D97" s="15" t="s">
-        <v>611</v>
       </c>
       <c r="E97" s="15" t="s">
         <v>265</v>
@@ -13717,7 +13717,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="15" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C98" s="15" t="s">
         <v>280</v>
@@ -13770,7 +13770,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="15" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C99" s="15" t="s">
         <v>282</v>
@@ -13823,7 +13823,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="15" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C100" s="15" t="s">
         <v>284</v>
@@ -13876,7 +13876,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="15" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C101" s="15" t="s">
         <v>286</v>
@@ -13929,10 +13929,10 @@
         <v>101</v>
       </c>
       <c r="B102" s="15" t="s">
+        <v>615</v>
+      </c>
+      <c r="C102" s="15" t="s">
         <v>616</v>
-      </c>
-      <c r="C102" s="15" t="s">
-        <v>617</v>
       </c>
       <c r="D102" s="15" t="s">
         <v>289</v>
@@ -13982,7 +13982,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="15" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C103" s="15" t="s">
         <v>290</v>
@@ -14035,7 +14035,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="15" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C104" s="15" t="s">
         <v>292</v>
@@ -14088,7 +14088,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="15" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C105" s="15" t="s">
         <v>294</v>
@@ -14141,7 +14141,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="15" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C106" s="15" t="s">
         <v>296</v>
@@ -14194,7 +14194,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C107" s="15" t="s">
         <v>298</v>
@@ -14247,7 +14247,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="15" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C108" s="15" t="s">
         <v>300</v>
@@ -14300,7 +14300,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="15" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C109" s="15" t="s">
         <v>302</v>
@@ -14353,7 +14353,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="15" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C110" s="15" t="s">
         <v>304</v>
@@ -14406,7 +14406,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="15" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C111" s="15" t="s">
         <v>308</v>
@@ -14459,7 +14459,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="15" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C112" s="15" t="s">
         <v>310</v>
@@ -14512,7 +14512,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="15" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C113" s="15" t="s">
         <v>312</v>
@@ -14565,7 +14565,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="15" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C114" s="15" t="s">
         <v>314</v>
@@ -14618,7 +14618,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="15" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C115" s="15" t="s">
         <v>316</v>
@@ -14671,7 +14671,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="15" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C116" s="15" t="s">
         <v>318</v>
@@ -14724,7 +14724,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="15" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C117" s="15" t="s">
         <v>320</v>
@@ -14777,7 +14777,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="15" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C118" s="15" t="s">
         <v>322</v>
@@ -14830,7 +14830,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="15" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C119" s="15" t="s">
         <v>325</v>
@@ -14883,7 +14883,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="15" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C120" s="15" t="s">
         <v>327</v>
@@ -14936,7 +14936,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="15" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C121" s="15" t="s">
         <v>329</v>
@@ -14989,7 +14989,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="15" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C122" s="15" t="s">
         <v>331</v>
@@ -15042,7 +15042,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="15" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C123" s="15" t="s">
         <v>333</v>
@@ -15095,7 +15095,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="15" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C124" s="15" t="s">
         <v>335</v>
@@ -15148,7 +15148,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="15" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C125" s="15" t="s">
         <v>337</v>
@@ -15201,7 +15201,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="15" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C126" s="15" t="s">
         <v>339</v>
@@ -15254,7 +15254,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="15" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C127" s="15" t="s">
         <v>340</v>
@@ -15307,7 +15307,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="15" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C128" s="15" t="s">
         <v>342</v>
@@ -15360,7 +15360,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="15" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C129" s="15" t="s">
         <v>344</v>
@@ -15413,7 +15413,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="15" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C130" s="15" t="s">
         <v>346</v>
@@ -15466,7 +15466,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="15" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C131" s="15" t="s">
         <v>349</v>
@@ -15519,7 +15519,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="15" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C132" s="15" t="s">
         <v>351</v>
@@ -15572,7 +15572,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="15" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C133" s="15" t="s">
         <v>354</v>
@@ -15625,7 +15625,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="15" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C134" s="15" t="s">
         <v>356</v>
@@ -15678,7 +15678,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="15" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C135" s="15" t="s">
         <v>358</v>
@@ -15731,7 +15731,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="15" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C136" s="15" t="s">
         <v>360</v>
@@ -15784,7 +15784,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="15" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C137" s="15" t="s">
         <v>362</v>
@@ -15837,7 +15837,7 @@
         <v>137</v>
       </c>
       <c r="B138" s="15" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C138" s="15" t="s">
         <v>364</v>
@@ -15890,7 +15890,7 @@
         <v>138</v>
       </c>
       <c r="B139" s="15" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C139" s="15" t="s">
         <v>366</v>
@@ -15943,7 +15943,7 @@
         <v>139</v>
       </c>
       <c r="B140" s="15" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C140" s="15" t="s">
         <v>368</v>
@@ -15996,7 +15996,7 @@
         <v>140</v>
       </c>
       <c r="B141" s="15" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C141" s="15" t="s">
         <v>370</v>
@@ -16049,13 +16049,13 @@
         <v>141</v>
       </c>
       <c r="B142" s="15" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C142" s="15" t="s">
         <v>372</v>
       </c>
       <c r="D142" s="15" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E142" s="15" t="s">
         <v>324</v>
@@ -16102,10 +16102,10 @@
         <v>142</v>
       </c>
       <c r="B143" s="15" t="s">
+        <v>658</v>
+      </c>
+      <c r="C143" s="15" t="s">
         <v>659</v>
-      </c>
-      <c r="C143" s="15" t="s">
-        <v>660</v>
       </c>
       <c r="D143" s="15" t="s">
         <v>375</v>
@@ -16155,7 +16155,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="15" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C144" s="15" t="s">
         <v>378</v>
@@ -16208,7 +16208,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="15" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C145" s="15" t="s">
         <v>380</v>
@@ -16261,13 +16261,13 @@
         <v>145</v>
       </c>
       <c r="B146" s="15" t="s">
+        <v>662</v>
+      </c>
+      <c r="C146" s="15" t="s">
         <v>663</v>
       </c>
-      <c r="C146" s="15" t="s">
+      <c r="D146" s="15" t="s">
         <v>664</v>
-      </c>
-      <c r="D146" s="15" t="s">
-        <v>665</v>
       </c>
       <c r="E146" s="15" t="s">
         <v>162</v>
@@ -16314,13 +16314,13 @@
         <v>146</v>
       </c>
       <c r="B147" s="15" t="s">
+        <v>665</v>
+      </c>
+      <c r="C147" s="15" t="s">
         <v>666</v>
       </c>
-      <c r="C147" s="15" t="s">
+      <c r="D147" s="15" t="s">
         <v>667</v>
-      </c>
-      <c r="D147" s="15" t="s">
-        <v>668</v>
       </c>
       <c r="E147" s="15" t="s">
         <v>162</v>
@@ -16367,7 +16367,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="15" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C148" s="15" t="s">
         <v>385</v>
@@ -16420,7 +16420,7 @@
         <v>148</v>
       </c>
       <c r="B149" s="15" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C149" s="15" t="s">
         <v>160</v>
@@ -16473,13 +16473,13 @@
         <v>149</v>
       </c>
       <c r="B150" s="15" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C150" s="15" t="s">
         <v>387</v>
       </c>
       <c r="D150" s="15" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E150" s="15" t="s">
         <v>162</v>
@@ -16526,7 +16526,7 @@
         <v>150</v>
       </c>
       <c r="B151" s="15" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C151" s="15" t="s">
         <v>389</v>
@@ -16579,7 +16579,7 @@
         <v>151</v>
       </c>
       <c r="B152" s="15" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C152" s="15" t="s">
         <v>391</v>
@@ -16632,52 +16632,52 @@
         <v>152</v>
       </c>
       <c r="B153" s="15" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C153" s="15" t="s">
         <v>393</v>
       </c>
       <c r="D153" s="15" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E153" s="15" t="s">
         <v>162</v>
       </c>
       <c r="F153" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="G153" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H153" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I153" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="J153" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="K153" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="L153" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="M153" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="N153" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="O153" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="P153" s="15">
         <v>300</v>
       </c>
       <c r="Q153" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.2">
@@ -16685,7 +16685,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="15" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C154" s="15" t="s">
         <v>395</v>
@@ -16738,10 +16738,10 @@
         <v>154</v>
       </c>
       <c r="B155" s="15" t="s">
+        <v>677</v>
+      </c>
+      <c r="C155" s="15" t="s">
         <v>678</v>
-      </c>
-      <c r="C155" s="15" t="s">
-        <v>679</v>
       </c>
       <c r="D155" s="15" t="s">
         <v>397</v>
@@ -16791,13 +16791,13 @@
         <v>155</v>
       </c>
       <c r="B156" s="15" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C156" s="15" t="s">
         <v>398</v>
       </c>
       <c r="D156" s="15" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E156" s="15" t="s">
         <v>162</v>
@@ -16844,7 +16844,7 @@
         <v>156</v>
       </c>
       <c r="B157" s="15" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C157" s="15" t="s">
         <v>400</v>
@@ -16897,7 +16897,7 @@
         <v>157</v>
       </c>
       <c r="B158" s="15" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C158" s="15" t="s">
         <v>402</v>
@@ -16950,10 +16950,10 @@
         <v>158</v>
       </c>
       <c r="B159" s="15" t="s">
+        <v>683</v>
+      </c>
+      <c r="C159" s="15" t="s">
         <v>684</v>
-      </c>
-      <c r="C159" s="15" t="s">
-        <v>685</v>
       </c>
       <c r="D159" s="15" t="s">
         <v>405</v>
@@ -17003,7 +17003,7 @@
         <v>159</v>
       </c>
       <c r="B160" s="15" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C160" s="15" t="s">
         <v>406</v>
@@ -17056,7 +17056,7 @@
         <v>160</v>
       </c>
       <c r="B161" s="15" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C161" s="15" t="s">
         <v>408</v>
@@ -17109,7 +17109,7 @@
         <v>161</v>
       </c>
       <c r="B162" s="15" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C162" s="15" t="s">
         <v>410</v>
@@ -17162,10 +17162,10 @@
         <v>162</v>
       </c>
       <c r="B163" s="15" t="s">
+        <v>688</v>
+      </c>
+      <c r="C163" s="15" t="s">
         <v>689</v>
-      </c>
-      <c r="C163" s="15" t="s">
-        <v>690</v>
       </c>
       <c r="D163" s="15" t="s">
         <v>413</v>
@@ -17215,13 +17215,13 @@
         <v>163</v>
       </c>
       <c r="B164" s="15" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C164" s="15" t="s">
         <v>414</v>
       </c>
       <c r="D164" s="15" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E164" s="15" t="s">
         <v>162</v>
@@ -17268,13 +17268,13 @@
         <v>164</v>
       </c>
       <c r="B165" s="15" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C165" s="15" t="s">
         <v>416</v>
       </c>
       <c r="D165" s="15" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E165" s="15" t="s">
         <v>162</v>
@@ -17321,7 +17321,7 @@
         <v>165</v>
       </c>
       <c r="B166" s="15" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C166" s="15" t="s">
         <v>418</v>
@@ -17374,10 +17374,10 @@
         <v>166</v>
       </c>
       <c r="B167" s="15" t="s">
+        <v>695</v>
+      </c>
+      <c r="C167" s="15" t="s">
         <v>696</v>
-      </c>
-      <c r="C167" s="15" t="s">
-        <v>697</v>
       </c>
       <c r="D167" s="15" t="s">
         <v>421</v>
@@ -17427,7 +17427,7 @@
         <v>167</v>
       </c>
       <c r="B168" s="15" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C168" s="15" t="s">
         <v>422</v>
@@ -17480,10 +17480,10 @@
         <v>168</v>
       </c>
       <c r="B169" s="15" t="s">
+        <v>698</v>
+      </c>
+      <c r="C169" s="15" t="s">
         <v>699</v>
-      </c>
-      <c r="C169" s="15" t="s">
-        <v>700</v>
       </c>
       <c r="D169" s="15" t="s">
         <v>425</v>
@@ -17533,7 +17533,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="15" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C170" s="15" t="s">
         <v>166</v>
@@ -17586,7 +17586,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="15" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C171" s="15" t="s">
         <v>427</v>
@@ -17639,7 +17639,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="15" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C172" s="15" t="s">
         <v>429</v>
@@ -17692,7 +17692,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="15" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C173" s="15" t="s">
         <v>431</v>
@@ -17745,7 +17745,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="15" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C174" s="15" t="s">
         <v>433</v>
@@ -17798,7 +17798,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="15" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C175" s="15" t="s">
         <v>437</v>
@@ -17851,10 +17851,10 @@
         <v>175</v>
       </c>
       <c r="B176" s="15" t="s">
+        <v>706</v>
+      </c>
+      <c r="C176" s="15" t="s">
         <v>707</v>
-      </c>
-      <c r="C176" s="15" t="s">
-        <v>708</v>
       </c>
       <c r="D176" s="15" t="s">
         <v>440</v>
@@ -17904,7 +17904,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="15" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C177" s="15" t="s">
         <v>441</v>
@@ -17957,7 +17957,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="15" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C178" s="15" t="s">
         <v>95</v>
@@ -18010,7 +18010,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="15" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C179" s="15" t="s">
         <v>444</v>
@@ -18063,7 +18063,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="15" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C180" s="15" t="s">
         <v>446</v>
@@ -18096,7 +18096,7 @@
         <v>500</v>
       </c>
       <c r="M180" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="N180" s="15">
         <v>400</v>
@@ -18116,7 +18116,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="15" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C181" s="15" t="s">
         <v>448</v>
@@ -18169,7 +18169,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="15" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C182" s="15" t="s">
         <v>450</v>
@@ -18222,7 +18222,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="15" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C183" s="15" t="s">
         <v>452</v>
@@ -18275,10 +18275,10 @@
         <v>183</v>
       </c>
       <c r="B184" s="15" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C184" s="15" t="s">
-        <v>148</v>
+        <v>731</v>
       </c>
       <c r="D184" s="15" t="s">
         <v>149</v>
@@ -18297,7 +18297,7 @@
       <c r="N184" s="18"/>
       <c r="O184" s="18"/>
       <c r="P184" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="Q184" s="18"/>
     </row>
@@ -18306,10 +18306,10 @@
         <v>184</v>
       </c>
       <c r="B185" s="15" t="s">
-        <v>717</v>
-      </c>
-      <c r="C185" s="15" t="s">
-        <v>150</v>
+        <v>716</v>
+      </c>
+      <c r="C185" s="5" t="s">
+        <v>132</v>
       </c>
       <c r="D185" s="15" t="s">
         <v>151</v>
@@ -18328,7 +18328,7 @@
       <c r="N185" s="18"/>
       <c r="O185" s="18"/>
       <c r="P185" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="Q185" s="18"/>
     </row>
@@ -18337,7 +18337,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="15" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C186" s="15" t="s">
         <v>215</v>
@@ -18359,7 +18359,7 @@
       <c r="N186" s="18"/>
       <c r="O186" s="18"/>
       <c r="P186" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="Q186" s="18"/>
     </row>

--- a/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
+++ b/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dee/Desktop/GitHub- Repo/tms/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B087415-7EB7-0747-9746-CDB2E47BD445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EDB8DA0-9EAD-CB46-9B97-A0DA452595A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DB capacity" sheetId="1" r:id="rId1"/>

--- a/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
+++ b/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dee/Desktop/GitHub- Repo/tms/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EDB8DA0-9EAD-CB46-9B97-A0DA452595A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EFCED16-3A68-2546-B5B2-BCD3452CEBDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,8 +19,6 @@
     <sheet name="DB Target" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DB capacity'!$B$3:$F$199</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DB Target'!$A$1:$Q$186</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vehicle Database'!$A$1:$H$60</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -41,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1952" uniqueCount="732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1953" uniqueCount="731">
   <si>
     <t>S. N.</t>
   </si>
@@ -1402,6 +1400,9 @@
     <t>R S Deals</t>
   </si>
   <si>
+    <t>Other's</t>
+  </si>
+  <si>
     <t>FRANCHISE</t>
   </si>
   <si>
@@ -2231,12 +2232,6 @@
   </si>
   <si>
     <t>operational</t>
-  </si>
-  <si>
-    <t>Non Operational</t>
-  </si>
-  <si>
-    <t>GURU KRIPA BEVERAGES</t>
   </si>
 </sst>
 </file>
@@ -6279,7 +6274,7 @@
         <v>70</v>
       </c>
       <c r="F194" s="6">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="195" spans="2:6" x14ac:dyDescent="0.2">
@@ -6368,7 +6363,9 @@
       </c>
     </row>
     <row r="200" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B200" s="5"/>
+      <c r="B200" s="5" t="s">
+        <v>453</v>
+      </c>
       <c r="C200" s="4"/>
       <c r="D200" s="6"/>
       <c r="E200" s="6"/>
@@ -6376,7 +6373,7 @@
     </row>
     <row r="201" spans="2:6" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B201" s="12" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C201" s="12"/>
       <c r="D201" s="13"/>
@@ -6426,7 +6423,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="19" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -6452,7 +6449,7 @@
         <v>11</v>
       </c>
       <c r="H2" s="32" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -6464,7 +6461,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D3" s="20" t="s">
         <v>9</v>
@@ -6479,7 +6476,7 @@
         <v>11</v>
       </c>
       <c r="H3" s="32" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -6491,7 +6488,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>9</v>
@@ -6506,7 +6503,7 @@
         <v>11</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -6533,7 +6530,7 @@
         <v>11</v>
       </c>
       <c r="H5" s="32" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -6560,7 +6557,7 @@
         <v>11</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -6587,7 +6584,7 @@
         <v>11</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -6614,7 +6611,7 @@
         <v>11</v>
       </c>
       <c r="H8" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -6641,7 +6638,7 @@
         <v>11</v>
       </c>
       <c r="H9" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -6668,7 +6665,7 @@
         <v>11</v>
       </c>
       <c r="H10" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -6695,7 +6692,7 @@
         <v>11</v>
       </c>
       <c r="H11" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -6713,7 +6710,7 @@
         <v>9</v>
       </c>
       <c r="E12" s="21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F12" s="21" t="s">
         <v>10</v>
@@ -6722,7 +6719,7 @@
         <v>11</v>
       </c>
       <c r="H12" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -6749,7 +6746,7 @@
         <v>11</v>
       </c>
       <c r="H13" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -6776,7 +6773,7 @@
         <v>11</v>
       </c>
       <c r="H14" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -6803,7 +6800,7 @@
         <v>11</v>
       </c>
       <c r="H15" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -6830,7 +6827,7 @@
         <v>11</v>
       </c>
       <c r="H16" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
@@ -6857,7 +6854,7 @@
         <v>11</v>
       </c>
       <c r="H17" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -6884,7 +6881,7 @@
         <v>11</v>
       </c>
       <c r="H18" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -6911,7 +6908,7 @@
         <v>11</v>
       </c>
       <c r="H19" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -6938,7 +6935,7 @@
         <v>11</v>
       </c>
       <c r="H20" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
@@ -6965,7 +6962,7 @@
         <v>11</v>
       </c>
       <c r="H21" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
@@ -6992,7 +6989,7 @@
         <v>11</v>
       </c>
       <c r="H22" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
@@ -7019,7 +7016,7 @@
         <v>11</v>
       </c>
       <c r="H23" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
@@ -7046,7 +7043,7 @@
         <v>11</v>
       </c>
       <c r="H24" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
@@ -7073,7 +7070,7 @@
         <v>11</v>
       </c>
       <c r="H25" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
@@ -7100,7 +7097,7 @@
         <v>11</v>
       </c>
       <c r="H26" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -7127,7 +7124,7 @@
         <v>11</v>
       </c>
       <c r="H27" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
@@ -7154,7 +7151,7 @@
         <v>11</v>
       </c>
       <c r="H28" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
@@ -7181,7 +7178,7 @@
         <v>11</v>
       </c>
       <c r="H29" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
@@ -7208,7 +7205,7 @@
         <v>11</v>
       </c>
       <c r="H30" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -7235,7 +7232,7 @@
         <v>11</v>
       </c>
       <c r="H31" s="32" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
@@ -7262,7 +7259,7 @@
         <v>11</v>
       </c>
       <c r="H32" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
@@ -7289,7 +7286,7 @@
         <v>11</v>
       </c>
       <c r="H33" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
@@ -7301,7 +7298,7 @@
         <v>7</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D34" s="20" t="s">
         <v>9</v>
@@ -7316,7 +7313,7 @@
         <v>11</v>
       </c>
       <c r="H34" s="32" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
@@ -7343,7 +7340,7 @@
         <v>11</v>
       </c>
       <c r="H35" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
@@ -7370,7 +7367,7 @@
         <v>11</v>
       </c>
       <c r="H36" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -7397,7 +7394,7 @@
         <v>11</v>
       </c>
       <c r="H37" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
@@ -7451,7 +7448,7 @@
         <v>11</v>
       </c>
       <c r="H39" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
@@ -7478,7 +7475,7 @@
         <v>11</v>
       </c>
       <c r="H40" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
@@ -7490,7 +7487,7 @@
         <v>7</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="D41" s="20" t="s">
         <v>9</v>
@@ -7505,7 +7502,7 @@
         <v>11</v>
       </c>
       <c r="H41" s="32" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
@@ -7532,7 +7529,7 @@
         <v>11</v>
       </c>
       <c r="H42" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
@@ -7559,7 +7556,7 @@
         <v>11</v>
       </c>
       <c r="H43" s="32" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
@@ -7586,7 +7583,7 @@
         <v>11</v>
       </c>
       <c r="H44" s="32" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
@@ -7598,7 +7595,7 @@
         <v>7</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D45" s="20" t="s">
         <v>9</v>
@@ -7613,7 +7610,7 @@
         <v>11</v>
       </c>
       <c r="H45" s="32" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
@@ -7640,7 +7637,7 @@
         <v>11</v>
       </c>
       <c r="H46" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
@@ -7667,7 +7664,7 @@
         <v>11</v>
       </c>
       <c r="H47" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
@@ -7694,7 +7691,7 @@
         <v>11</v>
       </c>
       <c r="H48" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
@@ -7721,7 +7718,7 @@
         <v>11</v>
       </c>
       <c r="H49" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
@@ -7733,7 +7730,7 @@
         <v>7</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="D50" s="20" t="s">
         <v>9</v>
@@ -7748,7 +7745,7 @@
         <v>11</v>
       </c>
       <c r="H50" s="32" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
@@ -7775,7 +7772,7 @@
         <v>11</v>
       </c>
       <c r="H51" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
@@ -7802,7 +7799,7 @@
         <v>11</v>
       </c>
       <c r="H52" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
@@ -7829,7 +7826,7 @@
         <v>11</v>
       </c>
       <c r="H53" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
@@ -7883,7 +7880,7 @@
         <v>11</v>
       </c>
       <c r="H55" s="32" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
@@ -7895,7 +7892,7 @@
         <v>7</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D56" s="20" t="s">
         <v>9</v>
@@ -7910,7 +7907,7 @@
         <v>11</v>
       </c>
       <c r="H56" s="32" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
@@ -7937,7 +7934,7 @@
         <v>11</v>
       </c>
       <c r="H57" s="32" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
@@ -7949,7 +7946,7 @@
         <v>7</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D58" s="20" t="s">
         <v>9</v>
@@ -7964,7 +7961,7 @@
         <v>11</v>
       </c>
       <c r="H58" s="32" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
@@ -7991,7 +7988,7 @@
         <v>11</v>
       </c>
       <c r="H59" s="32" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
@@ -8018,7 +8015,7 @@
         <v>11</v>
       </c>
       <c r="H60" s="32" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
@@ -8547,15 +8544,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="27" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="23" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B2" s="24">
         <v>1200</v>
@@ -8563,7 +8560,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B3">
         <v>1000</v>
@@ -8571,7 +8568,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B4" s="24">
         <v>800</v>
@@ -8579,7 +8576,7 @@
     </row>
     <row r="5" spans="1:2" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B5" s="24">
         <v>600</v>
@@ -8587,7 +8584,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="25" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B6" s="26">
         <v>350</v>
@@ -8595,34 +8592,34 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="29" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="17" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="17" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="17" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -8637,61 +8634,60 @@
   <cols>
     <col min="1" max="1" width="4.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="P1" s="14" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="Q1" s="14" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
@@ -8699,7 +8695,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>67</v>
@@ -8752,7 +8748,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>73</v>
@@ -8805,10 +8801,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>76</v>
@@ -8858,7 +8854,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>77</v>
@@ -8911,7 +8907,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>79</v>
@@ -8964,7 +8960,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>81</v>
@@ -9017,7 +9013,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>87</v>
@@ -9070,7 +9066,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>89</v>
@@ -9123,7 +9119,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>91</v>
@@ -9176,10 +9172,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D11" s="15" t="s">
         <v>94</v>
@@ -9229,7 +9225,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>95</v>
@@ -9282,13 +9278,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>97</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E13" s="15" t="s">
         <v>69</v>
@@ -9335,7 +9331,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>99</v>
@@ -9388,7 +9384,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C15" s="15" t="s">
         <v>101</v>
@@ -9441,10 +9437,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D16" s="15" t="s">
         <v>104</v>
@@ -9494,7 +9490,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>105</v>
@@ -9547,7 +9543,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C18" s="15" t="s">
         <v>107</v>
@@ -9600,13 +9596,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>111</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E19" s="15" t="s">
         <v>69</v>
@@ -9653,7 +9649,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C20" s="15" t="s">
         <v>113</v>
@@ -9706,7 +9702,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>115</v>
@@ -9759,7 +9755,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C22" s="15" t="s">
         <v>117</v>
@@ -9812,7 +9808,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>121</v>
@@ -9865,13 +9861,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C24" s="15" t="s">
         <v>123</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E24" s="15" t="s">
         <v>69</v>
@@ -9918,7 +9914,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C25" s="15" t="s">
         <v>128</v>
@@ -9971,7 +9967,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C26" s="15" t="s">
         <v>130</v>
@@ -10024,7 +10020,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C27" s="15" t="s">
         <v>134</v>
@@ -10077,7 +10073,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C28" s="15" t="s">
         <v>136</v>
@@ -10130,7 +10126,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>138</v>
@@ -10183,7 +10179,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>140</v>
@@ -10236,7 +10232,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C31" s="15" t="s">
         <v>142</v>
@@ -10289,7 +10285,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C32" s="15" t="s">
         <v>144</v>
@@ -10342,7 +10338,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>146</v>
@@ -10395,7 +10391,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C34" s="15" t="s">
         <v>152</v>
@@ -10448,7 +10444,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C35" s="15" t="s">
         <v>154</v>
@@ -10501,7 +10497,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C36" s="15" t="s">
         <v>156</v>
@@ -10554,7 +10550,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C37" s="15" t="s">
         <v>157</v>
@@ -10607,10 +10603,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D38" s="15" t="s">
         <v>155</v>
@@ -10649,7 +10645,7 @@
         <v>9900</v>
       </c>
       <c r="P38" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="Q38" s="16">
         <v>6600</v>
@@ -10660,10 +10656,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D39" s="15" t="s">
         <v>155</v>
@@ -10682,7 +10678,7 @@
       <c r="N39" s="18"/>
       <c r="O39" s="18"/>
       <c r="P39" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="Q39" s="18"/>
     </row>
@@ -10691,7 +10687,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C40" s="15" t="s">
         <v>166</v>
@@ -10744,7 +10740,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C41" s="15" t="s">
         <v>168</v>
@@ -10797,7 +10793,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C42" s="15" t="s">
         <v>171</v>
@@ -10850,7 +10846,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>173</v>
@@ -10903,7 +10899,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C44" s="15" t="s">
         <v>175</v>
@@ -10956,13 +10952,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E45" s="15" t="s">
         <v>170</v>
@@ -11009,7 +11005,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C46" s="15" t="s">
         <v>177</v>
@@ -11062,7 +11058,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C47" s="15" t="s">
         <v>181</v>
@@ -11115,7 +11111,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C48" s="15" t="s">
         <v>182</v>
@@ -11168,7 +11164,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C49" s="15" t="s">
         <v>184</v>
@@ -11221,7 +11217,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C50" s="15" t="s">
         <v>186</v>
@@ -11274,7 +11270,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C51" s="15" t="s">
         <v>188</v>
@@ -11327,7 +11323,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C52" s="15" t="s">
         <v>190</v>
@@ -11380,7 +11376,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C53" s="15" t="s">
         <v>192</v>
@@ -11433,10 +11429,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="15" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D54" s="15" t="s">
         <v>195</v>
@@ -11486,13 +11482,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="15" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C55" s="15" t="s">
         <v>196</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E55" s="15" t="s">
         <v>170</v>
@@ -11539,7 +11535,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="15" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C56" s="15" t="s">
         <v>198</v>
@@ -11592,7 +11588,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="15" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C57" s="15" t="s">
         <v>200</v>
@@ -11645,7 +11641,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C58" s="15" t="s">
         <v>202</v>
@@ -11698,7 +11694,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="15" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C59" s="15" t="s">
         <v>204</v>
@@ -11751,7 +11747,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C60" s="15" t="s">
         <v>206</v>
@@ -11804,13 +11800,13 @@
         <v>60</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C61" s="15" t="s">
         <v>209</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E61" s="15" t="s">
         <v>170</v>
@@ -11833,7 +11829,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C62" s="15" t="s">
         <v>211</v>
@@ -11886,13 +11882,13 @@
         <v>62</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E63" s="15" t="s">
         <v>170</v>
@@ -11939,16 +11935,16 @@
         <v>63</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E64" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F64" s="16">
         <v>6000</v>
@@ -11992,7 +11988,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C65" s="15" t="s">
         <v>216</v>
@@ -12021,7 +12017,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C66" s="15" t="s">
         <v>219</v>
@@ -12030,7 +12026,7 @@
         <v>220</v>
       </c>
       <c r="E66" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F66" s="16">
         <v>3100</v>
@@ -12074,7 +12070,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C67" s="15" t="s">
         <v>221</v>
@@ -12083,7 +12079,7 @@
         <v>222</v>
       </c>
       <c r="E67" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F67" s="16">
         <v>15000</v>
@@ -12127,7 +12123,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C68" s="15" t="s">
         <v>223</v>
@@ -12136,7 +12132,7 @@
         <v>224</v>
       </c>
       <c r="E68" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F68" s="16">
         <v>6300</v>
@@ -12180,7 +12176,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C69" s="15" t="s">
         <v>225</v>
@@ -12189,7 +12185,7 @@
         <v>226</v>
       </c>
       <c r="E69" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F69" s="16">
         <v>5400</v>
@@ -12233,16 +12229,16 @@
         <v>69</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C70" s="15" t="s">
         <v>227</v>
       </c>
       <c r="D70" s="15" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F70" s="16">
         <v>10000</v>
@@ -12286,7 +12282,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="15" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C71" s="15" t="s">
         <v>229</v>
@@ -12295,7 +12291,7 @@
         <v>230</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F71" s="16">
         <v>4700</v>
@@ -12339,7 +12335,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C72" s="15" t="s">
         <v>231</v>
@@ -12348,7 +12344,7 @@
         <v>232</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F72" s="16">
         <v>6300</v>
@@ -12392,7 +12388,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="15" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C73" s="15" t="s">
         <v>233</v>
@@ -12401,7 +12397,7 @@
         <v>234</v>
       </c>
       <c r="E73" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F73" s="16">
         <v>5000</v>
@@ -12445,7 +12441,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="15" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C74" s="15" t="s">
         <v>235</v>
@@ -12454,7 +12450,7 @@
         <v>236</v>
       </c>
       <c r="E74" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F74" s="16">
         <v>1400</v>
@@ -12498,7 +12494,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="15" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C75" s="15" t="s">
         <v>237</v>
@@ -12507,7 +12503,7 @@
         <v>238</v>
       </c>
       <c r="E75" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F75" s="16">
         <v>5000</v>
@@ -12551,16 +12547,16 @@
         <v>75</v>
       </c>
       <c r="B76" s="15" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C76" s="15" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D76" s="15" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E76" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F76" s="16">
         <v>7000</v>
@@ -12604,7 +12600,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="15" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C77" s="15" t="s">
         <v>105</v>
@@ -12613,7 +12609,7 @@
         <v>241</v>
       </c>
       <c r="E77" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F77" s="16">
         <v>5900</v>
@@ -12657,7 +12653,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="15" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C78" s="15" t="s">
         <v>242</v>
@@ -12666,7 +12662,7 @@
         <v>243</v>
       </c>
       <c r="E78" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F78" s="16">
         <v>6400</v>
@@ -12710,16 +12706,16 @@
         <v>78</v>
       </c>
       <c r="B79" s="15" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D79" s="15" t="s">
         <v>245</v>
       </c>
       <c r="E79" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F79" s="16">
         <v>8000</v>
@@ -12763,16 +12759,16 @@
         <v>79</v>
       </c>
       <c r="B80" s="15" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D80" s="15" t="s">
         <v>247</v>
       </c>
       <c r="E80" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F80" s="16">
         <v>5800</v>
@@ -12816,16 +12812,16 @@
         <v>80</v>
       </c>
       <c r="B81" s="15" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C81" s="15" t="s">
         <v>248</v>
       </c>
       <c r="D81" s="15" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E81" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F81" s="16">
         <v>11000</v>
@@ -12869,7 +12865,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="15" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C82" s="15" t="s">
         <v>250</v>
@@ -12878,7 +12874,7 @@
         <v>251</v>
       </c>
       <c r="E82" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F82" s="16">
         <v>4900</v>
@@ -12922,7 +12918,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="15" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C83" s="15" t="s">
         <v>252</v>
@@ -12931,7 +12927,7 @@
         <v>253</v>
       </c>
       <c r="E83" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F83" s="16">
         <v>5100</v>
@@ -12975,7 +12971,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="15" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C84" s="15" t="s">
         <v>254</v>
@@ -12984,7 +12980,7 @@
         <v>255</v>
       </c>
       <c r="E84" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F84" s="16">
         <v>2800</v>
@@ -13028,16 +13024,16 @@
         <v>84</v>
       </c>
       <c r="B85" s="15" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D85" s="15" t="s">
         <v>257</v>
       </c>
       <c r="E85" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F85" s="16">
         <v>5900</v>
@@ -13081,16 +13077,16 @@
         <v>85</v>
       </c>
       <c r="B86" s="15" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C86" s="15" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D86" s="15" t="s">
         <v>259</v>
       </c>
       <c r="E86" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F86" s="16">
         <v>5000</v>
@@ -13134,7 +13130,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="15" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C87" s="15" t="s">
         <v>260</v>
@@ -13143,7 +13139,7 @@
         <v>261</v>
       </c>
       <c r="E87" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F87" s="16">
         <v>8000</v>
@@ -13187,7 +13183,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C88" s="15" t="s">
         <v>262</v>
@@ -13196,7 +13192,7 @@
         <v>263</v>
       </c>
       <c r="E88" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F88" s="16">
         <v>2900</v>
@@ -13240,7 +13236,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="15" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C89" s="15" t="s">
         <v>264</v>
@@ -13293,7 +13289,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="15" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C90" s="15" t="s">
         <v>266</v>
@@ -13305,40 +13301,40 @@
         <v>265</v>
       </c>
       <c r="F90" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="G90" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H90" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="I90" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="J90" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="K90" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="L90" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M90" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N90" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O90" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P90" s="16">
         <v>1600</v>
       </c>
       <c r="Q90" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.2">
@@ -13346,7 +13342,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="15" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C91" s="15" t="s">
         <v>268</v>
@@ -13399,7 +13395,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C92" s="15" t="s">
         <v>270</v>
@@ -13452,7 +13448,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="15" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C93" s="15" t="s">
         <v>272</v>
@@ -13505,7 +13501,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="15" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C94" s="15" t="s">
         <v>274</v>
@@ -13558,7 +13554,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="15" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C95" s="15" t="s">
         <v>276</v>
@@ -13611,7 +13607,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="15" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C96" s="15" t="s">
         <v>278</v>
@@ -13664,13 +13660,13 @@
         <v>96</v>
       </c>
       <c r="B97" s="15" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C97" s="15" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D97" s="15" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E97" s="15" t="s">
         <v>265</v>
@@ -13717,7 +13713,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="15" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C98" s="15" t="s">
         <v>280</v>
@@ -13770,7 +13766,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="15" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C99" s="15" t="s">
         <v>282</v>
@@ -13823,7 +13819,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="15" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C100" s="15" t="s">
         <v>284</v>
@@ -13876,7 +13872,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="15" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C101" s="15" t="s">
         <v>286</v>
@@ -13929,10 +13925,10 @@
         <v>101</v>
       </c>
       <c r="B102" s="15" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C102" s="15" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D102" s="15" t="s">
         <v>289</v>
@@ -13982,7 +13978,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="15" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C103" s="15" t="s">
         <v>290</v>
@@ -14035,7 +14031,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="15" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C104" s="15" t="s">
         <v>292</v>
@@ -14088,7 +14084,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="15" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C105" s="15" t="s">
         <v>294</v>
@@ -14141,7 +14137,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="15" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C106" s="15" t="s">
         <v>296</v>
@@ -14194,7 +14190,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="15" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C107" s="15" t="s">
         <v>298</v>
@@ -14247,7 +14243,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="15" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C108" s="15" t="s">
         <v>300</v>
@@ -14300,7 +14296,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="15" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C109" s="15" t="s">
         <v>302</v>
@@ -14353,7 +14349,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="15" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C110" s="15" t="s">
         <v>304</v>
@@ -14406,7 +14402,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="15" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C111" s="15" t="s">
         <v>308</v>
@@ -14459,7 +14455,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="15" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C112" s="15" t="s">
         <v>310</v>
@@ -14512,7 +14508,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="15" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C113" s="15" t="s">
         <v>312</v>
@@ -14565,7 +14561,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="15" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C114" s="15" t="s">
         <v>314</v>
@@ -14618,7 +14614,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="15" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C115" s="15" t="s">
         <v>316</v>
@@ -14671,7 +14667,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="15" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C116" s="15" t="s">
         <v>318</v>
@@ -14724,7 +14720,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="15" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C117" s="15" t="s">
         <v>320</v>
@@ -14777,7 +14773,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="15" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C118" s="15" t="s">
         <v>322</v>
@@ -14830,7 +14826,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="15" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C119" s="15" t="s">
         <v>325</v>
@@ -14883,7 +14879,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="15" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C120" s="15" t="s">
         <v>327</v>
@@ -14936,7 +14932,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="15" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C121" s="15" t="s">
         <v>329</v>
@@ -14989,7 +14985,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="15" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C122" s="15" t="s">
         <v>331</v>
@@ -15042,7 +15038,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="15" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C123" s="15" t="s">
         <v>333</v>
@@ -15095,7 +15091,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="15" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C124" s="15" t="s">
         <v>335</v>
@@ -15148,7 +15144,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="15" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C125" s="15" t="s">
         <v>337</v>
@@ -15201,7 +15197,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="15" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C126" s="15" t="s">
         <v>339</v>
@@ -15254,7 +15250,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="15" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C127" s="15" t="s">
         <v>340</v>
@@ -15307,7 +15303,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="15" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C128" s="15" t="s">
         <v>342</v>
@@ -15360,7 +15356,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="15" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C129" s="15" t="s">
         <v>344</v>
@@ -15413,7 +15409,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="15" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C130" s="15" t="s">
         <v>346</v>
@@ -15466,7 +15462,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="15" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C131" s="15" t="s">
         <v>349</v>
@@ -15519,7 +15515,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="15" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C132" s="15" t="s">
         <v>351</v>
@@ -15572,7 +15568,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="15" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C133" s="15" t="s">
         <v>354</v>
@@ -15625,7 +15621,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="15" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C134" s="15" t="s">
         <v>356</v>
@@ -15678,7 +15674,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="15" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C135" s="15" t="s">
         <v>358</v>
@@ -15731,7 +15727,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="15" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C136" s="15" t="s">
         <v>360</v>
@@ -15784,7 +15780,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="15" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C137" s="15" t="s">
         <v>362</v>
@@ -15837,7 +15833,7 @@
         <v>137</v>
       </c>
       <c r="B138" s="15" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C138" s="15" t="s">
         <v>364</v>
@@ -15890,7 +15886,7 @@
         <v>138</v>
       </c>
       <c r="B139" s="15" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C139" s="15" t="s">
         <v>366</v>
@@ -15943,7 +15939,7 @@
         <v>139</v>
       </c>
       <c r="B140" s="15" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C140" s="15" t="s">
         <v>368</v>
@@ -15996,7 +15992,7 @@
         <v>140</v>
       </c>
       <c r="B141" s="15" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C141" s="15" t="s">
         <v>370</v>
@@ -16049,13 +16045,13 @@
         <v>141</v>
       </c>
       <c r="B142" s="15" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C142" s="15" t="s">
         <v>372</v>
       </c>
       <c r="D142" s="15" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E142" s="15" t="s">
         <v>324</v>
@@ -16102,10 +16098,10 @@
         <v>142</v>
       </c>
       <c r="B143" s="15" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C143" s="15" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="D143" s="15" t="s">
         <v>375</v>
@@ -16155,7 +16151,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="15" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C144" s="15" t="s">
         <v>378</v>
@@ -16208,7 +16204,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="15" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C145" s="15" t="s">
         <v>380</v>
@@ -16261,13 +16257,13 @@
         <v>145</v>
       </c>
       <c r="B146" s="15" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C146" s="15" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D146" s="15" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="E146" s="15" t="s">
         <v>162</v>
@@ -16314,13 +16310,13 @@
         <v>146</v>
       </c>
       <c r="B147" s="15" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C147" s="15" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D147" s="15" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E147" s="15" t="s">
         <v>162</v>
@@ -16367,7 +16363,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="15" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C148" s="15" t="s">
         <v>385</v>
@@ -16420,7 +16416,7 @@
         <v>148</v>
       </c>
       <c r="B149" s="15" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C149" s="15" t="s">
         <v>160</v>
@@ -16473,13 +16469,13 @@
         <v>149</v>
       </c>
       <c r="B150" s="15" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C150" s="15" t="s">
         <v>387</v>
       </c>
       <c r="D150" s="15" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E150" s="15" t="s">
         <v>162</v>
@@ -16526,7 +16522,7 @@
         <v>150</v>
       </c>
       <c r="B151" s="15" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C151" s="15" t="s">
         <v>389</v>
@@ -16579,7 +16575,7 @@
         <v>151</v>
       </c>
       <c r="B152" s="15" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C152" s="15" t="s">
         <v>391</v>
@@ -16632,52 +16628,52 @@
         <v>152</v>
       </c>
       <c r="B153" s="15" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C153" s="15" t="s">
         <v>393</v>
       </c>
       <c r="D153" s="15" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E153" s="15" t="s">
         <v>162</v>
       </c>
       <c r="F153" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="G153" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H153" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="I153" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="J153" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="K153" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="L153" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M153" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N153" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O153" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P153" s="15">
         <v>300</v>
       </c>
       <c r="Q153" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.2">
@@ -16685,7 +16681,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="15" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C154" s="15" t="s">
         <v>395</v>
@@ -16738,10 +16734,10 @@
         <v>154</v>
       </c>
       <c r="B155" s="15" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C155" s="15" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D155" s="15" t="s">
         <v>397</v>
@@ -16791,13 +16787,13 @@
         <v>155</v>
       </c>
       <c r="B156" s="15" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C156" s="15" t="s">
         <v>398</v>
       </c>
       <c r="D156" s="15" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E156" s="15" t="s">
         <v>162</v>
@@ -16844,7 +16840,7 @@
         <v>156</v>
       </c>
       <c r="B157" s="15" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C157" s="15" t="s">
         <v>400</v>
@@ -16897,7 +16893,7 @@
         <v>157</v>
       </c>
       <c r="B158" s="15" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C158" s="15" t="s">
         <v>402</v>
@@ -16950,10 +16946,10 @@
         <v>158</v>
       </c>
       <c r="B159" s="15" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C159" s="15" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D159" s="15" t="s">
         <v>405</v>
@@ -17003,7 +16999,7 @@
         <v>159</v>
       </c>
       <c r="B160" s="15" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C160" s="15" t="s">
         <v>406</v>
@@ -17056,7 +17052,7 @@
         <v>160</v>
       </c>
       <c r="B161" s="15" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C161" s="15" t="s">
         <v>408</v>
@@ -17109,7 +17105,7 @@
         <v>161</v>
       </c>
       <c r="B162" s="15" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C162" s="15" t="s">
         <v>410</v>
@@ -17162,10 +17158,10 @@
         <v>162</v>
       </c>
       <c r="B163" s="15" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C163" s="15" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D163" s="15" t="s">
         <v>413</v>
@@ -17215,13 +17211,13 @@
         <v>163</v>
       </c>
       <c r="B164" s="15" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C164" s="15" t="s">
         <v>414</v>
       </c>
       <c r="D164" s="15" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E164" s="15" t="s">
         <v>162</v>
@@ -17268,13 +17264,13 @@
         <v>164</v>
       </c>
       <c r="B165" s="15" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C165" s="15" t="s">
         <v>416</v>
       </c>
       <c r="D165" s="15" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E165" s="15" t="s">
         <v>162</v>
@@ -17321,7 +17317,7 @@
         <v>165</v>
       </c>
       <c r="B166" s="15" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C166" s="15" t="s">
         <v>418</v>
@@ -17374,10 +17370,10 @@
         <v>166</v>
       </c>
       <c r="B167" s="15" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C167" s="15" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D167" s="15" t="s">
         <v>421</v>
@@ -17427,7 +17423,7 @@
         <v>167</v>
       </c>
       <c r="B168" s="15" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C168" s="15" t="s">
         <v>422</v>
@@ -17480,10 +17476,10 @@
         <v>168</v>
       </c>
       <c r="B169" s="15" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C169" s="15" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D169" s="15" t="s">
         <v>425</v>
@@ -17533,7 +17529,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="15" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C170" s="15" t="s">
         <v>166</v>
@@ -17586,7 +17582,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="15" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C171" s="15" t="s">
         <v>427</v>
@@ -17639,7 +17635,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="15" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C172" s="15" t="s">
         <v>429</v>
@@ -17692,7 +17688,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="15" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C173" s="15" t="s">
         <v>431</v>
@@ -17745,7 +17741,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="15" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C174" s="15" t="s">
         <v>433</v>
@@ -17798,7 +17794,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="15" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C175" s="15" t="s">
         <v>437</v>
@@ -17851,10 +17847,10 @@
         <v>175</v>
       </c>
       <c r="B176" s="15" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C176" s="15" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D176" s="15" t="s">
         <v>440</v>
@@ -17904,7 +17900,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="15" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C177" s="15" t="s">
         <v>441</v>
@@ -17957,7 +17953,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="15" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C178" s="15" t="s">
         <v>95</v>
@@ -18010,7 +18006,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="15" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C179" s="15" t="s">
         <v>444</v>
@@ -18063,7 +18059,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="15" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C180" s="15" t="s">
         <v>446</v>
@@ -18096,7 +18092,7 @@
         <v>500</v>
       </c>
       <c r="M180" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N180" s="15">
         <v>400</v>
@@ -18116,7 +18112,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="15" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C181" s="15" t="s">
         <v>448</v>
@@ -18169,7 +18165,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="15" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C182" s="15" t="s">
         <v>450</v>
@@ -18222,7 +18218,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="15" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C183" s="15" t="s">
         <v>452</v>
@@ -18275,10 +18271,10 @@
         <v>183</v>
       </c>
       <c r="B184" s="15" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C184" s="15" t="s">
-        <v>731</v>
+        <v>148</v>
       </c>
       <c r="D184" s="15" t="s">
         <v>149</v>
@@ -18297,7 +18293,7 @@
       <c r="N184" s="18"/>
       <c r="O184" s="18"/>
       <c r="P184" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="Q184" s="18"/>
     </row>
@@ -18306,10 +18302,10 @@
         <v>184</v>
       </c>
       <c r="B185" s="15" t="s">
-        <v>716</v>
-      </c>
-      <c r="C185" s="5" t="s">
-        <v>132</v>
+        <v>717</v>
+      </c>
+      <c r="C185" s="15" t="s">
+        <v>150</v>
       </c>
       <c r="D185" s="15" t="s">
         <v>151</v>
@@ -18328,7 +18324,7 @@
       <c r="N185" s="18"/>
       <c r="O185" s="18"/>
       <c r="P185" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="Q185" s="18"/>
     </row>
@@ -18337,7 +18333,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="15" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C186" s="15" t="s">
         <v>215</v>
@@ -18359,7 +18355,7 @@
       <c r="N186" s="18"/>
       <c r="O186" s="18"/>
       <c r="P186" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="Q186" s="18"/>
     </row>

--- a/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
+++ b/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dee/Desktop/GitHub- Repo/tms/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EFCED16-3A68-2546-B5B2-BCD3452CEBDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E00CEF65-91F1-D04C-9110-23595466B9C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,6 +19,8 @@
     <sheet name="DB Target" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DB capacity'!$B$3:$F$199</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DB Target'!$A$1:$Q$186</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vehicle Database'!$A$1:$H$60</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1953" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1952" uniqueCount="732">
   <si>
     <t>S. N.</t>
   </si>
@@ -1400,9 +1402,6 @@
     <t>R S Deals</t>
   </si>
   <si>
-    <t>Other's</t>
-  </si>
-  <si>
     <t>FRANCHISE</t>
   </si>
   <si>
@@ -2232,6 +2231,12 @@
   </si>
   <si>
     <t>operational</t>
+  </si>
+  <si>
+    <t>Non Operational</t>
+  </si>
+  <si>
+    <t>GURU KRIPA BEVERAGES</t>
   </si>
 </sst>
 </file>
@@ -6274,7 +6279,7 @@
         <v>70</v>
       </c>
       <c r="F194" s="6">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="195" spans="2:6" x14ac:dyDescent="0.2">
@@ -6363,9 +6368,7 @@
       </c>
     </row>
     <row r="200" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B200" s="5" t="s">
-        <v>453</v>
-      </c>
+      <c r="B200" s="5"/>
       <c r="C200" s="4"/>
       <c r="D200" s="6"/>
       <c r="E200" s="6"/>
@@ -6373,7 +6376,7 @@
     </row>
     <row r="201" spans="2:6" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B201" s="12" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C201" s="12"/>
       <c r="D201" s="13"/>
@@ -6423,7 +6426,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="19" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -6449,7 +6452,7 @@
         <v>11</v>
       </c>
       <c r="H2" s="32" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -6461,7 +6464,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D3" s="20" t="s">
         <v>9</v>
@@ -6476,7 +6479,7 @@
         <v>11</v>
       </c>
       <c r="H3" s="32" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -6488,7 +6491,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>9</v>
@@ -6503,7 +6506,7 @@
         <v>11</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -6530,7 +6533,7 @@
         <v>11</v>
       </c>
       <c r="H5" s="32" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -6557,7 +6560,7 @@
         <v>11</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -6584,7 +6587,7 @@
         <v>11</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -6611,7 +6614,7 @@
         <v>11</v>
       </c>
       <c r="H8" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -6638,7 +6641,7 @@
         <v>11</v>
       </c>
       <c r="H9" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -6665,7 +6668,7 @@
         <v>11</v>
       </c>
       <c r="H10" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -6692,7 +6695,7 @@
         <v>11</v>
       </c>
       <c r="H11" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -6710,7 +6713,7 @@
         <v>9</v>
       </c>
       <c r="E12" s="21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F12" s="21" t="s">
         <v>10</v>
@@ -6719,7 +6722,7 @@
         <v>11</v>
       </c>
       <c r="H12" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -6746,7 +6749,7 @@
         <v>11</v>
       </c>
       <c r="H13" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -6773,7 +6776,7 @@
         <v>11</v>
       </c>
       <c r="H14" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -6800,7 +6803,7 @@
         <v>11</v>
       </c>
       <c r="H15" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -6827,7 +6830,7 @@
         <v>11</v>
       </c>
       <c r="H16" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
@@ -6854,7 +6857,7 @@
         <v>11</v>
       </c>
       <c r="H17" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -6881,7 +6884,7 @@
         <v>11</v>
       </c>
       <c r="H18" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -6908,7 +6911,7 @@
         <v>11</v>
       </c>
       <c r="H19" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -6935,7 +6938,7 @@
         <v>11</v>
       </c>
       <c r="H20" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
@@ -6962,7 +6965,7 @@
         <v>11</v>
       </c>
       <c r="H21" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
@@ -6989,7 +6992,7 @@
         <v>11</v>
       </c>
       <c r="H22" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
@@ -7016,7 +7019,7 @@
         <v>11</v>
       </c>
       <c r="H23" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
@@ -7043,7 +7046,7 @@
         <v>11</v>
       </c>
       <c r="H24" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
@@ -7070,7 +7073,7 @@
         <v>11</v>
       </c>
       <c r="H25" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
@@ -7097,7 +7100,7 @@
         <v>11</v>
       </c>
       <c r="H26" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -7124,7 +7127,7 @@
         <v>11</v>
       </c>
       <c r="H27" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
@@ -7151,7 +7154,7 @@
         <v>11</v>
       </c>
       <c r="H28" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
@@ -7178,7 +7181,7 @@
         <v>11</v>
       </c>
       <c r="H29" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
@@ -7205,7 +7208,7 @@
         <v>11</v>
       </c>
       <c r="H30" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -7232,7 +7235,7 @@
         <v>11</v>
       </c>
       <c r="H31" s="32" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
@@ -7259,7 +7262,7 @@
         <v>11</v>
       </c>
       <c r="H32" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
@@ -7286,7 +7289,7 @@
         <v>11</v>
       </c>
       <c r="H33" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
@@ -7298,7 +7301,7 @@
         <v>7</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D34" s="20" t="s">
         <v>9</v>
@@ -7313,7 +7316,7 @@
         <v>11</v>
       </c>
       <c r="H34" s="32" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
@@ -7340,7 +7343,7 @@
         <v>11</v>
       </c>
       <c r="H35" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
@@ -7367,7 +7370,7 @@
         <v>11</v>
       </c>
       <c r="H36" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -7394,7 +7397,7 @@
         <v>11</v>
       </c>
       <c r="H37" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
@@ -7448,7 +7451,7 @@
         <v>11</v>
       </c>
       <c r="H39" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
@@ -7475,7 +7478,7 @@
         <v>11</v>
       </c>
       <c r="H40" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
@@ -7487,7 +7490,7 @@
         <v>7</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D41" s="20" t="s">
         <v>9</v>
@@ -7502,7 +7505,7 @@
         <v>11</v>
       </c>
       <c r="H41" s="32" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
@@ -7529,7 +7532,7 @@
         <v>11</v>
       </c>
       <c r="H42" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
@@ -7556,7 +7559,7 @@
         <v>11</v>
       </c>
       <c r="H43" s="32" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
@@ -7583,7 +7586,7 @@
         <v>11</v>
       </c>
       <c r="H44" s="32" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
@@ -7595,7 +7598,7 @@
         <v>7</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D45" s="20" t="s">
         <v>9</v>
@@ -7610,7 +7613,7 @@
         <v>11</v>
       </c>
       <c r="H45" s="32" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
@@ -7637,7 +7640,7 @@
         <v>11</v>
       </c>
       <c r="H46" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
@@ -7664,7 +7667,7 @@
         <v>11</v>
       </c>
       <c r="H47" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
@@ -7691,7 +7694,7 @@
         <v>11</v>
       </c>
       <c r="H48" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
@@ -7718,7 +7721,7 @@
         <v>11</v>
       </c>
       <c r="H49" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
@@ -7730,7 +7733,7 @@
         <v>7</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D50" s="20" t="s">
         <v>9</v>
@@ -7745,7 +7748,7 @@
         <v>11</v>
       </c>
       <c r="H50" s="32" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
@@ -7772,7 +7775,7 @@
         <v>11</v>
       </c>
       <c r="H51" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
@@ -7799,7 +7802,7 @@
         <v>11</v>
       </c>
       <c r="H52" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
@@ -7826,7 +7829,7 @@
         <v>11</v>
       </c>
       <c r="H53" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
@@ -7880,7 +7883,7 @@
         <v>11</v>
       </c>
       <c r="H55" s="32" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
@@ -7892,7 +7895,7 @@
         <v>7</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D56" s="20" t="s">
         <v>9</v>
@@ -7907,7 +7910,7 @@
         <v>11</v>
       </c>
       <c r="H56" s="32" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
@@ -7934,7 +7937,7 @@
         <v>11</v>
       </c>
       <c r="H57" s="32" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
@@ -7946,7 +7949,7 @@
         <v>7</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D58" s="20" t="s">
         <v>9</v>
@@ -7961,7 +7964,7 @@
         <v>11</v>
       </c>
       <c r="H58" s="32" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
@@ -7988,7 +7991,7 @@
         <v>11</v>
       </c>
       <c r="H59" s="32" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
@@ -8015,7 +8018,7 @@
         <v>11</v>
       </c>
       <c r="H60" s="32" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
@@ -8544,15 +8547,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="27" t="s">
+        <v>454</v>
+      </c>
+      <c r="B1" s="28" t="s">
         <v>455</v>
-      </c>
-      <c r="B1" s="28" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="23" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B2" s="24">
         <v>1200</v>
@@ -8560,7 +8563,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B3">
         <v>1000</v>
@@ -8568,7 +8571,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="23" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B4" s="24">
         <v>800</v>
@@ -8576,7 +8579,7 @@
     </row>
     <row r="5" spans="1:2" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B5" s="24">
         <v>600</v>
@@ -8584,7 +8587,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="25" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B6" s="26">
         <v>350</v>
@@ -8592,34 +8595,34 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="29" t="s">
+        <v>461</v>
+      </c>
+      <c r="B12" s="29" t="s">
         <v>462</v>
-      </c>
-      <c r="B12" s="29" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="17" t="s">
+        <v>463</v>
+      </c>
+      <c r="B13" s="17" t="s">
         <v>464</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="17" t="s">
+        <v>465</v>
+      </c>
+      <c r="B14" s="17" t="s">
         <v>466</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="17" t="s">
+        <v>467</v>
+      </c>
+      <c r="B15" s="17" t="s">
         <v>468</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -8634,60 +8637,61 @@
   <cols>
     <col min="1" max="1" width="4.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
+        <v>469</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>470</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="C1" s="14" t="s">
         <v>471</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="D1" s="14" t="s">
         <v>472</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="E1" s="14" t="s">
         <v>473</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="F1" s="14" t="s">
         <v>474</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="G1" s="14" t="s">
         <v>475</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="H1" s="14" t="s">
         <v>476</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="I1" s="14" t="s">
         <v>477</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="J1" s="14" t="s">
         <v>478</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="K1" s="14" t="s">
         <v>479</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="L1" s="14" t="s">
         <v>480</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="M1" s="14" t="s">
         <v>481</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="N1" s="14" t="s">
         <v>482</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="O1" s="14" t="s">
         <v>483</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="P1" s="14" t="s">
         <v>484</v>
       </c>
-      <c r="P1" s="14" t="s">
+      <c r="Q1" s="14" t="s">
         <v>485</v>
-      </c>
-      <c r="Q1" s="14" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
@@ -8695,7 +8699,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>67</v>
@@ -8748,7 +8752,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>73</v>
@@ -8801,10 +8805,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>489</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>490</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>76</v>
@@ -8854,7 +8858,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>77</v>
@@ -8907,7 +8911,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>79</v>
@@ -8960,7 +8964,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>81</v>
@@ -9013,7 +9017,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>87</v>
@@ -9066,7 +9070,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>89</v>
@@ -9119,7 +9123,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>91</v>
@@ -9172,10 +9176,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="15" t="s">
+        <v>496</v>
+      </c>
+      <c r="C11" s="15" t="s">
         <v>497</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>498</v>
       </c>
       <c r="D11" s="15" t="s">
         <v>94</v>
@@ -9225,7 +9229,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>95</v>
@@ -9278,13 +9282,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>97</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E13" s="15" t="s">
         <v>69</v>
@@ -9331,7 +9335,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>99</v>
@@ -9384,7 +9388,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C15" s="15" t="s">
         <v>101</v>
@@ -9437,10 +9441,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="15" t="s">
+        <v>503</v>
+      </c>
+      <c r="C16" s="15" t="s">
         <v>504</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>505</v>
       </c>
       <c r="D16" s="15" t="s">
         <v>104</v>
@@ -9490,7 +9494,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>105</v>
@@ -9543,7 +9547,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C18" s="15" t="s">
         <v>107</v>
@@ -9596,13 +9600,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>111</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E19" s="15" t="s">
         <v>69</v>
@@ -9649,7 +9653,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C20" s="15" t="s">
         <v>113</v>
@@ -9702,7 +9706,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>115</v>
@@ -9755,7 +9759,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C22" s="15" t="s">
         <v>117</v>
@@ -9808,7 +9812,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>121</v>
@@ -9861,13 +9865,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C24" s="15" t="s">
         <v>123</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E24" s="15" t="s">
         <v>69</v>
@@ -9914,7 +9918,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C25" s="15" t="s">
         <v>128</v>
@@ -9967,7 +9971,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C26" s="15" t="s">
         <v>130</v>
@@ -10020,7 +10024,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C27" s="15" t="s">
         <v>134</v>
@@ -10073,7 +10077,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C28" s="15" t="s">
         <v>136</v>
@@ -10126,7 +10130,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>138</v>
@@ -10179,7 +10183,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>140</v>
@@ -10232,7 +10236,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C31" s="15" t="s">
         <v>142</v>
@@ -10285,7 +10289,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C32" s="15" t="s">
         <v>144</v>
@@ -10338,7 +10342,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>146</v>
@@ -10391,7 +10395,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C34" s="15" t="s">
         <v>152</v>
@@ -10444,7 +10448,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C35" s="15" t="s">
         <v>154</v>
@@ -10497,7 +10501,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C36" s="15" t="s">
         <v>156</v>
@@ -10550,7 +10554,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C37" s="15" t="s">
         <v>157</v>
@@ -10603,10 +10607,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="15" t="s">
+        <v>528</v>
+      </c>
+      <c r="C38" s="15" t="s">
         <v>529</v>
-      </c>
-      <c r="C38" s="15" t="s">
-        <v>530</v>
       </c>
       <c r="D38" s="15" t="s">
         <v>155</v>
@@ -10645,7 +10649,7 @@
         <v>9900</v>
       </c>
       <c r="P38" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="Q38" s="16">
         <v>6600</v>
@@ -10656,10 +10660,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="15" t="s">
+        <v>531</v>
+      </c>
+      <c r="C39" s="15" t="s">
         <v>532</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>533</v>
       </c>
       <c r="D39" s="15" t="s">
         <v>155</v>
@@ -10678,7 +10682,7 @@
       <c r="N39" s="18"/>
       <c r="O39" s="18"/>
       <c r="P39" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="Q39" s="18"/>
     </row>
@@ -10687,7 +10691,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C40" s="15" t="s">
         <v>166</v>
@@ -10740,7 +10744,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C41" s="15" t="s">
         <v>168</v>
@@ -10793,7 +10797,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C42" s="15" t="s">
         <v>171</v>
@@ -10846,7 +10850,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>173</v>
@@ -10899,7 +10903,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C44" s="15" t="s">
         <v>175</v>
@@ -10952,13 +10956,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="15" t="s">
+        <v>538</v>
+      </c>
+      <c r="C45" s="15" t="s">
         <v>539</v>
       </c>
-      <c r="C45" s="15" t="s">
+      <c r="D45" s="15" t="s">
         <v>540</v>
-      </c>
-      <c r="D45" s="15" t="s">
-        <v>541</v>
       </c>
       <c r="E45" s="15" t="s">
         <v>170</v>
@@ -11005,7 +11009,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C46" s="15" t="s">
         <v>177</v>
@@ -11058,7 +11062,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C47" s="15" t="s">
         <v>181</v>
@@ -11111,7 +11115,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C48" s="15" t="s">
         <v>182</v>
@@ -11164,7 +11168,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C49" s="15" t="s">
         <v>184</v>
@@ -11217,7 +11221,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C50" s="15" t="s">
         <v>186</v>
@@ -11270,7 +11274,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C51" s="15" t="s">
         <v>188</v>
@@ -11323,7 +11327,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C52" s="15" t="s">
         <v>190</v>
@@ -11376,7 +11380,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C53" s="15" t="s">
         <v>192</v>
@@ -11429,10 +11433,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="15" t="s">
+        <v>549</v>
+      </c>
+      <c r="C54" s="15" t="s">
         <v>550</v>
-      </c>
-      <c r="C54" s="15" t="s">
-        <v>551</v>
       </c>
       <c r="D54" s="15" t="s">
         <v>195</v>
@@ -11482,13 +11486,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="15" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C55" s="15" t="s">
         <v>196</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E55" s="15" t="s">
         <v>170</v>
@@ -11535,7 +11539,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="15" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C56" s="15" t="s">
         <v>198</v>
@@ -11588,7 +11592,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="15" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C57" s="15" t="s">
         <v>200</v>
@@ -11641,7 +11645,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C58" s="15" t="s">
         <v>202</v>
@@ -11694,7 +11698,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="15" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C59" s="15" t="s">
         <v>204</v>
@@ -11747,7 +11751,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C60" s="15" t="s">
         <v>206</v>
@@ -11800,13 +11804,13 @@
         <v>60</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C61" s="15" t="s">
         <v>209</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="E61" s="15" t="s">
         <v>170</v>
@@ -11829,7 +11833,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C62" s="15" t="s">
         <v>211</v>
@@ -11882,13 +11886,13 @@
         <v>62</v>
       </c>
       <c r="B63" s="15" t="s">
+        <v>561</v>
+      </c>
+      <c r="C63" s="15" t="s">
         <v>562</v>
       </c>
-      <c r="C63" s="15" t="s">
+      <c r="D63" s="15" t="s">
         <v>563</v>
-      </c>
-      <c r="D63" s="15" t="s">
-        <v>564</v>
       </c>
       <c r="E63" s="15" t="s">
         <v>170</v>
@@ -11935,16 +11939,16 @@
         <v>63</v>
       </c>
       <c r="B64" s="15" t="s">
+        <v>564</v>
+      </c>
+      <c r="C64" s="15" t="s">
         <v>565</v>
       </c>
-      <c r="C64" s="15" t="s">
+      <c r="D64" s="15" t="s">
         <v>566</v>
       </c>
-      <c r="D64" s="15" t="s">
+      <c r="E64" s="15" t="s">
         <v>567</v>
-      </c>
-      <c r="E64" s="15" t="s">
-        <v>568</v>
       </c>
       <c r="F64" s="16">
         <v>6000</v>
@@ -11988,7 +11992,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C65" s="15" t="s">
         <v>216</v>
@@ -12017,7 +12021,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C66" s="15" t="s">
         <v>219</v>
@@ -12026,7 +12030,7 @@
         <v>220</v>
       </c>
       <c r="E66" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F66" s="16">
         <v>3100</v>
@@ -12070,7 +12074,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C67" s="15" t="s">
         <v>221</v>
@@ -12079,7 +12083,7 @@
         <v>222</v>
       </c>
       <c r="E67" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F67" s="16">
         <v>15000</v>
@@ -12123,7 +12127,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C68" s="15" t="s">
         <v>223</v>
@@ -12132,7 +12136,7 @@
         <v>224</v>
       </c>
       <c r="E68" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F68" s="16">
         <v>6300</v>
@@ -12176,7 +12180,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C69" s="15" t="s">
         <v>225</v>
@@ -12185,7 +12189,7 @@
         <v>226</v>
       </c>
       <c r="E69" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F69" s="16">
         <v>5400</v>
@@ -12229,16 +12233,16 @@
         <v>69</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C70" s="15" t="s">
         <v>227</v>
       </c>
       <c r="D70" s="15" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F70" s="16">
         <v>10000</v>
@@ -12282,7 +12286,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="15" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C71" s="15" t="s">
         <v>229</v>
@@ -12291,7 +12295,7 @@
         <v>230</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F71" s="16">
         <v>4700</v>
@@ -12335,7 +12339,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C72" s="15" t="s">
         <v>231</v>
@@ -12344,7 +12348,7 @@
         <v>232</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F72" s="16">
         <v>6300</v>
@@ -12388,7 +12392,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="15" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C73" s="15" t="s">
         <v>233</v>
@@ -12397,7 +12401,7 @@
         <v>234</v>
       </c>
       <c r="E73" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F73" s="16">
         <v>5000</v>
@@ -12441,7 +12445,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="15" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C74" s="15" t="s">
         <v>235</v>
@@ -12450,7 +12454,7 @@
         <v>236</v>
       </c>
       <c r="E74" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F74" s="16">
         <v>1400</v>
@@ -12494,7 +12498,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="15" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C75" s="15" t="s">
         <v>237</v>
@@ -12503,7 +12507,7 @@
         <v>238</v>
       </c>
       <c r="E75" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F75" s="16">
         <v>5000</v>
@@ -12547,16 +12551,16 @@
         <v>75</v>
       </c>
       <c r="B76" s="15" t="s">
+        <v>580</v>
+      </c>
+      <c r="C76" s="15" t="s">
         <v>581</v>
       </c>
-      <c r="C76" s="15" t="s">
+      <c r="D76" s="15" t="s">
         <v>582</v>
       </c>
-      <c r="D76" s="15" t="s">
-        <v>583</v>
-      </c>
       <c r="E76" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F76" s="16">
         <v>7000</v>
@@ -12600,7 +12604,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="15" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C77" s="15" t="s">
         <v>105</v>
@@ -12609,7 +12613,7 @@
         <v>241</v>
       </c>
       <c r="E77" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F77" s="16">
         <v>5900</v>
@@ -12653,7 +12657,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="15" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C78" s="15" t="s">
         <v>242</v>
@@ -12662,7 +12666,7 @@
         <v>243</v>
       </c>
       <c r="E78" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F78" s="16">
         <v>6400</v>
@@ -12706,16 +12710,16 @@
         <v>78</v>
       </c>
       <c r="B79" s="15" t="s">
+        <v>585</v>
+      </c>
+      <c r="C79" s="15" t="s">
         <v>586</v>
-      </c>
-      <c r="C79" s="15" t="s">
-        <v>587</v>
       </c>
       <c r="D79" s="15" t="s">
         <v>245</v>
       </c>
       <c r="E79" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F79" s="16">
         <v>8000</v>
@@ -12759,16 +12763,16 @@
         <v>79</v>
       </c>
       <c r="B80" s="15" t="s">
+        <v>587</v>
+      </c>
+      <c r="C80" s="15" t="s">
         <v>588</v>
-      </c>
-      <c r="C80" s="15" t="s">
-        <v>589</v>
       </c>
       <c r="D80" s="15" t="s">
         <v>247</v>
       </c>
       <c r="E80" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F80" s="16">
         <v>5800</v>
@@ -12812,16 +12816,16 @@
         <v>80</v>
       </c>
       <c r="B81" s="15" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C81" s="15" t="s">
         <v>248</v>
       </c>
       <c r="D81" s="15" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E81" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F81" s="16">
         <v>11000</v>
@@ -12865,7 +12869,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="15" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C82" s="15" t="s">
         <v>250</v>
@@ -12874,7 +12878,7 @@
         <v>251</v>
       </c>
       <c r="E82" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F82" s="16">
         <v>4900</v>
@@ -12918,7 +12922,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="15" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C83" s="15" t="s">
         <v>252</v>
@@ -12927,7 +12931,7 @@
         <v>253</v>
       </c>
       <c r="E83" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F83" s="16">
         <v>5100</v>
@@ -12971,7 +12975,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="15" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C84" s="15" t="s">
         <v>254</v>
@@ -12980,7 +12984,7 @@
         <v>255</v>
       </c>
       <c r="E84" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F84" s="16">
         <v>2800</v>
@@ -13024,16 +13028,16 @@
         <v>84</v>
       </c>
       <c r="B85" s="15" t="s">
+        <v>594</v>
+      </c>
+      <c r="C85" s="15" t="s">
         <v>595</v>
-      </c>
-      <c r="C85" s="15" t="s">
-        <v>596</v>
       </c>
       <c r="D85" s="15" t="s">
         <v>257</v>
       </c>
       <c r="E85" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F85" s="16">
         <v>5900</v>
@@ -13077,16 +13081,16 @@
         <v>85</v>
       </c>
       <c r="B86" s="15" t="s">
+        <v>596</v>
+      </c>
+      <c r="C86" s="15" t="s">
         <v>597</v>
-      </c>
-      <c r="C86" s="15" t="s">
-        <v>598</v>
       </c>
       <c r="D86" s="15" t="s">
         <v>259</v>
       </c>
       <c r="E86" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F86" s="16">
         <v>5000</v>
@@ -13130,7 +13134,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="15" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C87" s="15" t="s">
         <v>260</v>
@@ -13139,7 +13143,7 @@
         <v>261</v>
       </c>
       <c r="E87" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F87" s="16">
         <v>8000</v>
@@ -13183,7 +13187,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C88" s="15" t="s">
         <v>262</v>
@@ -13192,7 +13196,7 @@
         <v>263</v>
       </c>
       <c r="E88" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F88" s="16">
         <v>2900</v>
@@ -13236,7 +13240,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="15" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C89" s="15" t="s">
         <v>264</v>
@@ -13289,7 +13293,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="15" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C90" s="15" t="s">
         <v>266</v>
@@ -13301,40 +13305,40 @@
         <v>265</v>
       </c>
       <c r="F90" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="G90" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H90" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I90" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="J90" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="K90" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="L90" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="M90" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="N90" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="O90" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="P90" s="16">
         <v>1600</v>
       </c>
       <c r="Q90" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.2">
@@ -13342,7 +13346,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="15" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C91" s="15" t="s">
         <v>268</v>
@@ -13395,7 +13399,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C92" s="15" t="s">
         <v>270</v>
@@ -13448,7 +13452,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="15" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C93" s="15" t="s">
         <v>272</v>
@@ -13501,7 +13505,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="15" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C94" s="15" t="s">
         <v>274</v>
@@ -13554,7 +13558,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="15" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C95" s="15" t="s">
         <v>276</v>
@@ -13607,7 +13611,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="15" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C96" s="15" t="s">
         <v>278</v>
@@ -13660,13 +13664,13 @@
         <v>96</v>
       </c>
       <c r="B97" s="15" t="s">
+        <v>608</v>
+      </c>
+      <c r="C97" s="15" t="s">
         <v>609</v>
       </c>
-      <c r="C97" s="15" t="s">
+      <c r="D97" s="15" t="s">
         <v>610</v>
-      </c>
-      <c r="D97" s="15" t="s">
-        <v>611</v>
       </c>
       <c r="E97" s="15" t="s">
         <v>265</v>
@@ -13713,7 +13717,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="15" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C98" s="15" t="s">
         <v>280</v>
@@ -13766,7 +13770,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="15" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C99" s="15" t="s">
         <v>282</v>
@@ -13819,7 +13823,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="15" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C100" s="15" t="s">
         <v>284</v>
@@ -13872,7 +13876,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="15" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C101" s="15" t="s">
         <v>286</v>
@@ -13925,10 +13929,10 @@
         <v>101</v>
       </c>
       <c r="B102" s="15" t="s">
+        <v>615</v>
+      </c>
+      <c r="C102" s="15" t="s">
         <v>616</v>
-      </c>
-      <c r="C102" s="15" t="s">
-        <v>617</v>
       </c>
       <c r="D102" s="15" t="s">
         <v>289</v>
@@ -13978,7 +13982,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="15" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C103" s="15" t="s">
         <v>290</v>
@@ -14031,7 +14035,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="15" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C104" s="15" t="s">
         <v>292</v>
@@ -14084,7 +14088,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="15" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C105" s="15" t="s">
         <v>294</v>
@@ -14137,7 +14141,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="15" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C106" s="15" t="s">
         <v>296</v>
@@ -14190,7 +14194,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C107" s="15" t="s">
         <v>298</v>
@@ -14243,7 +14247,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="15" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C108" s="15" t="s">
         <v>300</v>
@@ -14296,7 +14300,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="15" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C109" s="15" t="s">
         <v>302</v>
@@ -14349,7 +14353,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="15" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C110" s="15" t="s">
         <v>304</v>
@@ -14402,7 +14406,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="15" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C111" s="15" t="s">
         <v>308</v>
@@ -14455,7 +14459,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="15" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C112" s="15" t="s">
         <v>310</v>
@@ -14508,7 +14512,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="15" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C113" s="15" t="s">
         <v>312</v>
@@ -14561,7 +14565,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="15" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C114" s="15" t="s">
         <v>314</v>
@@ -14614,7 +14618,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="15" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C115" s="15" t="s">
         <v>316</v>
@@ -14667,7 +14671,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="15" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C116" s="15" t="s">
         <v>318</v>
@@ -14720,7 +14724,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="15" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C117" s="15" t="s">
         <v>320</v>
@@ -14773,7 +14777,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="15" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C118" s="15" t="s">
         <v>322</v>
@@ -14826,7 +14830,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="15" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C119" s="15" t="s">
         <v>325</v>
@@ -14879,7 +14883,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="15" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C120" s="15" t="s">
         <v>327</v>
@@ -14932,7 +14936,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="15" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C121" s="15" t="s">
         <v>329</v>
@@ -14985,7 +14989,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="15" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C122" s="15" t="s">
         <v>331</v>
@@ -15038,7 +15042,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="15" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C123" s="15" t="s">
         <v>333</v>
@@ -15091,7 +15095,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="15" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C124" s="15" t="s">
         <v>335</v>
@@ -15144,7 +15148,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="15" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C125" s="15" t="s">
         <v>337</v>
@@ -15197,7 +15201,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="15" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C126" s="15" t="s">
         <v>339</v>
@@ -15250,7 +15254,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="15" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C127" s="15" t="s">
         <v>340</v>
@@ -15303,7 +15307,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="15" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C128" s="15" t="s">
         <v>342</v>
@@ -15356,7 +15360,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="15" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C129" s="15" t="s">
         <v>344</v>
@@ -15409,7 +15413,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="15" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C130" s="15" t="s">
         <v>346</v>
@@ -15462,7 +15466,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="15" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C131" s="15" t="s">
         <v>349</v>
@@ -15515,7 +15519,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="15" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C132" s="15" t="s">
         <v>351</v>
@@ -15568,7 +15572,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="15" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C133" s="15" t="s">
         <v>354</v>
@@ -15621,7 +15625,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="15" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C134" s="15" t="s">
         <v>356</v>
@@ -15674,7 +15678,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="15" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C135" s="15" t="s">
         <v>358</v>
@@ -15727,7 +15731,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="15" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C136" s="15" t="s">
         <v>360</v>
@@ -15780,7 +15784,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="15" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C137" s="15" t="s">
         <v>362</v>
@@ -15833,7 +15837,7 @@
         <v>137</v>
       </c>
       <c r="B138" s="15" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C138" s="15" t="s">
         <v>364</v>
@@ -15886,7 +15890,7 @@
         <v>138</v>
       </c>
       <c r="B139" s="15" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C139" s="15" t="s">
         <v>366</v>
@@ -15939,7 +15943,7 @@
         <v>139</v>
       </c>
       <c r="B140" s="15" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C140" s="15" t="s">
         <v>368</v>
@@ -15992,7 +15996,7 @@
         <v>140</v>
       </c>
       <c r="B141" s="15" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C141" s="15" t="s">
         <v>370</v>
@@ -16045,13 +16049,13 @@
         <v>141</v>
       </c>
       <c r="B142" s="15" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C142" s="15" t="s">
         <v>372</v>
       </c>
       <c r="D142" s="15" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E142" s="15" t="s">
         <v>324</v>
@@ -16098,10 +16102,10 @@
         <v>142</v>
       </c>
       <c r="B143" s="15" t="s">
+        <v>658</v>
+      </c>
+      <c r="C143" s="15" t="s">
         <v>659</v>
-      </c>
-      <c r="C143" s="15" t="s">
-        <v>660</v>
       </c>
       <c r="D143" s="15" t="s">
         <v>375</v>
@@ -16151,7 +16155,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="15" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C144" s="15" t="s">
         <v>378</v>
@@ -16204,7 +16208,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="15" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C145" s="15" t="s">
         <v>380</v>
@@ -16257,13 +16261,13 @@
         <v>145</v>
       </c>
       <c r="B146" s="15" t="s">
+        <v>662</v>
+      </c>
+      <c r="C146" s="15" t="s">
         <v>663</v>
       </c>
-      <c r="C146" s="15" t="s">
+      <c r="D146" s="15" t="s">
         <v>664</v>
-      </c>
-      <c r="D146" s="15" t="s">
-        <v>665</v>
       </c>
       <c r="E146" s="15" t="s">
         <v>162</v>
@@ -16310,13 +16314,13 @@
         <v>146</v>
       </c>
       <c r="B147" s="15" t="s">
+        <v>665</v>
+      </c>
+      <c r="C147" s="15" t="s">
         <v>666</v>
       </c>
-      <c r="C147" s="15" t="s">
+      <c r="D147" s="15" t="s">
         <v>667</v>
-      </c>
-      <c r="D147" s="15" t="s">
-        <v>668</v>
       </c>
       <c r="E147" s="15" t="s">
         <v>162</v>
@@ -16363,7 +16367,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="15" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C148" s="15" t="s">
         <v>385</v>
@@ -16416,7 +16420,7 @@
         <v>148</v>
       </c>
       <c r="B149" s="15" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C149" s="15" t="s">
         <v>160</v>
@@ -16469,13 +16473,13 @@
         <v>149</v>
       </c>
       <c r="B150" s="15" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C150" s="15" t="s">
         <v>387</v>
       </c>
       <c r="D150" s="15" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E150" s="15" t="s">
         <v>162</v>
@@ -16522,7 +16526,7 @@
         <v>150</v>
       </c>
       <c r="B151" s="15" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C151" s="15" t="s">
         <v>389</v>
@@ -16575,7 +16579,7 @@
         <v>151</v>
       </c>
       <c r="B152" s="15" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C152" s="15" t="s">
         <v>391</v>
@@ -16628,52 +16632,52 @@
         <v>152</v>
       </c>
       <c r="B153" s="15" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C153" s="15" t="s">
         <v>393</v>
       </c>
       <c r="D153" s="15" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E153" s="15" t="s">
         <v>162</v>
       </c>
       <c r="F153" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="G153" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H153" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I153" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="J153" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="K153" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="L153" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="M153" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="N153" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="O153" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="P153" s="15">
         <v>300</v>
       </c>
       <c r="Q153" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.2">
@@ -16681,7 +16685,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="15" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C154" s="15" t="s">
         <v>395</v>
@@ -16734,10 +16738,10 @@
         <v>154</v>
       </c>
       <c r="B155" s="15" t="s">
+        <v>677</v>
+      </c>
+      <c r="C155" s="15" t="s">
         <v>678</v>
-      </c>
-      <c r="C155" s="15" t="s">
-        <v>679</v>
       </c>
       <c r="D155" s="15" t="s">
         <v>397</v>
@@ -16787,13 +16791,13 @@
         <v>155</v>
       </c>
       <c r="B156" s="15" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C156" s="15" t="s">
         <v>398</v>
       </c>
       <c r="D156" s="15" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E156" s="15" t="s">
         <v>162</v>
@@ -16840,7 +16844,7 @@
         <v>156</v>
       </c>
       <c r="B157" s="15" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C157" s="15" t="s">
         <v>400</v>
@@ -16893,7 +16897,7 @@
         <v>157</v>
       </c>
       <c r="B158" s="15" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C158" s="15" t="s">
         <v>402</v>
@@ -16946,10 +16950,10 @@
         <v>158</v>
       </c>
       <c r="B159" s="15" t="s">
+        <v>683</v>
+      </c>
+      <c r="C159" s="15" t="s">
         <v>684</v>
-      </c>
-      <c r="C159" s="15" t="s">
-        <v>685</v>
       </c>
       <c r="D159" s="15" t="s">
         <v>405</v>
@@ -16999,7 +17003,7 @@
         <v>159</v>
       </c>
       <c r="B160" s="15" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C160" s="15" t="s">
         <v>406</v>
@@ -17052,7 +17056,7 @@
         <v>160</v>
       </c>
       <c r="B161" s="15" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C161" s="15" t="s">
         <v>408</v>
@@ -17105,7 +17109,7 @@
         <v>161</v>
       </c>
       <c r="B162" s="15" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C162" s="15" t="s">
         <v>410</v>
@@ -17158,10 +17162,10 @@
         <v>162</v>
       </c>
       <c r="B163" s="15" t="s">
+        <v>688</v>
+      </c>
+      <c r="C163" s="15" t="s">
         <v>689</v>
-      </c>
-      <c r="C163" s="15" t="s">
-        <v>690</v>
       </c>
       <c r="D163" s="15" t="s">
         <v>413</v>
@@ -17211,13 +17215,13 @@
         <v>163</v>
       </c>
       <c r="B164" s="15" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C164" s="15" t="s">
         <v>414</v>
       </c>
       <c r="D164" s="15" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E164" s="15" t="s">
         <v>162</v>
@@ -17264,13 +17268,13 @@
         <v>164</v>
       </c>
       <c r="B165" s="15" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C165" s="15" t="s">
         <v>416</v>
       </c>
       <c r="D165" s="15" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E165" s="15" t="s">
         <v>162</v>
@@ -17317,7 +17321,7 @@
         <v>165</v>
       </c>
       <c r="B166" s="15" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C166" s="15" t="s">
         <v>418</v>
@@ -17370,10 +17374,10 @@
         <v>166</v>
       </c>
       <c r="B167" s="15" t="s">
+        <v>695</v>
+      </c>
+      <c r="C167" s="15" t="s">
         <v>696</v>
-      </c>
-      <c r="C167" s="15" t="s">
-        <v>697</v>
       </c>
       <c r="D167" s="15" t="s">
         <v>421</v>
@@ -17423,7 +17427,7 @@
         <v>167</v>
       </c>
       <c r="B168" s="15" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C168" s="15" t="s">
         <v>422</v>
@@ -17476,10 +17480,10 @@
         <v>168</v>
       </c>
       <c r="B169" s="15" t="s">
+        <v>698</v>
+      </c>
+      <c r="C169" s="15" t="s">
         <v>699</v>
-      </c>
-      <c r="C169" s="15" t="s">
-        <v>700</v>
       </c>
       <c r="D169" s="15" t="s">
         <v>425</v>
@@ -17529,7 +17533,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="15" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C170" s="15" t="s">
         <v>166</v>
@@ -17582,7 +17586,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="15" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C171" s="15" t="s">
         <v>427</v>
@@ -17635,7 +17639,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="15" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C172" s="15" t="s">
         <v>429</v>
@@ -17688,7 +17692,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="15" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C173" s="15" t="s">
         <v>431</v>
@@ -17741,7 +17745,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="15" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C174" s="15" t="s">
         <v>433</v>
@@ -17794,7 +17798,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="15" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C175" s="15" t="s">
         <v>437</v>
@@ -17847,10 +17851,10 @@
         <v>175</v>
       </c>
       <c r="B176" s="15" t="s">
+        <v>706</v>
+      </c>
+      <c r="C176" s="15" t="s">
         <v>707</v>
-      </c>
-      <c r="C176" s="15" t="s">
-        <v>708</v>
       </c>
       <c r="D176" s="15" t="s">
         <v>440</v>
@@ -17900,7 +17904,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="15" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C177" s="15" t="s">
         <v>441</v>
@@ -17953,7 +17957,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="15" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C178" s="15" t="s">
         <v>95</v>
@@ -18006,7 +18010,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="15" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C179" s="15" t="s">
         <v>444</v>
@@ -18059,7 +18063,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="15" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C180" s="15" t="s">
         <v>446</v>
@@ -18092,7 +18096,7 @@
         <v>500</v>
       </c>
       <c r="M180" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="N180" s="15">
         <v>400</v>
@@ -18112,7 +18116,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="15" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C181" s="15" t="s">
         <v>448</v>
@@ -18165,7 +18169,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="15" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C182" s="15" t="s">
         <v>450</v>
@@ -18218,7 +18222,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="15" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C183" s="15" t="s">
         <v>452</v>
@@ -18271,10 +18275,10 @@
         <v>183</v>
       </c>
       <c r="B184" s="15" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C184" s="15" t="s">
-        <v>148</v>
+        <v>731</v>
       </c>
       <c r="D184" s="15" t="s">
         <v>149</v>
@@ -18293,7 +18297,7 @@
       <c r="N184" s="18"/>
       <c r="O184" s="18"/>
       <c r="P184" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="Q184" s="18"/>
     </row>
@@ -18302,10 +18306,10 @@
         <v>184</v>
       </c>
       <c r="B185" s="15" t="s">
-        <v>717</v>
-      </c>
-      <c r="C185" s="15" t="s">
-        <v>150</v>
+        <v>716</v>
+      </c>
+      <c r="C185" s="5" t="s">
+        <v>132</v>
       </c>
       <c r="D185" s="15" t="s">
         <v>151</v>
@@ -18324,7 +18328,7 @@
       <c r="N185" s="18"/>
       <c r="O185" s="18"/>
       <c r="P185" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="Q185" s="18"/>
     </row>
@@ -18333,7 +18337,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="15" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C186" s="15" t="s">
         <v>215</v>
@@ -18355,7 +18359,7 @@
       <c r="N186" s="18"/>
       <c r="O186" s="18"/>
       <c r="P186" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="Q186" s="18"/>
     </row>

--- a/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
+++ b/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dee/Desktop/GitHub- Repo/tms/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E00CEF65-91F1-D04C-9110-23595466B9C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93BB164A-6D57-0447-9826-2F79F3310869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17480" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DB capacity" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1952" uniqueCount="732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1960" uniqueCount="736">
   <si>
     <t>S. N.</t>
   </si>
@@ -2237,6 +2237,18 @@
   </si>
   <si>
     <t>GURU KRIPA BEVERAGES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zepto </t>
+  </si>
+  <si>
+    <t>Hasanganj</t>
+  </si>
+  <si>
+    <t>LKFLVD0001</t>
+  </si>
+  <si>
+    <t>Zepto</t>
   </si>
 </sst>
 </file>
@@ -2604,7 +2616,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2676,6 +2688,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma 4 4 2 2 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
@@ -6368,11 +6384,21 @@
       </c>
     </row>
     <row r="200" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B200" s="5"/>
-      <c r="C200" s="4"/>
-      <c r="D200" s="6"/>
-      <c r="E200" s="6"/>
-      <c r="F200" s="6"/>
+      <c r="B200" s="5" t="s">
+        <v>732</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="D200" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E200" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F200" s="6">
+        <v>18</v>
+      </c>
     </row>
     <row r="201" spans="2:6" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B201" s="12" t="s">
@@ -8632,7 +8658,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:Q186"/>
+  <dimension ref="A1:Q187"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.33203125" bestFit="1" customWidth="1"/>
@@ -18308,7 +18334,7 @@
       <c r="B185" s="15" t="s">
         <v>716</v>
       </c>
-      <c r="C185" s="5" t="s">
+      <c r="C185" s="33" t="s">
         <v>132</v>
       </c>
       <c r="D185" s="15" t="s">
@@ -18363,6 +18389,35 @@
       </c>
       <c r="Q186" s="18"/>
     </row>
+    <row r="187" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A187" s="34">
+        <v>186</v>
+      </c>
+      <c r="B187" s="15" t="s">
+        <v>734</v>
+      </c>
+      <c r="C187" s="34" t="s">
+        <v>735</v>
+      </c>
+      <c r="D187" s="34" t="s">
+        <v>733</v>
+      </c>
+      <c r="E187" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F187" s="32"/>
+      <c r="G187" s="32"/>
+      <c r="H187" s="32"/>
+      <c r="I187" s="32"/>
+      <c r="J187" s="32"/>
+      <c r="K187" s="32"/>
+      <c r="L187" s="32"/>
+      <c r="M187" s="32"/>
+      <c r="N187" s="32"/>
+      <c r="O187" s="32"/>
+      <c r="P187" s="32"/>
+      <c r="Q187" s="32"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
+++ b/data/Distributor_wise_Max_Vehicle_Capacity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dee/Desktop/GitHub- Repo/tms/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93BB164A-6D57-0447-9826-2F79F3310869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFA6B852-3664-F24F-8F49-AF386B75E277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17480" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1960" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1968" uniqueCount="738">
   <si>
     <t>S. N.</t>
   </si>
@@ -2249,6 +2249,12 @@
   </si>
   <si>
     <t>Zepto</t>
+  </si>
+  <si>
+    <t>MAA SHAKTI TRADERS</t>
+  </si>
+  <si>
+    <t>LKFLVD0002</t>
   </si>
 </sst>
 </file>
@@ -3029,7 +3035,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:F201"/>
+  <dimension ref="B2:F202"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="30.83203125" bestFit="1" customWidth="1"/>
@@ -6385,29 +6391,46 @@
     </row>
     <row r="200" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B200" s="5" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>733</v>
+        <v>147</v>
       </c>
       <c r="D200" s="6" t="s">
         <v>69</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>70</v>
+        <v>208</v>
       </c>
       <c r="F200" s="6">
         <v>18</v>
       </c>
     </row>
-    <row r="201" spans="2:6" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B201" s="12" t="s">
+    <row r="201" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B201" s="5" t="s">
+        <v>732</v>
+      </c>
+      <c r="C201" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="D201" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E201" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F201" s="6">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="202" spans="2:6" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B202" s="12" t="s">
         <v>453</v>
       </c>
-      <c r="C201" s="12"/>
-      <c r="D201" s="13"/>
-      <c r="E201" s="13"/>
-      <c r="F201" s="13"/>
+      <c r="C202" s="12"/>
+      <c r="D202" s="13"/>
+      <c r="E202" s="13"/>
+      <c r="F202" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8658,7 +8681,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:Q187"/>
+  <dimension ref="A1:Q188"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.33203125" bestFit="1" customWidth="1"/>
@@ -18390,19 +18413,19 @@
       <c r="Q186" s="18"/>
     </row>
     <row r="187" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A187" s="34">
+      <c r="A187" s="15">
         <v>186</v>
       </c>
       <c r="B187" s="15" t="s">
         <v>734</v>
       </c>
-      <c r="C187" s="34" t="s">
+      <c r="C187" s="15" t="s">
         <v>735</v>
       </c>
-      <c r="D187" s="34" t="s">
+      <c r="D187" s="15" t="s">
         <v>733</v>
       </c>
-      <c r="E187" s="34" t="s">
+      <c r="E187" s="15" t="s">
         <v>69</v>
       </c>
       <c r="F187" s="32"/>
@@ -18418,6 +18441,35 @@
       <c r="P187" s="32"/>
       <c r="Q187" s="32"/>
     </row>
+    <row r="188" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A188" s="34">
+        <v>187</v>
+      </c>
+      <c r="B188" s="15" t="s">
+        <v>737</v>
+      </c>
+      <c r="C188" s="33" t="s">
+        <v>736</v>
+      </c>
+      <c r="D188" s="34" t="s">
+        <v>147</v>
+      </c>
+      <c r="E188" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F188" s="32"/>
+      <c r="G188" s="32"/>
+      <c r="H188" s="32"/>
+      <c r="I188" s="32"/>
+      <c r="J188" s="32"/>
+      <c r="K188" s="32"/>
+      <c r="L188" s="32"/>
+      <c r="M188" s="32"/>
+      <c r="N188" s="32"/>
+      <c r="O188" s="32"/>
+      <c r="P188" s="32"/>
+      <c r="Q188" s="32"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
